--- a/vault-dalarna-university/02 IHV/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Omfång på lärandemål.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$234</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E107"/>
+  <dimension ref="A1:E234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AFT2CA</t>
+          <t>AFT2C8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -487,19 +487,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>32 ord: - redogöra för och värdera olika sätt att kategorisera smärta i förhållande till…</t>
+          <t>40 ord: - presentera och argumentera för vald design av en projektplan för en vetenskapl…</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2CA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AFT2CB</t>
+          <t>AFT2C9</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -514,19 +514,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>28 ord: - redogöra för centrala anpassningar i organ och vävnader som följer av regelbun…</t>
+          <t>29 ord: - genomföra en vetenskaplig undersökning med relevant design, metod och analys s…</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2CB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AFT2CB</t>
+          <t>AFT2C9</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -541,19 +541,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>28 ord: - genomföra enklare datainsamling av fysisk aktivitetsnivå och fysisk prestation…</t>
+          <t>36 ord: - analysera och värdera resultat från den vetenskapliga undersökningen i relatio…</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2CB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AFT2CB</t>
+          <t>AFT2C9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -568,24 +568,24 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>31 ord: - med stöd i relevant teoribildning identifiera hinder och underlättande faktore…</t>
+          <t>26 ord: - presentera, sammanfatta och försvara eget självständigt arbete, samt som oppon…</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2CB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AIH237</t>
+          <t>AFT2CA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>FYS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -595,24 +595,24 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>29 ord: - självständigt identifiera ett idrottsdidaktiskt problemområde och formulera fo…</t>
+          <t>32 ord: - redogöra för och värdera olika sätt att kategorisera smärta i förhållande till…</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH237</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2CA</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>AIH237</t>
+          <t>AFT2CB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>FYS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -622,24 +622,24 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>31 ord: - utifrån ett vetenskapsteoretiskt perspektiv diskutera kvalitativ och kvantitat…</t>
+          <t>28 ord: - redogöra för centrala anpassningar i organ och vävnader som följer av regelbun…</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH237</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2CB</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AIH237</t>
+          <t>AFT2CB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>FYS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -649,24 +649,24 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>30 ord: - genomföra ett självständigt idrottsdidaktiskt vetenskapligt arbete med tydlig …</t>
+          <t>28 ord: - genomföra enklare datainsamling av fysisk aktivitetsnivå och fysisk prestation…</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH237</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2CB</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AIH24T</t>
+          <t>AFT2CB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>FYS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -676,19 +676,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>29 ord: - självständigt identifiera ett idrottsdidaktiskt problemområde och formulera fo…</t>
+          <t>31 ord: - med stöd i relevant teoribildning identifiera hinder och underlättande faktore…</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH24T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2CB</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AIH24T</t>
+          <t>AIH237</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -703,19 +703,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>31 ord: - utifrån ett vetenskapsteoretiskt perspektiv diskutera kvalitativ och kvantitat…</t>
+          <t>29 ord: - självständigt identifiera ett idrottsdidaktiskt problemområde och formulera fo…</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH24T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH237</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AIH24T</t>
+          <t>AIH237</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -730,19 +730,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>30 ord: - genomföra ett självständigt idrottsdidaktiskt vetenskapligt arbete med tydlig …</t>
+          <t>31 ord: - utifrån ett vetenskapsteoretiskt perspektiv diskutera kvalitativ och kvantitat…</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH24T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH237</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZC</t>
+          <t>AIH237</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -752,24 +752,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>30 ord: - genomföra ett självständigt idrottsdidaktiskt vetenskapligt arbete med tydlig …</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH237</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZC</t>
+          <t>AIH24T</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -784,19 +784,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>26 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
+          <t>29 ord: - självständigt identifiera ett idrottsdidaktiskt problemområde och formulera fo…</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH24T</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZD</t>
+          <t>AIH24T</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -806,24 +806,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>31 ord: - utifrån ett vetenskapsteoretiskt perspektiv diskutera kvalitativ och kvantitat…</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH24T</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZD</t>
+          <t>AIH24T</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -838,19 +838,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
+          <t>30 ord: - genomföra ett självständigt idrottsdidaktiskt vetenskapligt arbete med tydlig …</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH24T</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZE</t>
+          <t>GIH2D8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -865,19 +865,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>2 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GIH32Z</t>
+          <t>GIH2D9</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -892,19 +892,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>2 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH32Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GIH335</t>
+          <t>GIH2DB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -924,14 +924,14 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH335</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DB</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GIH335</t>
+          <t>GIH2DC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -941,24 +941,24 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>27 ord: - formulera en affärsplan med tillhörande budget inom området idrott och hälsa s…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH335</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DC</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GIH34S</t>
+          <t>GIH2DD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -968,24 +968,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>28 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
+          <t>1 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DD</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GIH34S</t>
+          <t>GIH2DE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -995,24 +995,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
+          <t>1 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DE</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GIH35T</t>
+          <t>GIH2G4</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1027,19 +1027,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2G4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GIH37R</t>
+          <t>GIH2LT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1049,24 +1049,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 12)</t>
+          <t>2 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LT</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GIH37S</t>
+          <t>GIH2LU</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1076,24 +1076,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>19 lärandemål (maximum rekommenderat: 12)</t>
+          <t>2 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LU</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GIH38Z</t>
+          <t>GIH2LV</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1103,24 +1103,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>28 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH38Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LV</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GIH38Z</t>
+          <t>GIH2LW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1130,24 +1130,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH38Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LW</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GIH392</t>
+          <t>GIH2LX</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
+          <t>2 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH392</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LX</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GIH39E</t>
+          <t>GIH2LY</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1189,19 +1189,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>2 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LY</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GIH39E</t>
+          <t>GIH2M4</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1211,24 +1211,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
+          <t>2 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GIH39F</t>
+          <t>GIH2M5</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1248,14 +1248,14 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GIH39H</t>
+          <t>GIH2M6</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1270,19 +1270,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>2 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GIH39H</t>
+          <t>GIH2NR</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1292,24 +1292,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>26 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2NR</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GIH3AN</t>
+          <t>GIH2QL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1319,24 +1319,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12)</t>
+          <t>30 ord: - med goda rörelsekvaliteter delta i olika rörelseaktiviteter med relevans för t…</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QL</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GIH3AP</t>
+          <t>GIH2VK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1346,24 +1346,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VK</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GIH3AP</t>
+          <t>GIH2WY</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1378,19 +1378,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>28 ord: - på en grundläggande nivå diskutera och problematisera skolämnet idrott och häl…</t>
+          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WY</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GIH3AP</t>
+          <t>GIH2X3</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1405,19 +1405,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
+          <t>29 ord: - utifrån vetenskaplig grund inom området välja övningar och designa ett träning…</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2X3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GIH3AP</t>
+          <t>GIH2ZC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1427,24 +1427,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>26 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GIH3AP</t>
+          <t>GIH2ZC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1459,19 +1459,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
+          <t>26 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZC</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GIH3D4</t>
+          <t>GIH2ZD</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1481,24 +1481,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>29 ord: - utifrån vetenskaplig grund inom området välja övningar och designa ett träning…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZD</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GIH3D5</t>
+          <t>GIH2ZD</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1513,19 +1513,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>28 ord: - utifrån vetenskaplig grund inom området välja övningar och designa ett hälsoin…</t>
+          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZD</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GIH3F9</t>
+          <t>GIH2ZE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1545,14 +1545,14 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZE</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GIH3FA</t>
+          <t>GIH32Z</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1567,19 +1567,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3FA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH32Z</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GIH3FD</t>
+          <t>GIH335</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1599,14 +1599,14 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3FD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH335</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GIH3FF</t>
+          <t>GIH335</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>27 ord: - formulera en affärsplan med tillhörande budget inom området idrott och hälsa s…</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3FF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH335</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GIH3G4</t>
+          <t>GIH33K</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1648,19 +1648,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>1 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33K</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GIH3GD</t>
+          <t>GIH33P</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1680,14 +1680,14 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33P</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GIH3GG</t>
+          <t>GIH34S</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1697,24 +1697,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>28 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34S</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GIH3GH</t>
+          <t>GIH34S</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1724,24 +1724,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34S</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GIH3GJ</t>
+          <t>GIH35P</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1761,127 +1761,127 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35P</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>AMC288</t>
+          <t>GIH35T</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>38 ord: - beskriva samband mellan fysisk aktivitet och hälsa vid en vald diagnos eller s…</t>
+          <t>2 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35T</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>AMC288</t>
+          <t>GIH35V</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>27 ord: - jämföra och kritiskt diskutera olika mät- och utvärderingsmetoder för fysisk a…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35V</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>AMC288</t>
+          <t>GIH37P</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>34 ord: - utifrån vetenskaplig evidens beskriva hur fysisk träning kan utformas beroende…</t>
+          <t>23 lärandemål (maximum rekommenderat: 12)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>AMC288</t>
+          <t>GIH37Q</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>35 ord: - med stöd i vetenskaplig litteratur och egen erfarenhet reflektera kring den ro…</t>
+          <t>23 lärandemål (maximum rekommenderat: 12)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>AMC288</t>
+          <t>GIH37Q</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>31 ord: - med stöd i relevant teoribildning identifiera hinder och underlättande faktore…</t>
+          <t>28 ord: - på en grundläggande nivå diskutera och problematisera skolämnet idrott och häl…</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>AMC28N</t>
+          <t>GIH37Q</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>26 ord: - presentera och argumentera för vald design hos ett tänkt forskningsprojekt ino…</t>
+          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC28N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>AMC29F</t>
+          <t>GIH37Q</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>26 ord: - självständigt identifiera och formulera problemställning och syfte för en vete…</t>
+          <t>26 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>AMC29F</t>
+          <t>GIH37Q</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1972,78 +1972,78 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>29 ord: - genomföra en vetenskaplig undersökning med relevant design, metod och analys s…</t>
+          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>AMC29F</t>
+          <t>GIH37R</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>32 ord: - analysera och värdera resultat från den vetenskapliga undersökningen i relatio…</t>
+          <t>15 lärandemål (maximum rekommenderat: 12)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>AMC29F</t>
+          <t>GIH37S</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>28 ord: - försvara eget självständigt arbete samt kritiskt granska och värdera annat exa…</t>
+          <t>19 lärandemål (maximum rekommenderat: 12)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37S</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>AMC2BG</t>
+          <t>GIH38Z</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
+          <t>28 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH38Z</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GMC32X</t>
+          <t>GIH38Z</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2080,159 +2080,159 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>29 ord: - förskriva och informera om förbrukningsartiklar vid urindysfunktion, urinreten…</t>
+          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC32X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH38Z</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GMC37E</t>
+          <t>GIH392</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 4)</t>
+          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH392</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GMC37E</t>
+          <t>GIH39E</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>30 ord: - Namnge, beskriva och förklara anatomi och funktion under människans livscykel …</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39E</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GMC37T</t>
+          <t>GIH39E</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39E</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>MC1072</t>
+          <t>GIH39F</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>26 ord: - söka relevant information utifrån fysiologiska frågeställningar relaterade til…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1072</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39F</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GNV367</t>
+          <t>GIH39H</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>16 lärandemål (maximum rekommenderat: 12)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39H</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GNV367</t>
+          <t>GIH39H</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2242,132 +2242,132 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>33 ord: - visa grundläggande kunskap om lärande för hållbar utveckling i grundskolans år…</t>
+          <t>26 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39H</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>NV1036</t>
+          <t>GIH3AM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 12)</t>
+          <t>2 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>NV1036</t>
+          <t>GIH3AN</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>26 ord: - visa god förtrogenhet med och reflektera över kursplanerna inom SO, NO och tek…</t>
+          <t>23 lärandemål (maximum rekommenderat: 12)</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AN</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>NV1036</t>
+          <t>GIH3AP</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>32 ord: - visa insikt om hur närmiljö, förstahandsupplevelser, estetik och digital tekni…</t>
+          <t>23 lärandemål (maximum rekommenderat: 12)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>GIH3AP</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 12)</t>
+          <t>28 ord: - på en grundläggande nivå diskutera och problematisera skolämnet idrott och häl…</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>GIH3AP</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>29 ord: - uppvisa kunskaper om en tolkningsram (till exempel teori, teoretiska begrepp, …</t>
+          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>GIH3AP</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>28 ord: - välja och beskriva en relevant tolkningsram (till exempel teori, teoretiska be…</t>
+          <t>26 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>GIH3AP</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2431,51 +2431,51 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>32 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
+          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GSA2BV</t>
+          <t>GIH3CS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>26 ord: - visa förmåga att under handledning planera, strukturera och självständigt geno…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3CS</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GSA2BV</t>
+          <t>GIH3D4</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga och färdigheter att identifiera, definiera, analysera och dokumen…</t>
+          <t>29 ord: - utifrån vetenskaplig grund inom området välja övningar och designa ett träning…</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GSA2BV</t>
+          <t>GIH3D5</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2512,240 +2512,240 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>28 ord: - kritiskt reflektera över den egna förmågan och den personliga och professionel…</t>
+          <t>28 ord: - utifrån vetenskaplig grund inom området välja övningar och designa ett hälsoin…</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GSA3DM</t>
+          <t>GIH3F4</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GSA3DM</t>
+          <t>GIH3F8</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GSA3DM</t>
+          <t>GIH3F9</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F9</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GSA3DQ</t>
+          <t>GIH3FA</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 12)</t>
+          <t>2 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3FA</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GSA3DQ</t>
+          <t>GIH3FD</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för perspektiv på och metoder för socialt arbete med barn, familjer, …</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3FD</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GSA3DQ</t>
+          <t>GIH3FF</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna rörande …</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3FF</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GSA3FK</t>
+          <t>GIH3G4</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>34 ord: - utifrån ett brukarperspektiv genomföra olika typer av utredningar inom socialt…</t>
+          <t>2 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G4</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GSA3FL</t>
+          <t>GIH3G6</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>18 lärandemål (maximum rekommenderat: 12)</t>
+          <t>2 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G6</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>SA1032</t>
+          <t>GIH3G9</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2760,208 +2760,208 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>SA3008</t>
+          <t>GIH3G9</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 12)</t>
+          <t>28 ord: - formulera en affärsplan med tillhörande budget inom området idrott och hälsa s…</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>SA3008</t>
+          <t>GIH3GD</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>30 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GD</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>ASR29S</t>
+          <t>GIH3GG</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>27 ord: - analysera och värdera resultat i relation till tidigare forskning, värdera den…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GG</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>ASR29T</t>
+          <t>GIH3GH</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>26 ord: - problematisera och reflektera över kvinnans, barnets och närståendes roller oc…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GH</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>ASR29T</t>
+          <t>GIH3GJ</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GJ</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>ASR29V</t>
+          <t>GIH3JL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 12)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3JL</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>ASR29V</t>
+          <t>IH1002</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
+          <t>13 lärandemål (maximum rekommenderat: 12)</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>ASR29V</t>
+          <t>IH1002</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2971,105 +2971,105 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
+          <t>26 ord: - skapa lärandesituationer i ett urval av de behandlade rörelseaktiviteterna med…</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>ASR29W</t>
+          <t>IH1006</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1006</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>ASR2AD</t>
+          <t>IH1007</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av k…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2AD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1007</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>ASR2CE</t>
+          <t>IH1008</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1008</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GSR3BZ</t>
+          <t>IH1011</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3079,24 +3079,24 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>2 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR3BZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>SR3009</t>
+          <t>IH1011</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3106,159 +3106,159 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>26 ord: - analysera betydelsen av hälsofrämjande arbete under den reproduktiva livscykel…</t>
+          <t>27 ord: - skapa stimulerande lärandesituationer i olika pedagogiska sammanhang, som ocks…</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>SR3009</t>
+          <t>IH1012</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>29 ord: - identifiera problemområden och formulera relevanta frågeställningar som rör gr…</t>
+          <t>2 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1012</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>SR3009</t>
+          <t>IH1015</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för benigna och maligna gynekologiska förändringar, värdera hälsotill…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1015</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>SR3014</t>
+          <t>IH1023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>30 ord: - med ett professionellt förhållningssätt informera, ge stöd och trygghet i dial…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1023</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>SR3015</t>
+          <t>IH1024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 12)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1024</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>SR3015</t>
+          <t>IH1026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>35 ord: - självständigt handlägga preventivmedelsrådgivning och informera om lämpliga an…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>SR3015</t>
+          <t>IH1029</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3268,71 +3268,3500 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>26 ord: - kritiskt analysera, värdera, föreslå och följa upp vårdnadsinsatser och behand…</t>
+          <t>29 ord: - skapa lärandesituationer i de kunskapsområden som explicit nämns i kursplanern…</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1029</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>AVV2A6</t>
+          <t>IH1062</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>16 lärandemål (maximum rekommenderat: 12)</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV2A6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1062</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>IH1095</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>1 lärandemål (minimum rekommenderat: 4)</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1095</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>IH1096</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>1 lärandemål (minimum rekommenderat: 4)</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1096</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>IH1097</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>1 lärandemål (minimum rekommenderat: 4)</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1097</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>IH1098</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>1 lärandemål (minimum rekommenderat: 4)</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1098</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>IH1099</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>1 lärandemål (minimum rekommenderat: 4)</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1099</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>IH1100</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>1 lärandemål (minimum rekommenderat: 4)</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1100</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>IH1101</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>1 lärandemål (minimum rekommenderat: 4)</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1101</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>IH1102</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>1 lärandemål (minimum rekommenderat: 4)</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>IH1113</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>30 ord: - tillämpa grundläggande kunskaper inom ämnesområdet fysisk träning med specifik…</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>IH1113</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>26 ord: - praktisk genomföra och instruera övningar inriktade mot optimering av de fysis…</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>IH1114</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>IH1114</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>28 ord: - redogöra för de viktigaste mikro- och makronutrienterna och deras betydelse vi…</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>IH1114</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>36 ord: - visa förståelse för samt praktiskt tillämpa de centrala principerna för utform…</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>IH2001</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>IH2002</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>20 lärandemål (maximum rekommenderat: 12)</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>IH2002</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>26 ord: - självständigt identifiera, formulera och diskutera frågeställningar som berör …</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>IH2005</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>26 ord: - självständigt identifiera, formulera och diskutera frågeställningar som berör …</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>AMC243</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>26 ord: - självständigt söka, sammanställa och kritiskt granska evidensbaserad informati…</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC243</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>AMC288</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>38 ord: - beskriva samband mellan fysisk aktivitet och hälsa vid en vald diagnos eller s…</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>AMC288</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>27 ord: - jämföra och kritiskt diskutera olika mät- och utvärderingsmetoder för fysisk a…</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>AMC288</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>34 ord: - utifrån vetenskaplig evidens beskriva hur fysisk träning kan utformas beroende…</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>AMC288</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>35 ord: - med stöd i vetenskaplig litteratur och egen erfarenhet reflektera kring den ro…</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>AMC288</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>31 ord: - med stöd i relevant teoribildning identifiera hinder och underlättande faktore…</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>AMC28N</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>26 ord: - presentera och argumentera för vald design hos ett tänkt forskningsprojekt ino…</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC28N</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>AMC29F</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>26 ord: - självständigt identifiera och formulera problemställning och syfte för en vete…</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>AMC29F</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>29 ord: - genomföra en vetenskaplig undersökning med relevant design, metod och analys s…</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>AMC29F</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>32 ord: - analysera och värdera resultat från den vetenskapliga undersökningen i relatio…</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>AMC29F</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>28 ord: - försvara eget självständigt arbete samt kritiskt granska och värdera annat exa…</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>AMC29Y</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>AMC2BG</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>GMC32X</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>29 ord: - förskriva och informera om förbrukningsartiklar vid urindysfunktion, urinreten…</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC32X</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>GMC37E</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>1 lärandemål (minimum rekommenderat: 4)</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>GMC37E</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>30 ord: - Namnge, beskriva och förklara anatomi och funktion under människans livscykel …</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>GMC37T</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37T</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>MC1072</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>26 ord: - söka relevant information utifrån fysiologiska frågeställningar relaterade til…</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1072</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>MC1077</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>31 ord: - redogöra för hygieniska principer i vårdarbetet samt visa kännedom om de lagar…</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>MC2017</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>26 ord: -  redogöra för innehållet i de författningar som reglerar ansvarsfrågor och ans…</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>MC2017</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>26 ord: -  redogöra för hur anpassningsstörningar kan manifesteras hos barn, ungdomar oc…</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>MC2020</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>MC3027</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>GNV367</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>16 lärandemål (maximum rekommenderat: 12)</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>GNV367</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>33 ord: - visa grundläggande kunskap om lärande för hållbar utveckling i grundskolans år…</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>GNV3GV</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>28 ord: - redogöra för grundläggande kunskaper i naturvetenskap, med särskilt fokus på e…</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>GNV3GV</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>34 ord: - reflektera över och problematisera skolans roll i arbetet med lärande för håll…</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>NV1035</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>20 lärandemål (maximum rekommenderat: 12)</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>NV1036</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>14 lärandemål (maximum rekommenderat: 12)</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>NV1036</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>26 ord: - visa god förtrogenhet med och reflektera över kursplanerna inom SO, NO och tek…</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>NV1036</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>32 ord: - visa insikt om hur närmiljö, förstahandsupplevelser, estetik och digital tekni…</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>NV3001</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>27 ord: - kritiskt diskutera begreppet hållbar utveckling och dess olika dimensioner, so…</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>NV3001</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>27 ord: - reflektera över vilken roll den högre utbildningen har för hållbar utveckling,…</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>GSA24V</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>14 lärandemål (maximum rekommenderat: 12)</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>GSA24V</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>27 ord: - redogöra för perspektiv på och metoder för socialt arbete med barn, familjer, …</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>GSA24V</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>27 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna rörande …</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>GSA2AF</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>14 lärandemål (maximum rekommenderat: 12)</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>GSA2AF</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>29 ord: - uppvisa kunskaper om en tolkningsram (till exempel teori, teoretiska begrepp, …</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>GSA2AF</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>28 ord: - välja och beskriva en relevant tolkningsram (till exempel teori, teoretiska be…</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>GSA2AF</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>32 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>GSA2BV</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>26 ord: - visa förmåga att under handledning planera, strukturera och självständigt geno…</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>GSA2BV</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>28 ord: - visa förmåga och färdigheter att identifiera, definiera, analysera och dokumen…</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>GSA2BV</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>28 ord: - kritiskt reflektera över den egna förmågan och den personliga och professionel…</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>GSA2DW</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>29 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna avseende…</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>GSA2E4</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>29 ord: - visa kunskap om och förståelse för hur familje- och samhällsförhållanden påver…</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>GSA2GZ</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2GZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>GSA2NC</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>14 lärandemål (maximum rekommenderat: 12)</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>GSA32Y</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>18 lärandemål (maximum rekommenderat: 12)</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>GSA3DM</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>23 lärandemål (maximum rekommenderat: 12)</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>GSA3DM</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>GSA3DM</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>GSA3DN</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>29 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna avseende…</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>GSA3DQ</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>14 lärandemål (maximum rekommenderat: 12)</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>GSA3DQ</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>27 ord: - redogöra för perspektiv på och metoder för socialt arbete med barn, familjer, …</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>GSA3DQ</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>27 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna rörande …</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>GSA3DS</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>18 lärandemål (maximum rekommenderat: 12)</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>GSA3FK</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>34 ord: - utifrån ett brukarperspektiv genomföra olika typer av utredningar inom socialt…</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>GSA3FL</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>18 lärandemål (maximum rekommenderat: 12)</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FL</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>SA1032</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>SA1048</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>23 lärandemål (maximum rekommenderat: 12)</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>SA1048</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>SA1048</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>SA2020</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>26 lärandemål (maximum rekommenderat: 12)</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>SA2020</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>32 ord: - uppvisa kunskaper som utgör innehåll i en tolkningsram (till exempel teori, te…</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>SA2020</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>32 ord: - analysera resultat från ett vetenskapligt arbete på sådant sätt att tolkningsr…</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>SA2020</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>32 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>SA3008</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>13 lärandemål (maximum rekommenderat: 12)</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>SA3008</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>30 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>ASR24V</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>ASR24V</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>27 ord: - ur ett rättighetsperspektiv analysera och diskutera hur sociala, ekonomiska, m…</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>ASR25P</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>ASR26N</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>30 ord: - diskutera vikten av samarbete och lagarbete inom och mellan utbildningsinstitu…</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>ASR284</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>ASR285</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>13 lärandemål (maximum rekommenderat: 12)</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>ASR285</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>ASR285</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>ASR29S</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>27 ord: - analysera och värdera resultat i relation till tidigare forskning, värdera den…</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>ASR29T</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>26 ord: - problematisera och reflektera över kvinnans, barnets och närståendes roller oc…</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>ASR29T</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>ASR29U</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>26 ord: - i simulerad miljö utföra undersökningar och behandlingar vid komplicerad gravi…</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>ASR29V</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>13 lärandemål (maximum rekommenderat: 12)</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>ASR29V</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>ASR29V</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>ASR29W</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29W</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>ASR2AD</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av k…</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>ASR2CE</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>GSR38B</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>33 ord: - uppvisa kunskap, förståelse och reflekterande färdigheter om sexuell och repro…</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>GSR3BZ</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR3BZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>SR3001</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>30 ord: - värdera olika strategier för ledarskap och interventioner som har potential at…</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>SR3002</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>27 ord: - analysera och kritiskt värdera styrkor och svagheter i forskningsprocessens ol…</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>SR3009</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>26 ord: - analysera betydelsen av hälsofrämjande arbete under den reproduktiva livscykel…</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>SR3009</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>29 ord: - identifiera problemområden och formulera relevanta frågeställningar som rör gr…</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>SR3009</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>27 ord: - redogöra för benigna och maligna gynekologiska förändringar, värdera hälsotill…</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>SR3010</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>27 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av g…</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>SR3011</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>SR3012</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>13 lärandemål (maximum rekommenderat: 12)</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>SR3012</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>SR3012</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>SR3014</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>30 ord: - med ett professionellt förhållningssätt informera, ge stöd och trygghet i dial…</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>SR3015</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>14 lärandemål (maximum rekommenderat: 12)</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>SR3015</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>35 ord: - självständigt handlägga preventivmedelsrådgivning och informera om lämpliga an…</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>SR3015</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>26 ord: - kritiskt analysera, värdera, föreslå och följa upp vårdnadsinsatser och behand…</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
           <t>AVV2A6</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B226" t="inlineStr">
         <is>
           <t>VÅE</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV2A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>AVV2A6</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
         <is>
           <t>26 ord: - kritiskt reflektera över hur kvalitets- och säkerhetsledning organiseras och r…</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E227" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV2A6</t>
         </is>
       </c>
     </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>VV2002</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>29 ord: - redogöra för gällande regelverk för olika professioner inom kommunal äldreomso…</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>VV3011</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>19 lärandemål (maximum rekommenderat: 12)</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>VV3012</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>29 ord: - tillämpa adekvat vetenskaplig design och metod i datainsamling och analys samt…</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>VV3012</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>29 ord: - analysera och värdera resultat i relation till tidigare forskning samt den kli…</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>VV3017</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>29 ord: - tillämpa adekvat vetenskaplig design och metod i datainsamling och analys samt…</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>VV3017</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>29 ord: - analysera och värdera resultat i relation till tidigare forskning samt den kli…</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>VV3017</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>26 ord: - göra relevanta bedömningar på mikro-, meso- och makronivå med hänsyn till samh…</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E107"/>
+  <autoFilter ref="A1:E234"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -3546,6 +6975,260 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A175" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E175" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A176" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A179" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A180" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A181" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A182" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A183" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A184" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A185" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A186" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A187" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A188" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A195" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A196" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A197" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A198" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A201" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A202" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A203" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A204" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A205" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A206" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A207" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A208" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A209" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A210" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A211" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A212" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E212" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A213" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E213" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A214" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E214" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A215" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E215" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A216" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E216" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A217" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E217" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A218" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E218" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A219" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A220" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A221" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A222" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A223" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A224" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A225" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A226" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A227" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A228" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E228" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A229" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A230" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E230" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A231" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E231" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A232" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E232" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A233" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E233" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A234" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E234" r:id="rId466"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Omfång på lärandemål.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$234</definedName>

--- a/vault-dalarna-university/02 IHV/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Omfång på lärandemål.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$234</definedName>

--- a/vault-dalarna-university/02 IHV/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Omfång på lärandemål.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$234</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$224</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E234"/>
+  <dimension ref="A1:E224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 2 hp)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 2 hp)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -904,7 +904,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GIH2DB</t>
+          <t>GIH2DD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -919,19 +919,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>1 lärandemål (minimum rekommenderat: 3 för 3 hp)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DD</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GIH2DC</t>
+          <t>GIH2DE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -946,19 +946,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>1 lärandemål (minimum rekommenderat: 3 för 3 hp)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DE</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GIH2DD</t>
+          <t>GIH2G4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -973,19 +973,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 4)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2G4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GIH2DE</t>
+          <t>GIH2LT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1000,19 +1000,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 4)</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 2.5 hp)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LT</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GIH2G4</t>
+          <t>GIH2LU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1027,19 +1027,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 2.5 hp)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2G4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LU</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GIH2LT</t>
+          <t>GIH2LX</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1054,19 +1054,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 5 hp)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LX</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GIH2LU</t>
+          <t>GIH2LY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1081,19 +1081,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 5 hp)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LY</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GIH2LV</t>
+          <t>GIH2M4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1108,19 +1108,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 5 hp)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GIH2LW</t>
+          <t>GIH2M6</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1135,19 +1135,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 2.5 hp)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GIH2LX</t>
+          <t>GIH2QL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>30 ord: - med goda rörelsekvaliteter delta i olika rörelseaktiviteter med relevans för t…</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QL</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GIH2LY</t>
+          <t>GIH2WT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1184,24 +1184,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WT</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GIH2M4</t>
+          <t>GIH2WY</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1211,24 +1211,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WY</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GIH2M5</t>
+          <t>GIH2X3</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1238,24 +1238,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>29 ord: - utifrån vetenskaplig grund inom området välja övningar och designa ett träning…</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2X3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GIH2M6</t>
+          <t>GIH2ZC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1265,24 +1265,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>26 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZC</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GIH2NR</t>
+          <t>GIH2ZD</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1292,24 +1292,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2NR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZD</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GIH2QL</t>
+          <t>GIH335</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>30 ord: - med goda rörelsekvaliteter delta i olika rörelseaktiviteter med relevans för t…</t>
+          <t>27 ord: - formulera en affärsplan med tillhörande budget inom området idrott och hälsa s…</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH335</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GIH2VK</t>
+          <t>GIH33K</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1351,19 +1351,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>1 lärandemål (minimum rekommenderat: 3 för 3 hp)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33K</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GIH2WY</t>
+          <t>GIH34S</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1378,19 +1378,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
+          <t>28 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34S</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GIH2X3</t>
+          <t>GIH34S</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1405,19 +1405,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>29 ord: - utifrån vetenskaplig grund inom området välja övningar och designa ett träning…</t>
+          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2X3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34S</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZC</t>
+          <t>GIH35T</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1432,19 +1432,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35T</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZC</t>
+          <t>GIH37P</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1454,24 +1454,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>26 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
+          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZD</t>
+          <t>GIH37Q</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1481,24 +1481,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZD</t>
+          <t>GIH37Q</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1513,19 +1513,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
+          <t>28 ord: - på en grundläggande nivå diskutera och problematisera skolämnet idrott och häl…</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZE</t>
+          <t>GIH37Q</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1535,24 +1535,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GIH32Z</t>
+          <t>GIH37Q</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1562,24 +1562,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>26 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH32Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GIH335</t>
+          <t>GIH37Q</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1589,24 +1589,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH335</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GIH335</t>
+          <t>GIH37R</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>27 ord: - formulera en affärsplan med tillhörande budget inom området idrott och hälsa s…</t>
+          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH335</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GIH33K</t>
+          <t>GIH37S</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 4)</t>
+          <t>19 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37S</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GIH33P</t>
+          <t>GIH38Z</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1670,24 +1670,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>28 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH38Z</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GIH34S</t>
+          <t>GIH38Z</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1702,19 +1702,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>28 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
+          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH38Z</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GIH34S</t>
+          <t>GIH392</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1734,14 +1734,14 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH392</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GIH35P</t>
+          <t>GIH39E</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1751,24 +1751,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39E</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GIH35T</t>
+          <t>GIH39H</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1778,24 +1778,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>26 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39H</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GIH35V</t>
+          <t>GIH3AM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1810,19 +1810,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 2 hp)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GIH37P</t>
+          <t>GIH3AN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12)</t>
+          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AN</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GIH37Q</t>
+          <t>GIH3AP</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1864,19 +1864,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12)</t>
+          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GIH37Q</t>
+          <t>GIH3AP</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1896,14 +1896,14 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GIH37Q</t>
+          <t>GIH3AP</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1923,14 +1923,14 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GIH37Q</t>
+          <t>GIH3AP</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1950,14 +1950,14 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GIH37Q</t>
+          <t>GIH3AP</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1977,14 +1977,14 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GIH37R</t>
+          <t>GIH3D4</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1994,24 +1994,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 12)</t>
+          <t>29 ord: - utifrån vetenskaplig grund inom området välja övningar och designa ett träning…</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GIH37S</t>
+          <t>GIH3D5</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2021,24 +2021,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>19 lärandemål (maximum rekommenderat: 12)</t>
+          <t>28 ord: - utifrån vetenskaplig grund inom området välja övningar och designa ett hälsoin…</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GIH38Z</t>
+          <t>GIH3FA</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2048,24 +2048,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>28 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH38Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3FA</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GIH38Z</t>
+          <t>GIH3G4</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2075,24 +2075,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH38Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GIH392</t>
+          <t>GIH3G6</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2102,24 +2102,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH392</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GIH39E</t>
+          <t>GIH3G9</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2129,24 +2129,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>28 ord: - formulera en affärsplan med tillhörande budget inom området idrott och hälsa s…</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GIH39E</t>
+          <t>IH1002</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2156,24 +2156,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
+          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GIH39F</t>
+          <t>IH1002</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2183,24 +2183,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>26 ord: - skapa lärandesituationer i ett urval av de behandlade rörelseaktiviteterna med…</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GIH39H</t>
+          <t>IH1011</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2215,19 +2215,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GIH39H</t>
+          <t>IH1011</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2242,19 +2242,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>26 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
+          <t>27 ord: - skapa stimulerande lärandesituationer i olika pedagogiska sammanhang, som ocks…</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GIH3AM</t>
+          <t>IH1012</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2269,19 +2269,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1012</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GIH3AN</t>
+          <t>IH1029</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2291,24 +2291,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12)</t>
+          <t>29 ord: - skapa lärandesituationer i de kunskapsområden som explicit nämns i kursplanern…</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1029</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GIH3AP</t>
+          <t>IH1062</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2323,19 +2323,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12)</t>
+          <t>16 lärandemål (maximum rekommenderat: 12 för 20 hp)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1062</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GIH3AP</t>
+          <t>IH1095</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2345,24 +2345,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>28 ord: - på en grundläggande nivå diskutera och problematisera skolämnet idrott och häl…</t>
+          <t>1 lärandemål (minimum rekommenderat: 3 för 1.5 hp)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1095</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GIH3AP</t>
+          <t>IH1096</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2372,24 +2372,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
+          <t>1 lärandemål (minimum rekommenderat: 3 för 1.5 hp)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1096</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GIH3AP</t>
+          <t>IH1097</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2399,24 +2399,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>26 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
+          <t>1 lärandemål (minimum rekommenderat: 3 för 1.5 hp)</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1097</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GIH3AP</t>
+          <t>IH1098</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2426,24 +2426,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
+          <t>1 lärandemål (minimum rekommenderat: 3 för 1.5 hp)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1098</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GIH3CS</t>
+          <t>IH1099</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2458,19 +2458,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>1 lärandemål (minimum rekommenderat: 3 för 1.5 hp)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3CS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1099</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GIH3D4</t>
+          <t>IH1100</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2480,24 +2480,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>29 ord: - utifrån vetenskaplig grund inom området välja övningar och designa ett träning…</t>
+          <t>1 lärandemål (minimum rekommenderat: 3 för 1.5 hp)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1100</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GIH3D5</t>
+          <t>IH1101</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2507,24 +2507,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>28 ord: - utifrån vetenskaplig grund inom området välja övningar och designa ett hälsoin…</t>
+          <t>1 lärandemål (minimum rekommenderat: 3 för 1.5 hp)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1101</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GIH3F4</t>
+          <t>IH1102</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2539,19 +2539,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>1 lärandemål (minimum rekommenderat: 3 för 1.5 hp)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1102</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GIH3F8</t>
+          <t>IH1113</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>30 ord: - tillämpa grundläggande kunskaper inom ämnesområdet fysisk träning med specifik…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GIH3F9</t>
+          <t>IH1113</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2588,24 +2588,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>26 ord: - praktisk genomföra och instruera övningar inriktade mot optimering av de fysis…</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GIH3FA</t>
+          <t>IH1114</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2615,24 +2615,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>28 ord: - redogöra för de viktigaste mikro- och makronutrienterna och deras betydelse vi…</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3FA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GIH3FD</t>
+          <t>IH1114</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2642,24 +2642,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>36 ord: - visa förståelse för samt praktiskt tillämpa de centrala principerna för utform…</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3FD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GIH3FF</t>
+          <t>IH2001</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2674,19 +2674,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>3 lärandemål (minimum rekommenderat: 5 för 30 hp)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3FF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GIH3G4</t>
+          <t>IH2002</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2696,24 +2696,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GIH3G6</t>
+          <t>IH2002</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2723,24 +2723,24 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>26 ord: - självständigt identifiera, formulera och diskutera frågeställningar som berör …</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GIH3G9</t>
+          <t>IH2005</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2750,29 +2750,29 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>26 ord: - självständigt identifiera, formulera och diskutera frågeställningar som berör …</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2005</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GIH3G9</t>
+          <t>AMC243</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2782,186 +2782,186 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>28 ord: - formulera en affärsplan med tillhörande budget inom området idrott och hälsa s…</t>
+          <t>26 ord: - självständigt söka, sammanställa och kritiskt granska evidensbaserad informati…</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC243</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GIH3GD</t>
+          <t>AMC288</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>38 ord: - beskriva samband mellan fysisk aktivitet och hälsa vid en vald diagnos eller s…</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GIH3GG</t>
+          <t>AMC288</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>27 ord: - jämföra och kritiskt diskutera olika mät- och utvärderingsmetoder för fysisk a…</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GIH3GH</t>
+          <t>AMC288</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>34 ord: - utifrån vetenskaplig evidens beskriva hur fysisk träning kan utformas beroende…</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GIH3GJ</t>
+          <t>AMC288</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>35 ord: - med stöd i vetenskaplig litteratur och egen erfarenhet reflektera kring den ro…</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GIH3JL</t>
+          <t>AMC288</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>31 ord: - med stöd i relevant teoribildning identifiera hinder och underlättande faktore…</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3JL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>IH1002</t>
+          <t>AMC28N</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 12)</t>
+          <t>26 ord: - presentera och argumentera för vald design hos ett tänkt forskningsprojekt ino…</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC28N</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>IH1002</t>
+          <t>AMC29F</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2971,213 +2971,213 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>26 ord: - skapa lärandesituationer i ett urval av de behandlade rörelseaktiviteterna med…</t>
+          <t>26 ord: - självständigt identifiera och formulera problemställning och syfte för en vete…</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>IH1006</t>
+          <t>AMC29F</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>29 ord: - genomföra en vetenskaplig undersökning med relevant design, metod och analys s…</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>IH1007</t>
+          <t>AMC29F</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>32 ord: - analysera och värdera resultat från den vetenskapliga undersökningen i relatio…</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>IH1008</t>
+          <t>AMC29F</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>28 ord: - försvara eget självständigt arbete samt kritiskt granska och värdera annat exa…</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>IH1011</t>
+          <t>AMC29Y</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>IH1011</t>
+          <t>AMC2A7</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>27 ord: - skapa stimulerande lärandesituationer i olika pedagogiska sammanhang, som ocks…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>IH1012</t>
+          <t>AMC2BG</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>IH1015</t>
+          <t>GMC32X</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>29 ord: - förskriva och informera om förbrukningsartiklar vid urindysfunktion, urinreten…</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC32X</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>IH1023</t>
+          <t>GMC37E</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3187,51 +3187,51 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>1 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>IH1024</t>
+          <t>GMC37E</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>30 ord: - Namnge, beskriva och förklara anatomi och funktion under människans livscykel …</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>IH1026</t>
+          <t>GMC37T</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 6 hp)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37T</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>IH1029</t>
+          <t>MC1072</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3268,348 +3268,348 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>29 ord: - skapa lärandesituationer i de kunskapsområden som explicit nämns i kursplanern…</t>
+          <t>26 ord: - söka relevant information utifrån fysiologiska frågeställningar relaterade til…</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1072</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>IH1062</t>
+          <t>MC1077</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>16 lärandemål (maximum rekommenderat: 12)</t>
+          <t>31 ord: - redogöra för hygieniska principer i vårdarbetet samt visa kännedom om de lagar…</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1062</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>IH1095</t>
+          <t>MC2017</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 4)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1095</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>IH1096</t>
+          <t>MC2017</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 4)</t>
+          <t>26 ord: -  redogöra för innehållet i de författningar som reglerar ansvarsfrågor och ans…</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1096</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>IH1097</t>
+          <t>MC2017</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 4)</t>
+          <t>26 ord: -  redogöra för hur anpassningsstörningar kan manifesteras hos barn, ungdomar oc…</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1097</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>IH1098</t>
+          <t>MC3027</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 4)</t>
+          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1098</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>IH1099</t>
+          <t>GNV367</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 4)</t>
+          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1099</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>IH1100</t>
+          <t>GNV367</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 4)</t>
+          <t>33 ord: - visa grundläggande kunskap om lärande för hållbar utveckling i grundskolans år…</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1100</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>IH1101</t>
+          <t>GNV3GV</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 4)</t>
+          <t>28 ord: - redogöra för grundläggande kunskaper i naturvetenskap, med särskilt fokus på e…</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1101</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>IH1102</t>
+          <t>GNV3GV</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 4)</t>
+          <t>34 ord: - reflektera över och problematisera skolans roll i arbetet med lärande för håll…</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1102</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>IH1113</t>
+          <t>NV1035</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>30 ord: - tillämpa grundläggande kunskaper inom ämnesområdet fysisk träning med specifik…</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>IH1113</t>
+          <t>NV1036</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>26 ord: - praktisk genomföra och instruera övningar inriktade mot optimering av de fysis…</t>
+          <t>14 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>IH1114</t>
+          <t>NV1036</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>26 ord: - visa god förtrogenhet med och reflektera över kursplanerna inom SO, NO och tek…</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>IH1114</t>
+          <t>NV1036</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3619,24 +3619,24 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>28 ord: - redogöra för de viktigaste mikro- och makronutrienterna och deras betydelse vi…</t>
+          <t>32 ord: - visa insikt om hur närmiljö, förstahandsupplevelser, estetik och digital tekni…</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>IH1114</t>
+          <t>NV3001</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3646,51 +3646,51 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>36 ord: - visa förståelse för samt praktiskt tillämpa de centrala principerna för utform…</t>
+          <t>27 ord: - kritiskt diskutera begreppet hållbar utveckling och dess olika dimensioner, so…</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>IH2001</t>
+          <t>NV3001</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>27 ord: - reflektera över vilken roll den högre utbildningen har för hållbar utveckling,…</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>IH2002</t>
+          <t>ASA24K</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3700,213 +3700,213 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24K</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>IH2002</t>
+          <t>ASA24L</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>26 ord: - självständigt identifiera, formulera och diskutera frågeställningar som berör …</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24L</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>IH2005</t>
+          <t>ASA266</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>26 ord: - självständigt identifiera, formulera och diskutera frågeställningar som berör …</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA266</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>AMC243</t>
+          <t>ASA26U</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>26 ord: - självständigt söka, sammanställa och kritiskt granska evidensbaserad informati…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC243</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA26U</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>AMC288</t>
+          <t>ASA27E</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>38 ord: - beskriva samband mellan fysisk aktivitet och hälsa vid en vald diagnos eller s…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 5 hp)</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>AMC288</t>
+          <t>ASA293</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>27 ord: - jämföra och kritiskt diskutera olika mät- och utvärderingsmetoder för fysisk a…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA293</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>AMC288</t>
+          <t>GSA24U</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>34 ord: - utifrån vetenskaplig evidens beskriva hur fysisk träning kan utformas beroende…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>AMC288</t>
+          <t>GSA24V</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>35 ord: - med stöd i vetenskaplig litteratur och egen erfarenhet reflektera kring den ro…</t>
+          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>AMC288</t>
+          <t>GSA24V</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3916,24 +3916,24 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>31 ord: - med stöd i relevant teoribildning identifiera hinder och underlättande faktore…</t>
+          <t>27 ord: - redogöra för perspektiv på och metoder för socialt arbete med barn, familjer, …</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>AMC28N</t>
+          <t>GSA24V</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3943,78 +3943,78 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>26 ord: - presentera och argumentera för vald design hos ett tänkt forskningsprojekt ino…</t>
+          <t>27 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna rörande …</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC28N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>AMC29F</t>
+          <t>GSA27Y</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>26 ord: - självständigt identifiera och formulera problemställning och syfte för en vete…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA27Y</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>AMC29F</t>
+          <t>GSA2AF</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>29 ord: - genomföra en vetenskaplig undersökning med relevant design, metod och analys s…</t>
+          <t>14 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>AMC29F</t>
+          <t>GSA2AF</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4024,24 +4024,24 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>32 ord: - analysera och värdera resultat från den vetenskapliga undersökningen i relatio…</t>
+          <t>29 ord: - uppvisa kunskaper om en tolkningsram (till exempel teori, teoretiska begrepp, …</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>AMC29F</t>
+          <t>GSA2AF</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4051,24 +4051,24 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>28 ord: - försvara eget självständigt arbete samt kritiskt granska och värdera annat exa…</t>
+          <t>28 ord: - välja och beskriva en relevant tolkningsram (till exempel teori, teoretiska be…</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>AMC29Y</t>
+          <t>GSA2AF</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4078,51 +4078,51 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
+          <t>32 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>AMC2BG</t>
+          <t>GSA2BV</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
+          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GMC32X</t>
+          <t>GSA2BV</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4132,51 +4132,51 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>29 ord: - förskriva och informera om förbrukningsartiklar vid urindysfunktion, urinreten…</t>
+          <t>26 ord: - visa förmåga att under handledning planera, strukturera och självständigt geno…</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC32X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GMC37E</t>
+          <t>GSA2BV</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 4)</t>
+          <t>28 ord: - visa förmåga och färdigheter att identifiera, definiera, analysera och dokumen…</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GMC37E</t>
+          <t>GSA2BV</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4186,51 +4186,51 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>30 ord: - Namnge, beskriva och förklara anatomi och funktion under människans livscykel …</t>
+          <t>28 ord: - kritiskt reflektera över den egna förmågan och den personliga och professionel…</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GMC37T</t>
+          <t>GSA2DW</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>MC1072</t>
+          <t>GSA2DW</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4240,78 +4240,78 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>26 ord: - söka relevant information utifrån fysiologiska frågeställningar relaterade til…</t>
+          <t>29 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna avseende…</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1072</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>MC1077</t>
+          <t>GSA2E3</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>31 ord: - redogöra för hygieniska principer i vårdarbetet samt visa kännedom om de lagar…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E3</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>MC2017</t>
+          <t>GSA2E4</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>26 ord: -  redogöra för innehållet i de författningar som reglerar ansvarsfrågor och ans…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>MC2017</t>
+          <t>GSA2E4</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4321,78 +4321,78 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>26 ord: -  redogöra för hur anpassningsstörningar kan manifesteras hos barn, ungdomar oc…</t>
+          <t>29 ord: - visa kunskap om och förståelse för hur familje- och samhällsförhållanden påver…</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>MC2020</t>
+          <t>GSA2E5</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>MC3027</t>
+          <t>GSA2NA</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NA</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GNV367</t>
+          <t>GSA2NC</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4402,105 +4402,105 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>16 lärandemål (maximum rekommenderat: 12)</t>
+          <t>14 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>GNV367</t>
+          <t>GSA2RE</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>33 ord: - visa grundläggande kunskap om lärande för hållbar utveckling i grundskolans år…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2RE</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GNV3GV</t>
+          <t>GSA2SD</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>28 ord: - redogöra för grundläggande kunskaper i naturvetenskap, med särskilt fokus på e…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GNV3GV</t>
+          <t>GSA2SE</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>34 ord: - reflektera över och problematisera skolans roll i arbetet med lärande för håll…</t>
+          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>NV1035</t>
+          <t>GSA32Y</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4510,24 +4510,24 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12)</t>
+          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>NV1036</t>
+          <t>GSA352</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4537,51 +4537,51 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 12)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA352</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>NV1036</t>
+          <t>GSA3DM</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>26 ord: - visa god förtrogenhet med och reflektera över kursplanerna inom SO, NO och tek…</t>
+          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>NV1036</t>
+          <t>GSA3DM</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>32 ord: - visa insikt om hur närmiljö, förstahandsupplevelser, estetik och digital tekni…</t>
+          <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>NV3001</t>
+          <t>GSA3DM</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4618,46 +4618,46 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>27 ord: - kritiskt diskutera begreppet hållbar utveckling och dess olika dimensioner, so…</t>
+          <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>NV3001</t>
+          <t>GSA3DN</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>27 ord: - reflektera över vilken roll den högre utbildningen har för hållbar utveckling,…</t>
+          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>GSA24V</t>
+          <t>GSA3DN</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4667,24 +4667,24 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 12)</t>
+          <t>29 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna avseende…</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>GSA24V</t>
+          <t>GSA3DP</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4694,24 +4694,24 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för perspektiv på och metoder för socialt arbete med barn, familjer, …</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DP</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>GSA24V</t>
+          <t>GSA3DQ</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4721,24 +4721,24 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna rörande …</t>
+          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>GSA3DQ</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4748,24 +4748,24 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 12)</t>
+          <t>27 ord: - redogöra för perspektiv på och metoder för socialt arbete med barn, familjer, …</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>GSA3DQ</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4780,19 +4780,19 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>29 ord: - uppvisa kunskaper om en tolkningsram (till exempel teori, teoretiska begrepp, …</t>
+          <t>27 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna rörande …</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>GSA3DR</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4802,24 +4802,24 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>28 ord: - välja och beskriva en relevant tolkningsram (till exempel teori, teoretiska be…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DR</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>GSA3DS</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4829,24 +4829,24 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>32 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
+          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>GSA2BV</t>
+          <t>GSA3FK</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4856,24 +4856,24 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>26 ord: - visa förmåga att under handledning planera, strukturera och självständigt geno…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>GSA2BV</t>
+          <t>GSA3FK</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4888,19 +4888,19 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga och färdigheter att identifiera, definiera, analysera och dokumen…</t>
+          <t>34 ord: - utifrån ett brukarperspektiv genomföra olika typer av utredningar inom socialt…</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>GSA2BV</t>
+          <t>GSA3FL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4910,24 +4910,24 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>28 ord: - kritiskt reflektera över den egna förmågan och den personliga och professionel…</t>
+          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FL</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>GSA2DW</t>
+          <t>GSA3HA</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4937,24 +4937,24 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna avseende…</t>
+          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3HA</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>GSA2E4</t>
+          <t>SA1045</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4964,24 +4964,24 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskap om och förståelse för hur familje- och samhällsförhållanden påver…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1045</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>GSA2GZ</t>
+          <t>SA1048</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4991,24 +4991,24 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2GZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>GSA2NC</t>
+          <t>SA1048</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5018,24 +5018,24 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 12)</t>
+          <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>GSA32Y</t>
+          <t>SA1048</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5045,24 +5045,24 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>18 lärandemål (maximum rekommenderat: 12)</t>
+          <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>GSA3DM</t>
+          <t>SA2020</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5077,19 +5077,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12)</t>
+          <t>26 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>GSA3DM</t>
+          <t>SA2020</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5104,19 +5104,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
+          <t>32 ord: - uppvisa kunskaper som utgör innehåll i en tolkningsram (till exempel teori, te…</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>GSA3DM</t>
+          <t>SA2020</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5131,19 +5131,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
+          <t>32 ord: - analysera resultat från ett vetenskapligt arbete på sådant sätt att tolkningsr…</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>GSA3DN</t>
+          <t>SA2020</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5158,19 +5158,19 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna avseende…</t>
+          <t>32 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>GSA3DQ</t>
+          <t>SA3008</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5185,19 +5185,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 12)</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>GSA3DQ</t>
+          <t>SA3008</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5212,24 +5212,24 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för perspektiv på och metoder för socialt arbete med barn, familjer, …</t>
+          <t>30 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>GSA3DQ</t>
+          <t>ASR24V</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5239,51 +5239,51 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna rörande …</t>
+          <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>GSA3DS</t>
+          <t>ASR24V</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>18 lärandemål (maximum rekommenderat: 12)</t>
+          <t>27 ord: - ur ett rättighetsperspektiv analysera och diskutera hur sociala, ekonomiska, m…</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>GSA3FK</t>
+          <t>ASR25P</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5293,24 +5293,24 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>34 ord: - utifrån ett brukarperspektiv genomföra olika typer av utredningar inom socialt…</t>
+          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>GSA3FL</t>
+          <t>ASR26N</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5320,105 +5320,105 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>18 lärandemål (maximum rekommenderat: 12)</t>
+          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>SA1032</t>
+          <t>ASR26N</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>30 ord: - diskutera vikten av samarbete och lagarbete inom och mellan utbildningsinstitu…</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>SA1048</t>
+          <t>ASR284</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12)</t>
+          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>SA1048</t>
+          <t>ASR285</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>SA1048</t>
+          <t>ASR285</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5428,51 +5428,51 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
+          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>SA2020</t>
+          <t>ASR285</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>26 lärandemål (maximum rekommenderat: 12)</t>
+          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>SA2020</t>
+          <t>ASR29S</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5482,24 +5482,24 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>32 ord: - uppvisa kunskaper som utgör innehåll i en tolkningsram (till exempel teori, te…</t>
+          <t>27 ord: - analysera och värdera resultat i relation till tidigare forskning, värdera den…</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>SA2020</t>
+          <t>ASR29T</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5509,24 +5509,24 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>32 ord: - analysera resultat från ett vetenskapligt arbete på sådant sätt att tolkningsr…</t>
+          <t>26 ord: - problematisera och reflektera över kvinnans, barnets och närståendes roller oc…</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>SA2020</t>
+          <t>ASR29T</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5536,73 +5536,73 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>32 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
+          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>SA3008</t>
+          <t>ASR29U</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 12)</t>
+          <t>26 ord: - i simulerad miljö utföra undersökningar och behandlingar vid komplicerad gravi…</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>SA3008</t>
+          <t>ASR29V</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>30 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>ASR24V</t>
+          <t>ASR29V</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5617,19 +5617,19 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
+          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>ASR24V</t>
+          <t>ASR29V</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5644,19 +5644,19 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>27 ord: - ur ett rättighetsperspektiv analysera och diskutera hur sociala, ekonomiska, m…</t>
+          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>ASR25P</t>
+          <t>ASR29W</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5671,19 +5671,19 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
+          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29W</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>ASR26N</t>
+          <t>ASR2AD</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5698,19 +5698,19 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>30 ord: - diskutera vikten av samarbete och lagarbete inom och mellan utbildningsinstitu…</t>
+          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av k…</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2AD</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>ASR284</t>
+          <t>ASR2BM</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5720,24 +5720,24 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2BM</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>ASR285</t>
+          <t>ASR2CE</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5747,24 +5747,24 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 12)</t>
+          <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CE</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>ASR285</t>
+          <t>GSR38B</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5779,19 +5779,19 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
+          <t>33 ord: - uppvisa kunskap, förståelse och reflekterande färdigheter om sexuell och repro…</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>ASR285</t>
+          <t>SR3001</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5806,19 +5806,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
+          <t>30 ord: - värdera olika strategier för ledarskap och interventioner som har potential at…</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>ASR29S</t>
+          <t>SR3002</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5833,19 +5833,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>27 ord: - analysera och värdera resultat i relation till tidigare forskning, värdera den…</t>
+          <t>27 ord: - analysera och kritiskt värdera styrkor och svagheter i forskningsprocessens ol…</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>ASR29T</t>
+          <t>SR3007</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5855,24 +5855,24 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>26 ord: - problematisera och reflektera över kvinnans, barnets och närståendes roller oc…</t>
+          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>ASR29T</t>
+          <t>SR3008</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5882,24 +5882,24 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>ASR29U</t>
+          <t>SR3009</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5914,19 +5914,19 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>26 ord: - i simulerad miljö utföra undersökningar och behandlingar vid komplicerad gravi…</t>
+          <t>26 ord: - analysera betydelsen av hälsofrämjande arbete under den reproduktiva livscykel…</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>ASR29V</t>
+          <t>SR3009</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5936,24 +5936,24 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 12)</t>
+          <t>29 ord: - identifiera problemområden och formulera relevanta frågeställningar som rör gr…</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>ASR29V</t>
+          <t>SR3009</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5968,19 +5968,19 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
+          <t>27 ord: - redogöra för benigna och maligna gynekologiska förändringar, värdera hälsotill…</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>ASR29V</t>
+          <t>SR3010</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5995,19 +5995,19 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
+          <t>27 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av g…</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>ASR29W</t>
+          <t>SR3011</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6027,14 +6027,14 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>ASR2AD</t>
+          <t>SR3012</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6044,24 +6044,24 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av k…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2AD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>ASR2CE</t>
+          <t>SR3012</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6076,19 +6076,19 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
+          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>GSR38B</t>
+          <t>SR3012</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6103,19 +6103,19 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>33 ord: - uppvisa kunskap, förståelse och reflekterande färdigheter om sexuell och repro…</t>
+          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>GSR3BZ</t>
+          <t>SR3014</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6125,24 +6125,24 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>11 lärandemål (maximum rekommenderat: 10 för 13.5 hp)</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR3BZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>SR3001</t>
+          <t>SR3014</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6157,19 +6157,19 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>30 ord: - värdera olika strategier för ledarskap och interventioner som har potential at…</t>
+          <t>30 ord: - med ett professionellt förhållningssätt informera, ge stöd och trygghet i dial…</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>SR3002</t>
+          <t>SR3015</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6179,24 +6179,24 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>27 ord: - analysera och kritiskt värdera styrkor och svagheter i forskningsprocessens ol…</t>
+          <t>14 lärandemål (maximum rekommenderat: 10 för 13.5 hp)</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>SR3009</t>
+          <t>SR3015</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6211,19 +6211,19 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>26 ord: - analysera betydelsen av hälsofrämjande arbete under den reproduktiva livscykel…</t>
+          <t>35 ord: - självständigt handlägga preventivmedelsrådgivning och informera om lämpliga an…</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>SR3009</t>
+          <t>SR3015</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6238,24 +6238,24 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>29 ord: - identifiera problemområden och formulera relevanta frågeställningar som rör gr…</t>
+          <t>26 ord: - kritiskt analysera, värdera, föreslå och följa upp vårdnadsinsatser och behand…</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>SR3009</t>
+          <t>AVV2A6</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6265,24 +6265,24 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för benigna och maligna gynekologiska förändringar, värdera hälsotill…</t>
+          <t>26 ord: - kritiskt reflektera över hur kvalitets- och säkerhetsledning organiseras och r…</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV2A6</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>SR3010</t>
+          <t>VV2002</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6292,51 +6292,51 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>27 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av g…</t>
+          <t>29 ord: - redogöra för gällande regelverk för olika professioner inom kommunal äldreomso…</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>SR3011</t>
+          <t>VV3006</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>SR3012</t>
+          <t>VV3011</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6346,24 +6346,24 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 12)</t>
+          <t>19 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>SR3012</t>
+          <t>VV3012</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -6373,24 +6373,24 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
+          <t>29 ord: - tillämpa adekvat vetenskaplig design och metod i datainsamling och analys samt…</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>SR3012</t>
+          <t>VV3012</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -6400,24 +6400,24 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
+          <t>29 ord: - analysera och värdera resultat i relation till tidigare forskning samt den kli…</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>SR3014</t>
+          <t>VV3017</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -6427,51 +6427,51 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>30 ord: - med ett professionellt förhållningssätt informera, ge stöd och trygghet i dial…</t>
+          <t>29 ord: - tillämpa adekvat vetenskaplig design och metod i datainsamling och analys samt…</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>SR3015</t>
+          <t>VV3017</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 12)</t>
+          <t>29 ord: - analysera och värdera resultat i relation till tidigare forskning samt den kli…</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>SR3015</t>
+          <t>VV3017</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -6481,287 +6481,17 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>35 ord: - självständigt handlägga preventivmedelsrådgivning och informera om lämpliga an…</t>
+          <t>26 ord: - göra relevanta bedömningar på mikro-, meso- och makronivå med hänsyn till samh…</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
-        <is>
-          <t>SR3015</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>26 ord: - kritiskt analysera, värdera, föreslå och följa upp vårdnadsinsatser och behand…</t>
-        </is>
-      </c>
-      <c r="E225" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
-        <is>
-          <t>AVV2A6</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>För få mål</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
-        </is>
-      </c>
-      <c r="E226" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV2A6</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
-        <is>
-          <t>AVV2A6</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>26 ord: - kritiskt reflektera över hur kvalitets- och säkerhetsledning organiseras och r…</t>
-        </is>
-      </c>
-      <c r="E227" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV2A6</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="2" t="inlineStr">
-        <is>
-          <t>VV2002</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>29 ord: - redogöra för gällande regelverk för olika professioner inom kommunal äldreomso…</t>
-        </is>
-      </c>
-      <c r="E228" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="2" t="inlineStr">
-        <is>
-          <t>VV3011</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>19 lärandemål (maximum rekommenderat: 12)</t>
-        </is>
-      </c>
-      <c r="E229" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="2" t="inlineStr">
-        <is>
-          <t>VV3012</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>29 ord: - tillämpa adekvat vetenskaplig design och metod i datainsamling och analys samt…</t>
-        </is>
-      </c>
-      <c r="E230" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="2" t="inlineStr">
-        <is>
-          <t>VV3012</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>29 ord: - analysera och värdera resultat i relation till tidigare forskning samt den kli…</t>
-        </is>
-      </c>
-      <c r="E231" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="2" t="inlineStr">
-        <is>
-          <t>VV3017</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>29 ord: - tillämpa adekvat vetenskaplig design och metod i datainsamling och analys samt…</t>
-        </is>
-      </c>
-      <c r="E232" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="2" t="inlineStr">
-        <is>
-          <t>VV3017</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>29 ord: - analysera och värdera resultat i relation till tidigare forskning samt den kli…</t>
-        </is>
-      </c>
-      <c r="E233" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="2" t="inlineStr">
-        <is>
-          <t>VV3017</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>26 ord: - göra relevanta bedömningar på mikro-, meso- och makronivå med hänsyn till samh…</t>
-        </is>
-      </c>
-      <c r="E234" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E234"/>
+  <autoFilter ref="A1:E224"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -7209,26 +6939,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId444"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A224" r:id="rId445"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A225" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A226" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A227" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A228" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E228" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A229" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A230" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E230" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A231" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E231" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A232" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E232" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A233" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E233" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A234" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E234" r:id="rId466"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Omfång på lärandemål.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$224</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$225</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E224"/>
+  <dimension ref="A1:E225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4495,7 +4495,7 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GSA32Y</t>
+          <t>GSA2XN</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4510,19 +4510,19 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2XN</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GSA352</t>
+          <t>GSA32Y</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4537,19 +4537,19 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA352</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>GSA3DM</t>
+          <t>GSA352</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA352</t>
         </is>
       </c>
     </row>
@@ -4586,12 +4586,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
+          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
+          <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -4630,7 +4630,7 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>GSA3DN</t>
+          <t>GSA3DM</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4640,17 +4640,17 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
         </is>
       </c>
     </row>
@@ -4667,12 +4667,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna avseende…</t>
+          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>GSA3DP</t>
+          <t>GSA3DN</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4694,24 +4694,24 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>29 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna avseende…</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>GSA3DQ</t>
+          <t>GSA3DP</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DP</t>
         </is>
       </c>
     </row>
@@ -4748,12 +4748,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för perspektiv på och metoder för socialt arbete med barn, familjer, …</t>
+          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna rörande …</t>
+          <t>27 ord: - redogöra för perspektiv på och metoder för socialt arbete med barn, familjer, …</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -4792,7 +4792,7 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>GSA3DR</t>
+          <t>GSA3DQ</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4802,24 +4802,24 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>27 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna rörande …</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>GSA3DS</t>
+          <t>GSA3DR</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4834,19 +4834,19 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DR</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>GSA3FK</t>
+          <t>GSA3DS</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
         </is>
       </c>
     </row>
@@ -4883,12 +4883,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>34 ord: - utifrån ett brukarperspektiv genomföra olika typer av utredningar inom socialt…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>GSA3FL</t>
+          <t>GSA3FK</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4910,24 +4910,24 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>34 ord: - utifrån ett brukarperspektiv genomföra olika typer av utredningar inom socialt…</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>GSA3HA</t>
+          <t>GSA3FL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4942,19 +4942,19 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3HA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FL</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>SA1045</t>
+          <t>GSA3HA</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4969,19 +4969,19 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3HA</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>SA1048</t>
+          <t>SA1045</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1045</t>
         </is>
       </c>
     </row>
@@ -5018,12 +5018,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
+          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
+          <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -5062,7 +5062,7 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>SA2020</t>
+          <t>SA1048</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5072,17 +5072,17 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>26 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
         </is>
       </c>
     </row>
@@ -5099,12 +5099,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>32 ord: - uppvisa kunskaper som utgör innehåll i en tolkningsram (till exempel teori, te…</t>
+          <t>26 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>32 ord: - analysera resultat från ett vetenskapligt arbete på sådant sätt att tolkningsr…</t>
+          <t>32 ord: - uppvisa kunskaper som utgör innehåll i en tolkningsram (till exempel teori, te…</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>32 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
+          <t>32 ord: - analysera resultat från ett vetenskapligt arbete på sådant sätt att tolkningsr…</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -5170,7 +5170,7 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>SA3008</t>
+          <t>SA2020</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5180,17 +5180,17 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>32 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
       </c>
     </row>
@@ -5207,12 +5207,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>30 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>ASR24V</t>
+          <t>SA3008</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
+          <t>30 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>27 ord: - ur ett rättighetsperspektiv analysera och diskutera hur sociala, ekonomiska, m…</t>
+          <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>ASR25P</t>
+          <t>ASR24V</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5293,19 +5293,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
+          <t>27 ord: - ur ett rättighetsperspektiv analysera och diskutera hur sociala, ekonomiska, m…</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>ASR26N</t>
+          <t>ASR25P</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5315,17 +5315,17 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
         </is>
       </c>
     </row>
@@ -5342,12 +5342,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>30 ord: - diskutera vikten av samarbete och lagarbete inom och mellan utbildningsinstitu…</t>
+          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -5359,7 +5359,7 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>ASR284</t>
+          <t>ASR26N</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5374,19 +5374,19 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
+          <t>30 ord: - diskutera vikten av samarbete och lagarbete inom och mellan utbildningsinstitu…</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>ASR285</t>
+          <t>ASR284</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5396,17 +5396,17 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
+          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
         </is>
       </c>
     </row>
@@ -5423,12 +5423,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
+          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>ASR29S</t>
+          <t>ASR285</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5482,19 +5482,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>27 ord: - analysera och värdera resultat i relation till tidigare forskning, värdera den…</t>
+          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>ASR29T</t>
+          <t>ASR29S</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>26 ord: - problematisera och reflektera över kvinnans, barnets och närståendes roller oc…</t>
+          <t>27 ord: - analysera och värdera resultat i relation till tidigare forskning, värdera den…</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
+          <t>26 ord: - problematisera och reflektera över kvinnans, barnets och närståendes roller oc…</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>ASR29U</t>
+          <t>ASR29T</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5563,19 +5563,19 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>26 ord: - i simulerad miljö utföra undersökningar och behandlingar vid komplicerad gravi…</t>
+          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>ASR29V</t>
+          <t>ASR29U</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5585,17 +5585,17 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
+          <t>26 ord: - i simulerad miljö utföra undersökningar och behandlingar vid komplicerad gravi…</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
         </is>
       </c>
     </row>
@@ -5612,12 +5612,12 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
+          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -5656,7 +5656,7 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>ASR29W</t>
+          <t>ASR29V</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5671,19 +5671,19 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
+          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>ASR2AD</t>
+          <t>ASR29W</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5698,19 +5698,19 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av k…</t>
+          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2AD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29W</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>ASR2BM</t>
+          <t>ASR2AD</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5720,24 +5720,24 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av k…</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2BM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2AD</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>ASR2CE</t>
+          <t>ASR2BM</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5747,24 +5747,24 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2BM</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>GSR38B</t>
+          <t>ASR2CE</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5779,19 +5779,19 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>33 ord: - uppvisa kunskap, förståelse och reflekterande färdigheter om sexuell och repro…</t>
+          <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CE</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>SR3001</t>
+          <t>GSR38B</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5806,19 +5806,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>30 ord: - värdera olika strategier för ledarskap och interventioner som har potential at…</t>
+          <t>33 ord: - uppvisa kunskap, förståelse och reflekterande färdigheter om sexuell och repro…</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>SR3002</t>
+          <t>SR3001</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5833,19 +5833,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>27 ord: - analysera och kritiskt värdera styrkor och svagheter i forskningsprocessens ol…</t>
+          <t>30 ord: - värdera olika strategier för ledarskap och interventioner som har potential at…</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>SR3007</t>
+          <t>SR3002</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5855,24 +5855,24 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>27 ord: - analysera och kritiskt värdera styrkor och svagheter i forskningsprocessens ol…</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>SR3008</t>
+          <t>SR3007</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5887,19 +5887,19 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>SR3009</t>
+          <t>SR3008</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5909,17 +5909,17 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>26 ord: - analysera betydelsen av hälsofrämjande arbete under den reproduktiva livscykel…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
         </is>
       </c>
     </row>
@@ -5941,7 +5941,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>29 ord: - identifiera problemområden och formulera relevanta frågeställningar som rör gr…</t>
+          <t>26 ord: - analysera betydelsen av hälsofrämjande arbete under den reproduktiva livscykel…</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för benigna och maligna gynekologiska förändringar, värdera hälsotill…</t>
+          <t>29 ord: - identifiera problemområden och formulera relevanta frågeställningar som rör gr…</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -5980,7 +5980,7 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>SR3010</t>
+          <t>SR3009</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5995,19 +5995,19 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>27 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av g…</t>
+          <t>27 ord: - redogöra för benigna och maligna gynekologiska förändringar, värdera hälsotill…</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>SR3011</t>
+          <t>SR3010</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6022,19 +6022,19 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
+          <t>27 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av g…</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>SR3012</t>
+          <t>SR3011</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6044,17 +6044,17 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
+          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
         </is>
       </c>
     </row>
@@ -6071,12 +6071,12 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
+          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -6115,7 +6115,7 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>SR3014</t>
+          <t>SR3012</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6125,17 +6125,17 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 10 för 13.5 hp)</t>
+          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
       </c>
     </row>
@@ -6152,12 +6152,12 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>30 ord: - med ett professionellt förhållningssätt informera, ge stöd och trygghet i dial…</t>
+          <t>11 lärandemål (maximum rekommenderat: 10 för 13.5 hp)</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>SR3015</t>
+          <t>SR3014</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6179,17 +6179,17 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 10 för 13.5 hp)</t>
+          <t>30 ord: - med ett professionellt förhållningssätt informera, ge stöd och trygghet i dial…</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
         </is>
       </c>
     </row>
@@ -6206,12 +6206,12 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>35 ord: - självständigt handlägga preventivmedelsrådgivning och informera om lämpliga an…</t>
+          <t>14 lärandemål (maximum rekommenderat: 10 för 13.5 hp)</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>26 ord: - kritiskt analysera, värdera, föreslå och följa upp vårdnadsinsatser och behand…</t>
+          <t>35 ord: - självständigt handlägga preventivmedelsrådgivning och informera om lämpliga an…</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -6250,12 +6250,12 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>AVV2A6</t>
+          <t>SR3015</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6265,19 +6265,19 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>26 ord: - kritiskt reflektera över hur kvalitets- och säkerhetsledning organiseras och r…</t>
+          <t>26 ord: - kritiskt analysera, värdera, föreslå och följa upp vårdnadsinsatser och behand…</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV2A6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>VV2002</t>
+          <t>AVV2A6</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6292,19 +6292,19 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för gällande regelverk för olika professioner inom kommunal äldreomso…</t>
+          <t>26 ord: - kritiskt reflektera över hur kvalitets- och säkerhetsledning organiseras och r…</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV2A6</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>VV3006</t>
+          <t>VV2002</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6314,24 +6314,24 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>29 ord: - redogöra för gällande regelverk för olika professioner inom kommunal äldreomso…</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>VV3011</t>
+          <t>VV3006</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6346,19 +6346,19 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>19 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>VV3012</t>
+          <t>VV3011</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6368,17 +6368,17 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>29 ord: - tillämpa adekvat vetenskaplig design och metod i datainsamling och analys samt…</t>
+          <t>19 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>29 ord: - analysera och värdera resultat i relation till tidigare forskning samt den kli…</t>
+          <t>29 ord: - tillämpa adekvat vetenskaplig design och metod i datainsamling och analys samt…</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -6412,7 +6412,7 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>VV3017</t>
+          <t>VV3012</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>29 ord: - tillämpa adekvat vetenskaplig design och metod i datainsamling och analys samt…</t>
+          <t>29 ord: - analysera och värdera resultat i relation till tidigare forskning samt den kli…</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
         </is>
       </c>
     </row>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>29 ord: - analysera och värdera resultat i relation till tidigare forskning samt den kli…</t>
+          <t>29 ord: - tillämpa adekvat vetenskaplig design och metod i datainsamling och analys samt…</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -6481,17 +6481,44 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
+          <t>29 ord: - analysera och värdera resultat i relation till tidigare forskning samt den kli…</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>VV3017</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
           <t>26 ord: - göra relevanta bedömningar på mikro-, meso- och makronivå med hänsyn till samh…</t>
         </is>
       </c>
-      <c r="E224" s="2" t="inlineStr">
+      <c r="E225" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E224"/>
+  <autoFilter ref="A1:E225"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -6939,6 +6966,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId444"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A224" r:id="rId445"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A225" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId448"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Omfång på lärandemål.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$225</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$223</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E225"/>
+  <dimension ref="A1:E223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1579,7 +1579,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GIH37Q</t>
+          <t>GIH37R</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1589,24 +1589,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
+          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GIH37R</t>
+          <t>GIH37S</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1621,19 +1621,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>19 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37S</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GIH37S</t>
+          <t>GIH38Z</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1643,17 +1643,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>19 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>28 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH38Z</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>28 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
+          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GIH38Z</t>
+          <t>GIH392</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1707,14 +1707,14 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH38Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH392</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GIH392</t>
+          <t>GIH39E</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1734,14 +1734,14 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH392</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39E</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GIH39E</t>
+          <t>GIH39H</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
+          <t>26 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39H</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GIH39H</t>
+          <t>GIH3AM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1778,24 +1778,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>26 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 2 hp)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GIH3AM</t>
+          <t>GIH3AN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1805,24 +1805,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 2 hp)</t>
+          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AN</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GIH3AN</t>
+          <t>GIH3AP</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>28 ord: - på en grundläggande nivå diskutera och problematisera skolämnet idrott och häl…</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>28 ord: - på en grundläggande nivå diskutera och problematisera skolämnet idrott och häl…</t>
+          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
+          <t>26 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GIH3AP</t>
+          <t>GIH3D4</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1945,19 +1945,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>26 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
+          <t>29 ord: - utifrån vetenskaplig grund inom området välja övningar och designa ett träning…</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GIH3AP</t>
+          <t>GIH3D5</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1972,19 +1972,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
+          <t>28 ord: - utifrån vetenskaplig grund inom området välja övningar och designa ett hälsoin…</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GIH3D4</t>
+          <t>GIH3FA</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1994,24 +1994,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>29 ord: - utifrån vetenskaplig grund inom området välja övningar och designa ett träning…</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3FA</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GIH3D5</t>
+          <t>GIH3G4</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2021,24 +2021,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>28 ord: - utifrån vetenskaplig grund inom området välja övningar och designa ett hälsoin…</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GIH3FA</t>
+          <t>GIH3G6</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2058,14 +2058,14 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3FA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GIH3G4</t>
+          <t>GIH3G9</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2075,24 +2075,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>28 ord: - formulera en affärsplan med tillhörande budget inom området idrott och hälsa s…</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GIH3G6</t>
+          <t>IH1002</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2102,24 +2102,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GIH3G9</t>
+          <t>IH1002</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2134,19 +2134,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>28 ord: - formulera en affärsplan med tillhörande budget inom området idrott och hälsa s…</t>
+          <t>26 ord: - skapa lärandesituationer i ett urval av de behandlade rörelseaktiviteterna med…</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>IH1002</t>
+          <t>IH1011</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2156,24 +2156,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>IH1002</t>
+          <t>IH1011</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2188,19 +2188,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>26 ord: - skapa lärandesituationer i ett urval av de behandlade rörelseaktiviteterna med…</t>
+          <t>27 ord: - skapa stimulerande lärandesituationer i olika pedagogiska sammanhang, som ocks…</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>IH1011</t>
+          <t>IH1012</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2220,14 +2220,14 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1012</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>IH1011</t>
+          <t>IH1029</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2242,19 +2242,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>27 ord: - skapa stimulerande lärandesituationer i olika pedagogiska sammanhang, som ocks…</t>
+          <t>29 ord: - skapa lärandesituationer i de kunskapsområden som explicit nämns i kursplanern…</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1029</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>IH1012</t>
+          <t>IH1062</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2264,24 +2264,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>16 lärandemål (maximum rekommenderat: 12 för 20 hp)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1062</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>IH1029</t>
+          <t>IH1095</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2291,24 +2291,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>29 ord: - skapa lärandesituationer i de kunskapsområden som explicit nämns i kursplanern…</t>
+          <t>1 lärandemål (minimum rekommenderat: 3 för 1.5 hp)</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1095</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>IH1062</t>
+          <t>IH1096</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2318,24 +2318,24 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>16 lärandemål (maximum rekommenderat: 12 för 20 hp)</t>
+          <t>1 lärandemål (minimum rekommenderat: 3 för 1.5 hp)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1062</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1096</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>IH1095</t>
+          <t>IH1097</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2355,14 +2355,14 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1095</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1097</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>IH1096</t>
+          <t>IH1098</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2382,14 +2382,14 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1096</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1098</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>IH1097</t>
+          <t>IH1099</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2409,14 +2409,14 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1097</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1099</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>IH1098</t>
+          <t>IH1100</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2436,14 +2436,14 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1098</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1100</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>IH1099</t>
+          <t>IH1101</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2463,14 +2463,14 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1099</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1101</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>IH1100</t>
+          <t>IH1102</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2490,14 +2490,14 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1100</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1102</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>IH1101</t>
+          <t>IH1113</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2507,24 +2507,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 3 för 1.5 hp)</t>
+          <t>30 ord: - tillämpa grundläggande kunskaper inom ämnesområdet fysisk träning med specifik…</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1101</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>IH1102</t>
+          <t>IH1113</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2534,24 +2534,24 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 3 för 1.5 hp)</t>
+          <t>26 ord: - praktisk genomföra och instruera övningar inriktade mot optimering av de fysis…</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1102</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>IH1113</t>
+          <t>IH1114</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2566,19 +2566,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>30 ord: - tillämpa grundläggande kunskaper inom ämnesområdet fysisk träning med specifik…</t>
+          <t>28 ord: - redogöra för de viktigaste mikro- och makronutrienterna och deras betydelse vi…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>IH1113</t>
+          <t>IH1114</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2593,19 +2593,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>26 ord: - praktisk genomföra och instruera övningar inriktade mot optimering av de fysis…</t>
+          <t>36 ord: - visa förståelse för samt praktiskt tillämpa de centrala principerna för utform…</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>IH1114</t>
+          <t>IH2001</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2615,24 +2615,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>28 ord: - redogöra för de viktigaste mikro- och makronutrienterna och deras betydelse vi…</t>
+          <t>3 lärandemål (minimum rekommenderat: 5 för 30 hp)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>IH1114</t>
+          <t>IH2002</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2642,24 +2642,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>36 ord: - visa förståelse för samt praktiskt tillämpa de centrala principerna för utform…</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>IH2001</t>
+          <t>IH2002</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2669,24 +2669,24 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 5 för 30 hp)</t>
+          <t>26 ord: - självständigt identifiera, formulera och diskutera frågeställningar som berör …</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>IH2002</t>
+          <t>IH2005</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2696,29 +2696,29 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - självständigt identifiera, formulera och diskutera frågeställningar som berör …</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2005</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>IH2002</t>
+          <t>AMC243</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>26 ord: - självständigt identifiera, formulera och diskutera frågeställningar som berör …</t>
+          <t>26 ord: - självständigt söka, sammanställa och kritiskt granska evidensbaserad informati…</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC243</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>IH2005</t>
+          <t>AMC288</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2755,19 +2755,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>26 ord: - självständigt identifiera, formulera och diskutera frågeställningar som berör …</t>
+          <t>38 ord: - beskriva samband mellan fysisk aktivitet och hälsa vid en vald diagnos eller s…</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>AMC243</t>
+          <t>AMC288</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2782,12 +2782,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>26 ord: - självständigt söka, sammanställa och kritiskt granska evidensbaserad informati…</t>
+          <t>27 ord: - jämföra och kritiskt diskutera olika mät- och utvärderingsmetoder för fysisk a…</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC243</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
         </is>
       </c>
     </row>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>38 ord: - beskriva samband mellan fysisk aktivitet och hälsa vid en vald diagnos eller s…</t>
+          <t>34 ord: - utifrån vetenskaplig evidens beskriva hur fysisk träning kan utformas beroende…</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>27 ord: - jämföra och kritiskt diskutera olika mät- och utvärderingsmetoder för fysisk a…</t>
+          <t>35 ord: - med stöd i vetenskaplig litteratur och egen erfarenhet reflektera kring den ro…</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>34 ord: - utifrån vetenskaplig evidens beskriva hur fysisk träning kan utformas beroende…</t>
+          <t>31 ord: - med stöd i relevant teoribildning identifiera hinder och underlättande faktore…</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -2875,7 +2875,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>AMC288</t>
+          <t>AMC28N</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2890,19 +2890,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>35 ord: - med stöd i vetenskaplig litteratur och egen erfarenhet reflektera kring den ro…</t>
+          <t>26 ord: - presentera och argumentera för vald design hos ett tänkt forskningsprojekt ino…</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC28N</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>AMC288</t>
+          <t>AMC29F</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2917,19 +2917,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>31 ord: - med stöd i relevant teoribildning identifiera hinder och underlättande faktore…</t>
+          <t>26 ord: - självständigt identifiera och formulera problemställning och syfte för en vete…</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>AMC28N</t>
+          <t>AMC29F</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>26 ord: - presentera och argumentera för vald design hos ett tänkt forskningsprojekt ino…</t>
+          <t>29 ord: - genomföra en vetenskaplig undersökning med relevant design, metod och analys s…</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC28N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>26 ord: - självständigt identifiera och formulera problemställning och syfte för en vete…</t>
+          <t>32 ord: - analysera och värdera resultat från den vetenskapliga undersökningen i relatio…</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>29 ord: - genomföra en vetenskaplig undersökning med relevant design, metod och analys s…</t>
+          <t>28 ord: - försvara eget självständigt arbete samt kritiskt granska och värdera annat exa…</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -3010,7 +3010,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>AMC29F</t>
+          <t>AMC29Y</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3025,19 +3025,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>32 ord: - analysera och värdera resultat från den vetenskapliga undersökningen i relatio…</t>
+          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>AMC29F</t>
+          <t>AMC2A7</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3047,24 +3047,24 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>28 ord: - försvara eget självständigt arbete samt kritiskt granska och värdera annat exa…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>AMC29Y</t>
+          <t>AMC2BG</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3084,14 +3084,14 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>AMC2A7</t>
+          <t>GMC32X</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3101,24 +3101,24 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>29 ord: - förskriva och informera om förbrukningsartiklar vid urindysfunktion, urinreten…</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC32X</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>AMC2BG</t>
+          <t>GMC37E</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3128,24 +3128,24 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
+          <t>1 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GMC32X</t>
+          <t>GMC37E</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3160,19 +3160,19 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>29 ord: - förskriva och informera om förbrukningsartiklar vid urindysfunktion, urinreten…</t>
+          <t>30 ord: - Namnge, beskriva och förklara anatomi och funktion under människans livscykel …</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC32X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GMC37E</t>
+          <t>GMC37T</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3187,19 +3187,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 6 hp)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37T</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GMC37E</t>
+          <t>MC1072</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3214,19 +3214,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>30 ord: - Namnge, beskriva och förklara anatomi och funktion under människans livscykel …</t>
+          <t>26 ord: - söka relevant information utifrån fysiologiska frågeställningar relaterade til…</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1072</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GMC37T</t>
+          <t>MC1077</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3236,24 +3236,24 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 6 hp)</t>
+          <t>31 ord: - redogöra för hygieniska principer i vårdarbetet samt visa kännedom om de lagar…</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>MC1072</t>
+          <t>MC2017</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3263,24 +3263,24 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>26 ord: - söka relevant information utifrån fysiologiska frågeställningar relaterade til…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1072</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>MC1077</t>
+          <t>MC2017</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>31 ord: - redogöra för hygieniska principer i vårdarbetet samt visa kännedom om de lagar…</t>
+          <t>26 ord: -  redogöra för innehållet i de författningar som reglerar ansvarsfrågor och ans…</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
         </is>
       </c>
     </row>
@@ -3317,12 +3317,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>26 ord: -  redogöra för hur anpassningsstörningar kan manifesteras hos barn, ungdomar oc…</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -3334,7 +3334,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>MC2017</t>
+          <t>MC3027</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3349,51 +3349,51 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>26 ord: -  redogöra för innehållet i de författningar som reglerar ansvarsfrågor och ans…</t>
+          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>MC2017</t>
+          <t>GNV367</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>26 ord: -  redogöra för hur anpassningsstörningar kan manifesteras hos barn, ungdomar oc…</t>
+          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>MC3027</t>
+          <t>GNV367</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3403,19 +3403,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
+          <t>33 ord: - visa grundläggande kunskap om lärande för hållbar utveckling i grundskolans år…</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GNV367</t>
+          <t>GNV3GV</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3425,24 +3425,24 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>28 ord: - redogöra för grundläggande kunskaper i naturvetenskap, med särskilt fokus på e…</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GNV367</t>
+          <t>GNV3GV</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3457,19 +3457,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>33 ord: - visa grundläggande kunskap om lärande för hållbar utveckling i grundskolans år…</t>
+          <t>34 ord: - reflektera över och problematisera skolans roll i arbetet med lärande för håll…</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GNV3GV</t>
+          <t>NV1035</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3479,24 +3479,24 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>28 ord: - redogöra för grundläggande kunskaper i naturvetenskap, med särskilt fokus på e…</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GNV3GV</t>
+          <t>NV1036</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>34 ord: - reflektera över och problematisera skolans roll i arbetet med lärande för håll…</t>
+          <t>14 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>NV1035</t>
+          <t>NV1036</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3533,17 +3533,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - visa god förtrogenhet med och reflektera över kursplanerna inom SO, NO och tek…</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
         </is>
       </c>
     </row>
@@ -3560,12 +3560,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>32 ord: - visa insikt om hur närmiljö, förstahandsupplevelser, estetik och digital tekni…</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -3577,7 +3577,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>NV1036</t>
+          <t>NV3001</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3592,19 +3592,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>26 ord: - visa god förtrogenhet med och reflektera över kursplanerna inom SO, NO och tek…</t>
+          <t>27 ord: - kritiskt diskutera begreppet hållbar utveckling och dess olika dimensioner, so…</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>NV1036</t>
+          <t>NV3001</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3619,73 +3619,73 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>32 ord: - visa insikt om hur närmiljö, förstahandsupplevelser, estetik och digital tekni…</t>
+          <t>27 ord: - reflektera över vilken roll den högre utbildningen har för hållbar utveckling,…</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>NV3001</t>
+          <t>ASA24K</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>27 ord: - kritiskt diskutera begreppet hållbar utveckling och dess olika dimensioner, so…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24K</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>NV3001</t>
+          <t>ASA24L</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>27 ord: - reflektera över vilken roll den högre utbildningen har för hållbar utveckling,…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24L</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>ASA24K</t>
+          <t>ASA266</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3705,14 +3705,14 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA266</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>ASA24L</t>
+          <t>ASA26U</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3727,19 +3727,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA26U</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>ASA266</t>
+          <t>ASA27E</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3754,19 +3754,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 5 hp)</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>ASA26U</t>
+          <t>ASA293</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3786,14 +3786,14 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA26U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA293</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>ASA27E</t>
+          <t>GSA24U</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3808,19 +3808,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>ASA293</t>
+          <t>GSA24V</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3835,19 +3835,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA293</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GSA24U</t>
+          <t>GSA24V</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3857,17 +3857,17 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>27 ord: - redogöra för perspektiv på och metoder för socialt arbete med barn, familjer, …</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
         </is>
       </c>
     </row>
@@ -3884,12 +3884,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>27 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna rörande …</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -3901,7 +3901,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GSA24V</t>
+          <t>GSA27Y</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3911,24 +3911,24 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för perspektiv på och metoder för socialt arbete med barn, familjer, …</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA27Y</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GSA24V</t>
+          <t>GSA2AF</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3938,24 +3938,24 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna rörande …</t>
+          <t>14 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GSA27Y</t>
+          <t>GSA2AF</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3965,17 +3965,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>29 ord: - uppvisa kunskaper om en tolkningsram (till exempel teori, teoretiska begrepp, …</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA27Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
       </c>
     </row>
@@ -3992,12 +3992,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>28 ord: - välja och beskriva en relevant tolkningsram (till exempel teori, teoretiska be…</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>29 ord: - uppvisa kunskaper om en tolkningsram (till exempel teori, teoretiska begrepp, …</t>
+          <t>32 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -4036,7 +4036,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>GSA2BV</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4046,24 +4046,24 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>28 ord: - välja och beskriva en relevant tolkningsram (till exempel teori, teoretiska be…</t>
+          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>GSA2BV</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4078,12 +4078,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>32 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
+          <t>26 ord: - visa förmåga att under handledning planera, strukturera och självständigt geno…</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
       </c>
     </row>
@@ -4100,12 +4100,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>28 ord: - visa förmåga och färdigheter att identifiera, definiera, analysera och dokumen…</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>26 ord: - visa förmåga att under handledning planera, strukturera och självständigt geno…</t>
+          <t>28 ord: - kritiskt reflektera över den egna förmågan och den personliga och professionel…</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GSA2BV</t>
+          <t>GSA2DW</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4154,24 +4154,24 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga och färdigheter att identifiera, definiera, analysera och dokumen…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GSA2BV</t>
+          <t>GSA2DW</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4186,19 +4186,19 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>28 ord: - kritiskt reflektera över den egna förmågan och den personliga och professionel…</t>
+          <t>29 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna avseende…</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GSA2DW</t>
+          <t>GSA2E3</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4213,19 +4213,19 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E3</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GSA2DW</t>
+          <t>GSA2E4</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4235,24 +4235,24 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna avseende…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GSA2E3</t>
+          <t>GSA2E4</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4262,24 +4262,24 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>29 ord: - visa kunskap om och förståelse för hur familje- och samhällsförhållanden påver…</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>GSA2E4</t>
+          <t>GSA2E5</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4294,19 +4294,19 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GSA2E4</t>
+          <t>GSA2NA</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4316,24 +4316,24 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskap om och förståelse för hur familje- och samhällsförhållanden påver…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NA</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>GSA2E5</t>
+          <t>GSA2NC</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4348,19 +4348,19 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>14 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GSA2NA</t>
+          <t>GSA2RE</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4380,14 +4380,14 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2RE</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GSA2NC</t>
+          <t>GSA2SD</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4402,19 +4402,19 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>GSA2RE</t>
+          <t>GSA2SE</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4429,19 +4429,19 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2RE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GSA2SD</t>
+          <t>GSA2XN</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4456,19 +4456,19 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2XN</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GSA2SE</t>
+          <t>GSA32Y</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4483,19 +4483,19 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GSA2XN</t>
+          <t>GSA352</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4510,19 +4510,19 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2XN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA352</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GSA32Y</t>
+          <t>GSA3DM</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4537,19 +4537,19 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>GSA352</t>
+          <t>GSA3DM</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4559,17 +4559,17 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA352</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
         </is>
       </c>
     </row>
@@ -4586,12 +4586,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -4603,7 +4603,7 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>GSA3DM</t>
+          <t>GSA3DN</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4613,24 +4613,24 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
+          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>GSA3DM</t>
+          <t>GSA3DN</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4645,19 +4645,19 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
+          <t>29 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna avseende…</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>GSA3DN</t>
+          <t>GSA3DP</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4672,19 +4672,19 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DP</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>GSA3DN</t>
+          <t>GSA3DQ</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4694,24 +4694,24 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna avseende…</t>
+          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>GSA3DP</t>
+          <t>GSA3DQ</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4721,17 +4721,17 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>27 ord: - redogöra för perspektiv på och metoder för socialt arbete med barn, familjer, …</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
         </is>
       </c>
     </row>
@@ -4748,12 +4748,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>27 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna rörande …</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -4765,7 +4765,7 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>GSA3DQ</t>
+          <t>GSA3DR</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4775,24 +4775,24 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för perspektiv på och metoder för socialt arbete med barn, familjer, …</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DR</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>GSA3DQ</t>
+          <t>GSA3DS</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4802,24 +4802,24 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna rörande …</t>
+          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>GSA3DR</t>
+          <t>GSA3FK</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4834,19 +4834,19 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>GSA3DS</t>
+          <t>GSA3FK</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4856,24 +4856,24 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>34 ord: - utifrån ett brukarperspektiv genomföra olika typer av utredningar inom socialt…</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>GSA3FK</t>
+          <t>GSA3FL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4888,19 +4888,19 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FL</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>GSA3FK</t>
+          <t>GSA3HA</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4910,24 +4910,24 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>34 ord: - utifrån ett brukarperspektiv genomföra olika typer av utredningar inom socialt…</t>
+          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3HA</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>GSA3FL</t>
+          <t>SA1045</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4942,19 +4942,19 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1045</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>GSA3HA</t>
+          <t>SA1048</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4969,19 +4969,19 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3HA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>SA1045</t>
+          <t>SA1048</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4991,17 +4991,17 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
         </is>
       </c>
     </row>
@@ -5018,12 +5018,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -5035,7 +5035,7 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>SA1048</t>
+          <t>SA2020</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5045,24 +5045,24 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
+          <t>26 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>SA1048</t>
+          <t>SA2020</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5077,12 +5077,12 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
+          <t>32 ord: - uppvisa kunskaper som utgör innehåll i en tolkningsram (till exempel teori, te…</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
       </c>
     </row>
@@ -5099,12 +5099,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>26 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>32 ord: - analysera resultat från ett vetenskapligt arbete på sådant sätt att tolkningsr…</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>32 ord: - uppvisa kunskaper som utgör innehåll i en tolkningsram (till exempel teori, te…</t>
+          <t>32 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -5143,7 +5143,7 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>SA2020</t>
+          <t>SA3008</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5153,24 +5153,24 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>32 ord: - analysera resultat från ett vetenskapligt arbete på sådant sätt att tolkningsr…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>SA2020</t>
+          <t>SA3008</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5185,51 +5185,51 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>32 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
+          <t>30 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>SA3008</t>
+          <t>ASR24V</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>SA3008</t>
+          <t>ASR24V</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5239,19 +5239,19 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>30 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
+          <t>27 ord: - ur ett rättighetsperspektiv analysera och diskutera hur sociala, ekonomiska, m…</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>ASR24V</t>
+          <t>ASR25P</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5266,19 +5266,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
+          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>ASR24V</t>
+          <t>ASR26N</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5288,24 +5288,24 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>27 ord: - ur ett rättighetsperspektiv analysera och diskutera hur sociala, ekonomiska, m…</t>
+          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>ASR25P</t>
+          <t>ASR26N</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5320,19 +5320,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
+          <t>30 ord: - diskutera vikten av samarbete och lagarbete inom och mellan utbildningsinstitu…</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>ASR26N</t>
+          <t>ASR284</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5342,24 +5342,24 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>ASR26N</t>
+          <t>ASR285</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5369,24 +5369,24 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>30 ord: - diskutera vikten av samarbete och lagarbete inom och mellan utbildningsinstitu…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>ASR284</t>
+          <t>ASR285</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
+          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
       </c>
     </row>
@@ -5423,12 +5423,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
+          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -5440,7 +5440,7 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>ASR285</t>
+          <t>ASR29S</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5455,19 +5455,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
+          <t>27 ord: - analysera och värdera resultat i relation till tidigare forskning, värdera den…</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>ASR285</t>
+          <t>ASR29T</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5482,19 +5482,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
+          <t>26 ord: - problematisera och reflektera över kvinnans, barnets och närståendes roller oc…</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>ASR29S</t>
+          <t>ASR29T</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5509,19 +5509,19 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>27 ord: - analysera och värdera resultat i relation till tidigare forskning, värdera den…</t>
+          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>ASR29T</t>
+          <t>ASR29U</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5536,19 +5536,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>26 ord: - problematisera och reflektera över kvinnans, barnets och närståendes roller oc…</t>
+          <t>26 ord: - i simulerad miljö utföra undersökningar och behandlingar vid komplicerad gravi…</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>ASR29T</t>
+          <t>ASR29V</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5558,24 +5558,24 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>ASR29U</t>
+          <t>ASR29V</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>26 ord: - i simulerad miljö utföra undersökningar och behandlingar vid komplicerad gravi…</t>
+          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
         </is>
       </c>
     </row>
@@ -5612,12 +5612,12 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
+          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -5629,7 +5629,7 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>ASR29V</t>
+          <t>ASR29W</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5644,19 +5644,19 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
+          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29W</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>ASR29V</t>
+          <t>ASR2AD</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5671,19 +5671,19 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
+          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av k…</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2AD</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>ASR29W</t>
+          <t>ASR2BM</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5693,24 +5693,24 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2BM</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>ASR2AD</t>
+          <t>ASR2CE</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5725,19 +5725,19 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av k…</t>
+          <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2AD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CE</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>ASR2BM</t>
+          <t>GSR38B</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5747,24 +5747,24 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>33 ord: - uppvisa kunskap, förståelse och reflekterande färdigheter om sexuell och repro…</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2BM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>ASR2CE</t>
+          <t>SR3001</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5779,19 +5779,19 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
+          <t>30 ord: - värdera olika strategier för ledarskap och interventioner som har potential at…</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>GSR38B</t>
+          <t>SR3002</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5806,19 +5806,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>33 ord: - uppvisa kunskap, förståelse och reflekterande färdigheter om sexuell och repro…</t>
+          <t>27 ord: - analysera och kritiskt värdera styrkor och svagheter i forskningsprocessens ol…</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>SR3001</t>
+          <t>SR3007</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5828,24 +5828,24 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>30 ord: - värdera olika strategier för ledarskap och interventioner som har potential at…</t>
+          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>SR3002</t>
+          <t>SR3008</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5855,24 +5855,24 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>27 ord: - analysera och kritiskt värdera styrkor och svagheter i forskningsprocessens ol…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>SR3007</t>
+          <t>SR3009</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5882,24 +5882,24 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>26 ord: - analysera betydelsen av hälsofrämjande arbete under den reproduktiva livscykel…</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>SR3008</t>
+          <t>SR3009</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5909,17 +5909,17 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>29 ord: - identifiera problemområden och formulera relevanta frågeställningar som rör gr…</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
         </is>
       </c>
     </row>
@@ -5941,7 +5941,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>26 ord: - analysera betydelsen av hälsofrämjande arbete under den reproduktiva livscykel…</t>
+          <t>27 ord: - redogöra för benigna och maligna gynekologiska förändringar, värdera hälsotill…</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>SR3009</t>
+          <t>SR3010</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5968,19 +5968,19 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>29 ord: - identifiera problemområden och formulera relevanta frågeställningar som rör gr…</t>
+          <t>27 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av g…</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>SR3009</t>
+          <t>SR3011</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5995,19 +5995,19 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för benigna och maligna gynekologiska förändringar, värdera hälsotill…</t>
+          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>SR3010</t>
+          <t>SR3012</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6017,24 +6017,24 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>27 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av g…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>SR3011</t>
+          <t>SR3012</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
+          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
       </c>
     </row>
@@ -6071,12 +6071,12 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
+          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>SR3012</t>
+          <t>SR3014</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6098,24 +6098,24 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
+          <t>11 lärandemål (maximum rekommenderat: 10 för 13.5 hp)</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>SR3012</t>
+          <t>SR3014</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6130,19 +6130,19 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
+          <t>30 ord: - med ett professionellt förhållningssätt informera, ge stöd och trygghet i dial…</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>SR3014</t>
+          <t>SR3015</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6157,19 +6157,19 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 10 för 13.5 hp)</t>
+          <t>14 lärandemål (maximum rekommenderat: 10 för 13.5 hp)</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>SR3014</t>
+          <t>SR3015</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>30 ord: - med ett professionellt förhållningssätt informera, ge stöd och trygghet i dial…</t>
+          <t>35 ord: - självständigt handlägga preventivmedelsrådgivning och informera om lämpliga an…</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
         </is>
       </c>
     </row>
@@ -6206,12 +6206,12 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 10 för 13.5 hp)</t>
+          <t>26 ord: - kritiskt analysera, värdera, föreslå och följa upp vårdnadsinsatser och behand…</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>SR3015</t>
+          <t>AVV2A6</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6238,24 +6238,24 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>35 ord: - självständigt handlägga preventivmedelsrådgivning och informera om lämpliga an…</t>
+          <t>26 ord: - kritiskt reflektera över hur kvalitets- och säkerhetsledning organiseras och r…</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV2A6</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>SR3015</t>
+          <t>VV2002</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6265,19 +6265,19 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>26 ord: - kritiskt analysera, värdera, föreslå och följa upp vårdnadsinsatser och behand…</t>
+          <t>29 ord: - redogöra för gällande regelverk för olika professioner inom kommunal äldreomso…</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>AVV2A6</t>
+          <t>VV3006</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6287,24 +6287,24 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>26 ord: - kritiskt reflektera över hur kvalitets- och säkerhetsledning organiseras och r…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV2A6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>VV2002</t>
+          <t>VV3011</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6314,24 +6314,24 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för gällande regelverk för olika professioner inom kommunal äldreomso…</t>
+          <t>19 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>VV3006</t>
+          <t>VV3012</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>29 ord: - tillämpa adekvat vetenskaplig design och metod i datainsamling och analys samt…</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>VV3011</t>
+          <t>VV3012</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6368,24 +6368,24 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>19 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>29 ord: - analysera och värdera resultat i relation till tidigare forskning samt den kli…</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>VV3012</t>
+          <t>VV3017</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6405,14 +6405,14 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>VV3012</t>
+          <t>VV3017</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
         </is>
       </c>
     </row>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>29 ord: - tillämpa adekvat vetenskaplig design och metod i datainsamling och analys samt…</t>
+          <t>26 ord: - göra relevanta bedömningar på mikro-, meso- och makronivå med hänsyn till samh…</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -6463,62 +6463,8 @@
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="2" t="inlineStr">
-        <is>
-          <t>VV3017</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>29 ord: - analysera och värdera resultat i relation till tidigare forskning samt den kli…</t>
-        </is>
-      </c>
-      <c r="E224" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
-        <is>
-          <t>VV3017</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>26 ord: - göra relevanta bedömningar på mikro-, meso- och makronivå med hänsyn till samh…</t>
-        </is>
-      </c>
-      <c r="E225" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E225"/>
+  <autoFilter ref="A1:E223"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -6964,10 +6910,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId442"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A223" r:id="rId443"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A224" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A225" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId448"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Omfång på lärandemål.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$223</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$203</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E223"/>
+  <dimension ref="A1:E203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -850,7 +850,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GIH2D8</t>
+          <t>GIH2G4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -865,19 +865,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 2 hp)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2G4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GIH2D9</t>
+          <t>GIH2QL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -887,24 +887,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 2 hp)</t>
+          <t>30 ord: - med goda rörelsekvaliteter delta i olika rörelseaktiviteter med relevans för t…</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QL</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GIH2DD</t>
+          <t>GIH2WT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -914,24 +914,24 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 3 för 3 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GIH2DE</t>
+          <t>GIH2WY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -941,24 +941,24 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 3 för 3 hp)</t>
+          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WY</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GIH2G4</t>
+          <t>GIH2X3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -968,24 +968,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>29 ord: - utifrån vetenskaplig grund inom området välja övningar och designa ett träning…</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2G4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2X3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GIH2LT</t>
+          <t>GIH2ZC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -995,24 +995,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 2.5 hp)</t>
+          <t>26 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GIH2LU</t>
+          <t>GIH2ZD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1022,24 +1022,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 2.5 hp)</t>
+          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZD</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GIH2LX</t>
+          <t>GIH335</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1049,24 +1049,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 5 hp)</t>
+          <t>27 ord: - formulera en affärsplan med tillhörande budget inom området idrott och hälsa s…</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH335</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GIH2LY</t>
+          <t>GIH34S</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1076,24 +1076,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 5 hp)</t>
+          <t>28 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34S</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GIH2M4</t>
+          <t>GIH34S</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1103,24 +1103,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 5 hp)</t>
+          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34S</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GIH2M6</t>
+          <t>GIH35T</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1135,19 +1135,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 2.5 hp)</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35T</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GIH2QL</t>
+          <t>GIH37P</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>30 ord: - med goda rörelsekvaliteter delta i olika rörelseaktiviteter med relevans för t…</t>
+          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GIH2WT</t>
+          <t>GIH37Q</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1189,19 +1189,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GIH2WY</t>
+          <t>GIH37Q</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
+          <t>28 ord: - på en grundläggande nivå diskutera och problematisera skolämnet idrott och häl…</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GIH2X3</t>
+          <t>GIH37Q</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1243,19 +1243,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>29 ord: - utifrån vetenskaplig grund inom området välja övningar och designa ett träning…</t>
+          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2X3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZC</t>
+          <t>GIH37Q</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1275,14 +1275,14 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZD</t>
+          <t>GIH37R</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1292,24 +1292,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
+          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GIH335</t>
+          <t>GIH37S</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1319,24 +1319,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>27 ord: - formulera en affärsplan med tillhörande budget inom området idrott och hälsa s…</t>
+          <t>19 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH335</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37S</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GIH33K</t>
+          <t>GIH38Z</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1346,24 +1346,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 3 för 3 hp)</t>
+          <t>28 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH38Z</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GIH34S</t>
+          <t>GIH38Z</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1378,19 +1378,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>28 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
+          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH38Z</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GIH34S</t>
+          <t>GIH392</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1410,14 +1410,14 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH392</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GIH35T</t>
+          <t>GIH39E</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1427,24 +1427,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39E</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GIH37P</t>
+          <t>GIH39H</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1454,24 +1454,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39H</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GIH37Q</t>
+          <t>GIH3AN</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1491,14 +1491,14 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AN</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GIH37Q</t>
+          <t>GIH3AP</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1508,24 +1508,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>28 ord: - på en grundläggande nivå diskutera och problematisera skolämnet idrott och häl…</t>
+          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GIH37Q</t>
+          <t>GIH3AP</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1540,19 +1540,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
+          <t>28 ord: - på en grundläggande nivå diskutera och problematisera skolämnet idrott och häl…</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GIH37Q</t>
+          <t>GIH3AP</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1567,19 +1567,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>26 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
+          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GIH37R</t>
+          <t>GIH3AP</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1589,24 +1589,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GIH37S</t>
+          <t>GIH3D4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>19 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>29 ord: - utifrån vetenskaplig grund inom området välja övningar och designa ett träning…</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GIH38Z</t>
+          <t>GIH3D5</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1648,19 +1648,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>28 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
+          <t>28 ord: - utifrån vetenskaplig grund inom området välja övningar och designa ett hälsoin…</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH38Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GIH38Z</t>
+          <t>GIH3FA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1670,24 +1670,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH38Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3FA</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GIH392</t>
+          <t>GIH3G4</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1697,24 +1697,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH392</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GIH39E</t>
+          <t>GIH3G6</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1724,24 +1724,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GIH39H</t>
+          <t>GIH3G9</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>26 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
+          <t>28 ord: - formulera en affärsplan med tillhörande budget inom området idrott och hälsa s…</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GIH3AM</t>
+          <t>IH1002</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1778,24 +1778,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 2 hp)</t>
+          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GIH3AN</t>
+          <t>IH1002</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1805,24 +1805,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - skapa lärandesituationer i ett urval av de behandlade rörelseaktiviteterna med…</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GIH3AP</t>
+          <t>IH1011</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1832,24 +1832,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GIH3AP</t>
+          <t>IH1011</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1864,19 +1864,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>28 ord: - på en grundläggande nivå diskutera och problematisera skolämnet idrott och häl…</t>
+          <t>27 ord: - skapa stimulerande lärandesituationer i olika pedagogiska sammanhang, som ocks…</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GIH3AP</t>
+          <t>IH1012</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1886,24 +1886,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1012</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GIH3AP</t>
+          <t>IH1029</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1918,19 +1918,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>26 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
+          <t>29 ord: - skapa lärandesituationer i de kunskapsområden som explicit nämns i kursplanern…</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1029</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GIH3D4</t>
+          <t>IH1062</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1940,24 +1940,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>29 ord: - utifrån vetenskaplig grund inom området välja övningar och designa ett träning…</t>
+          <t>16 lärandemål (maximum rekommenderat: 12 för 20 hp)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1062</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GIH3D5</t>
+          <t>IH1113</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1972,19 +1972,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>28 ord: - utifrån vetenskaplig grund inom området välja övningar och designa ett hälsoin…</t>
+          <t>30 ord: - tillämpa grundläggande kunskaper inom ämnesområdet fysisk träning med specifik…</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GIH3FA</t>
+          <t>IH1113</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1994,24 +1994,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>26 ord: - praktisk genomföra och instruera övningar inriktade mot optimering av de fysis…</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3FA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GIH3G4</t>
+          <t>IH1114</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2021,24 +2021,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>28 ord: - redogöra för de viktigaste mikro- och makronutrienterna och deras betydelse vi…</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GIH3G6</t>
+          <t>IH1114</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2048,24 +2048,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>36 ord: - visa förståelse för samt praktiskt tillämpa de centrala principerna för utform…</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GIH3G9</t>
+          <t>IH2001</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2075,24 +2075,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>28 ord: - formulera en affärsplan med tillhörande budget inom området idrott och hälsa s…</t>
+          <t>3 lärandemål (minimum rekommenderat: 5 för 30 hp)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>IH1002</t>
+          <t>IH2002</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2107,19 +2107,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>IH1002</t>
+          <t>IH2002</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2134,19 +2134,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>26 ord: - skapa lärandesituationer i ett urval av de behandlade rörelseaktiviteterna med…</t>
+          <t>26 ord: - självständigt identifiera, formulera och diskutera frågeställningar som berör …</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>IH1011</t>
+          <t>IH2005</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2156,29 +2156,29 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>26 ord: - självständigt identifiera, formulera och diskutera frågeställningar som berör …</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2005</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>IH1011</t>
+          <t>AMC243</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2188,51 +2188,51 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>27 ord: - skapa stimulerande lärandesituationer i olika pedagogiska sammanhang, som ocks…</t>
+          <t>26 ord: - självständigt söka, sammanställa och kritiskt granska evidensbaserad informati…</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC243</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>IH1012</t>
+          <t>AMC288</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>38 ord: - beskriva samband mellan fysisk aktivitet och hälsa vid en vald diagnos eller s…</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>IH1029</t>
+          <t>AMC288</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2242,294 +2242,294 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>29 ord: - skapa lärandesituationer i de kunskapsområden som explicit nämns i kursplanern…</t>
+          <t>27 ord: - jämföra och kritiskt diskutera olika mät- och utvärderingsmetoder för fysisk a…</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>IH1062</t>
+          <t>AMC288</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>16 lärandemål (maximum rekommenderat: 12 för 20 hp)</t>
+          <t>34 ord: - utifrån vetenskaplig evidens beskriva hur fysisk träning kan utformas beroende…</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1062</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>IH1095</t>
+          <t>AMC288</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 3 för 1.5 hp)</t>
+          <t>35 ord: - med stöd i vetenskaplig litteratur och egen erfarenhet reflektera kring den ro…</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1095</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>IH1096</t>
+          <t>AMC288</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 3 för 1.5 hp)</t>
+          <t>31 ord: - med stöd i relevant teoribildning identifiera hinder och underlättande faktore…</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1096</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>IH1097</t>
+          <t>AMC28N</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 3 för 1.5 hp)</t>
+          <t>26 ord: - presentera och argumentera för vald design hos ett tänkt forskningsprojekt ino…</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1097</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC28N</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>IH1098</t>
+          <t>AMC29F</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 3 för 1.5 hp)</t>
+          <t>26 ord: - självständigt identifiera och formulera problemställning och syfte för en vete…</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1098</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>IH1099</t>
+          <t>AMC29F</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 3 för 1.5 hp)</t>
+          <t>29 ord: - genomföra en vetenskaplig undersökning med relevant design, metod och analys s…</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1099</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>IH1100</t>
+          <t>AMC29F</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 3 för 1.5 hp)</t>
+          <t>32 ord: - analysera och värdera resultat från den vetenskapliga undersökningen i relatio…</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1100</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>IH1101</t>
+          <t>AMC29F</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 3 för 1.5 hp)</t>
+          <t>28 ord: - försvara eget självständigt arbete samt kritiskt granska och värdera annat exa…</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1101</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>IH1102</t>
+          <t>AMC29Y</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 3 för 1.5 hp)</t>
+          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1102</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>IH1113</t>
+          <t>AMC2A7</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>30 ord: - tillämpa grundläggande kunskaper inom ämnesområdet fysisk träning med specifik…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>IH1113</t>
+          <t>AMC2BG</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>26 ord: - praktisk genomföra och instruera övningar inriktade mot optimering av de fysis…</t>
+          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>IH1114</t>
+          <t>GMC32X</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2566,105 +2566,105 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>28 ord: - redogöra för de viktigaste mikro- och makronutrienterna och deras betydelse vi…</t>
+          <t>29 ord: - förskriva och informera om förbrukningsartiklar vid urindysfunktion, urinreten…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC32X</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>IH1114</t>
+          <t>GMC37E</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>36 ord: - visa förståelse för samt praktiskt tillämpa de centrala principerna för utform…</t>
+          <t>1 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>IH2001</t>
+          <t>GMC37E</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 5 för 30 hp)</t>
+          <t>30 ord: - Namnge, beskriva och förklara anatomi och funktion under människans livscykel …</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>IH2002</t>
+          <t>GMC37T</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 6 hp)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37T</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>IH2002</t>
+          <t>MC1072</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>26 ord: - självständigt identifiera, formulera och diskutera frågeställningar som berör …</t>
+          <t>26 ord: - söka relevant information utifrån fysiologiska frågeställningar relaterade til…</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1072</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>IH2005</t>
+          <t>MC1077</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2701,19 +2701,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>26 ord: - självständigt identifiera, formulera och diskutera frågeställningar som berör …</t>
+          <t>31 ord: - redogöra för hygieniska principer i vårdarbetet samt visa kännedom om de lagar…</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>AMC243</t>
+          <t>MC2017</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2723,24 +2723,24 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>26 ord: - självständigt söka, sammanställa och kritiskt granska evidensbaserad informati…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC243</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>AMC288</t>
+          <t>MC2017</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2755,19 +2755,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>38 ord: - beskriva samband mellan fysisk aktivitet och hälsa vid en vald diagnos eller s…</t>
+          <t>26 ord: -  redogöra för innehållet i de författningar som reglerar ansvarsfrågor och ans…</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>AMC288</t>
+          <t>MC2017</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2782,19 +2782,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>27 ord: - jämföra och kritiskt diskutera olika mät- och utvärderingsmetoder för fysisk a…</t>
+          <t>26 ord: -  redogöra för hur anpassningsstörningar kan manifesteras hos barn, ungdomar oc…</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>AMC288</t>
+          <t>MC3027</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2809,51 +2809,51 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>34 ord: - utifrån vetenskaplig evidens beskriva hur fysisk träning kan utformas beroende…</t>
+          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>AMC288</t>
+          <t>GNV367</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>35 ord: - med stöd i vetenskaplig litteratur och egen erfarenhet reflektera kring den ro…</t>
+          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>AMC288</t>
+          <t>GNV367</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>31 ord: - med stöd i relevant teoribildning identifiera hinder och underlättande faktore…</t>
+          <t>33 ord: - visa grundläggande kunskap om lärande för hållbar utveckling i grundskolans år…</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>AMC28N</t>
+          <t>GNV3GV</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>26 ord: - presentera och argumentera för vald design hos ett tänkt forskningsprojekt ino…</t>
+          <t>28 ord: - redogöra för grundläggande kunskaper i naturvetenskap, med särskilt fokus på e…</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC28N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>AMC29F</t>
+          <t>GNV3GV</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2917,78 +2917,78 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>26 ord: - självständigt identifiera och formulera problemställning och syfte för en vete…</t>
+          <t>34 ord: - reflektera över och problematisera skolans roll i arbetet med lärande för håll…</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>AMC29F</t>
+          <t>NV1035</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>29 ord: - genomföra en vetenskaplig undersökning med relevant design, metod och analys s…</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>AMC29F</t>
+          <t>NV1036</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>32 ord: - analysera och värdera resultat från den vetenskapliga undersökningen i relatio…</t>
+          <t>14 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>AMC29F</t>
+          <t>NV1036</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>28 ord: - försvara eget självständigt arbete samt kritiskt granska och värdera annat exa…</t>
+          <t>26 ord: - visa god förtrogenhet med och reflektera över kursplanerna inom SO, NO och tek…</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>AMC29Y</t>
+          <t>NV1036</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3025,51 +3025,51 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
+          <t>32 ord: - visa insikt om hur närmiljö, förstahandsupplevelser, estetik och digital tekni…</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>AMC2A7</t>
+          <t>NV3001</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>27 ord: - kritiskt diskutera begreppet hållbar utveckling och dess olika dimensioner, so…</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>AMC2BG</t>
+          <t>NV3001</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3079,186 +3079,186 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
+          <t>27 ord: - reflektera över vilken roll den högre utbildningen har för hållbar utveckling,…</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GMC32X</t>
+          <t>ASA24K</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>29 ord: - förskriva och informera om förbrukningsartiklar vid urindysfunktion, urinreten…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC32X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24K</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GMC37E</t>
+          <t>ASA24L</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24L</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GMC37E</t>
+          <t>ASA266</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>30 ord: - Namnge, beskriva och förklara anatomi och funktion under människans livscykel …</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA266</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GMC37T</t>
+          <t>ASA26U</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 6 hp)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA26U</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>MC1072</t>
+          <t>ASA27E</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>26 ord: - söka relevant information utifrån fysiologiska frågeställningar relaterade til…</t>
+          <t>9 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1072</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>MC1077</t>
+          <t>ASA293</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>31 ord: - redogöra för hygieniska principer i vårdarbetet samt visa kännedom om de lagar…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA293</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>MC2017</t>
+          <t>GSA24U</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3268,51 +3268,51 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>MC2017</t>
+          <t>GSA24V</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>26 ord: -  redogöra för innehållet i de författningar som reglerar ansvarsfrågor och ans…</t>
+          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>MC2017</t>
+          <t>GSA24V</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3322,24 +3322,24 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>26 ord: -  redogöra för hur anpassningsstörningar kan manifesteras hos barn, ungdomar oc…</t>
+          <t>27 ord: - redogöra för perspektiv på och metoder för socialt arbete med barn, familjer, …</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>MC3027</t>
+          <t>GSA24V</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3349,24 +3349,24 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
+          <t>27 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna rörande …</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GNV367</t>
+          <t>GSA27Y</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3376,51 +3376,51 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA27Y</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GNV367</t>
+          <t>GSA2AF</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>33 ord: - visa grundläggande kunskap om lärande för hållbar utveckling i grundskolans år…</t>
+          <t>14 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GNV3GV</t>
+          <t>GSA2AF</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3430,24 +3430,24 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>28 ord: - redogöra för grundläggande kunskaper i naturvetenskap, med särskilt fokus på e…</t>
+          <t>29 ord: - uppvisa kunskaper om en tolkningsram (till exempel teori, teoretiska begrepp, …</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GNV3GV</t>
+          <t>GSA2AF</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3457,51 +3457,51 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>34 ord: - reflektera över och problematisera skolans roll i arbetet med lärande för håll…</t>
+          <t>28 ord: - välja och beskriva en relevant tolkningsram (till exempel teori, teoretiska be…</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>NV1035</t>
+          <t>GSA2AF</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>32 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>NV1036</t>
+          <t>GSA2BV</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3511,24 +3511,24 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>NV1036</t>
+          <t>GSA2BV</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3538,24 +3538,24 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>26 ord: - visa god förtrogenhet med och reflektera över kursplanerna inom SO, NO och tek…</t>
+          <t>26 ord: - visa förmåga att under handledning planera, strukturera och självständigt geno…</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>NV1036</t>
+          <t>GSA2BV</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3565,24 +3565,24 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>32 ord: - visa insikt om hur närmiljö, förstahandsupplevelser, estetik och digital tekni…</t>
+          <t>28 ord: - visa förmåga och färdigheter att identifiera, definiera, analysera och dokumen…</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>NV3001</t>
+          <t>GSA2BV</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3592,46 +3592,46 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>27 ord: - kritiskt diskutera begreppet hållbar utveckling och dess olika dimensioner, so…</t>
+          <t>28 ord: - kritiskt reflektera över den egna förmågan och den personliga och professionel…</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>NV3001</t>
+          <t>GSA2DW</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>27 ord: - reflektera över vilken roll den högre utbildningen har för hållbar utveckling,…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>ASA24K</t>
+          <t>GSA2DW</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3641,24 +3641,24 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>29 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna avseende…</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>ASA24L</t>
+          <t>GSA2E3</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3678,14 +3678,14 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E3</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>ASA266</t>
+          <t>GSA2E4</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3700,19 +3700,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>ASA26U</t>
+          <t>GSA2E4</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3722,24 +3722,24 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>29 ord: - visa kunskap om och förståelse för hur familje- och samhällsförhållanden påver…</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA26U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>ASA27E</t>
+          <t>GSA2E5</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3754,19 +3754,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>ASA293</t>
+          <t>GSA2NA</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3786,14 +3786,14 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA293</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NA</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GSA24U</t>
+          <t>GSA2NC</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3808,19 +3808,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>14 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GSA24V</t>
+          <t>GSA2RE</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3835,19 +3835,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2RE</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GSA24V</t>
+          <t>GSA2SD</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3857,24 +3857,24 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för perspektiv på och metoder för socialt arbete med barn, familjer, …</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GSA24V</t>
+          <t>GSA2SE</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3884,24 +3884,24 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna rörande …</t>
+          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GSA27Y</t>
+          <t>GSA2XN</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3916,19 +3916,19 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA27Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2XN</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>GSA32Y</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3943,19 +3943,19 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>GSA352</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3965,24 +3965,24 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>29 ord: - uppvisa kunskaper om en tolkningsram (till exempel teori, teoretiska begrepp, …</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA352</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>GSA3DM</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3992,24 +3992,24 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>28 ord: - välja och beskriva en relevant tolkningsram (till exempel teori, teoretiska be…</t>
+          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>GSA3DM</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4024,19 +4024,19 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>32 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
+          <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GSA2BV</t>
+          <t>GSA3DM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4046,24 +4046,24 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GSA2BV</t>
+          <t>GSA3DN</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4073,24 +4073,24 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>26 ord: - visa förmåga att under handledning planera, strukturera och självständigt geno…</t>
+          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GSA2BV</t>
+          <t>GSA3DN</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4105,19 +4105,19 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga och färdigheter att identifiera, definiera, analysera och dokumen…</t>
+          <t>29 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna avseende…</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GSA2BV</t>
+          <t>GSA3DP</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4127,24 +4127,24 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>28 ord: - kritiskt reflektera över den egna förmågan och den personliga och professionel…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DP</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GSA2DW</t>
+          <t>GSA3DQ</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4159,19 +4159,19 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GSA2DW</t>
+          <t>GSA3DQ</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4186,19 +4186,19 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna avseende…</t>
+          <t>27 ord: - redogöra för perspektiv på och metoder för socialt arbete med barn, familjer, …</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GSA2E3</t>
+          <t>GSA3DQ</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4208,24 +4208,24 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>27 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna rörande …</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GSA2E4</t>
+          <t>GSA3DR</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4245,14 +4245,14 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DR</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GSA2E4</t>
+          <t>GSA3DS</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4262,24 +4262,24 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskap om och förståelse för hur familje- och samhällsförhållanden påver…</t>
+          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>GSA2E5</t>
+          <t>GSA3FK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4299,14 +4299,14 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GSA2NA</t>
+          <t>GSA3FK</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4316,24 +4316,24 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>34 ord: - utifrån ett brukarperspektiv genomföra olika typer av utredningar inom socialt…</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>GSA2NC</t>
+          <t>GSA3FL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4348,19 +4348,19 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FL</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GSA2RE</t>
+          <t>GSA3HA</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4375,19 +4375,19 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2RE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3HA</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GSA2SD</t>
+          <t>SA1045</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4402,19 +4402,19 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1045</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>GSA2SE</t>
+          <t>SA1048</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4429,19 +4429,19 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GSA2XN</t>
+          <t>SA1048</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2XN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GSA32Y</t>
+          <t>SA1048</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4478,24 +4478,24 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GSA352</t>
+          <t>SA2020</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4510,19 +4510,19 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>26 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA352</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GSA3DM</t>
+          <t>SA2020</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4532,24 +4532,24 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>32 ord: - uppvisa kunskaper som utgör innehåll i en tolkningsram (till exempel teori, te…</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>GSA3DM</t>
+          <t>SA2020</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4564,19 +4564,19 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
+          <t>32 ord: - analysera resultat från ett vetenskapligt arbete på sådant sätt att tolkningsr…</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>GSA3DM</t>
+          <t>SA2020</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4591,19 +4591,19 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
+          <t>32 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>GSA3DN</t>
+          <t>SA3008</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4618,19 +4618,19 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>GSA3DN</t>
+          <t>SA3008</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4645,78 +4645,78 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna avseende…</t>
+          <t>30 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>GSA3DP</t>
+          <t>ASR24V</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>GSA3DQ</t>
+          <t>ASR24V</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>27 ord: - ur ett rättighetsperspektiv analysera och diskutera hur sociala, ekonomiska, m…</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>GSA3DQ</t>
+          <t>ASR25P</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4726,105 +4726,105 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för perspektiv på och metoder för socialt arbete med barn, familjer, …</t>
+          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>GSA3DQ</t>
+          <t>ASR26N</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna rörande …</t>
+          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>GSA3DR</t>
+          <t>ASR26N</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>30 ord: - diskutera vikten av samarbete och lagarbete inom och mellan utbildningsinstitu…</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>GSA3DS</t>
+          <t>ASR284</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>GSA3FK</t>
+          <t>ASR285</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4834,24 +4834,24 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>GSA3FK</t>
+          <t>ASR285</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4861,132 +4861,132 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>34 ord: - utifrån ett brukarperspektiv genomföra olika typer av utredningar inom socialt…</t>
+          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>GSA3FL</t>
+          <t>ASR285</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>GSA3HA</t>
+          <t>ASR29S</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>27 ord: - analysera och värdera resultat i relation till tidigare forskning, värdera den…</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3HA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>SA1045</t>
+          <t>ASR29T</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>26 ord: - problematisera och reflektera över kvinnans, barnets och närståendes roller oc…</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>SA1048</t>
+          <t>ASR29T</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>SA1048</t>
+          <t>ASR29U</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4996,78 +4996,78 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
+          <t>26 ord: - i simulerad miljö utföra undersökningar och behandlingar vid komplicerad gravi…</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>SA1048</t>
+          <t>ASR29V</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>SA2020</t>
+          <t>ASR29V</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>26 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>SA2020</t>
+          <t>ASR29V</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5077,24 +5077,24 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>32 ord: - uppvisa kunskaper som utgör innehåll i en tolkningsram (till exempel teori, te…</t>
+          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>SA2020</t>
+          <t>ASR29W</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5104,24 +5104,24 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>32 ord: - analysera resultat från ett vetenskapligt arbete på sådant sätt att tolkningsr…</t>
+          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29W</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>SA2020</t>
+          <t>ASR2AD</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5131,24 +5131,24 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>32 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
+          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av k…</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2AD</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>SA3008</t>
+          <t>ASR2BM</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5158,24 +5158,24 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2BM</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>SA3008</t>
+          <t>ASR2CE</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5185,19 +5185,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>30 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
+          <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CE</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>ASR24V</t>
+          <t>GSR38B</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5212,19 +5212,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
+          <t>33 ord: - uppvisa kunskap, förståelse och reflekterande färdigheter om sexuell och repro…</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>ASR24V</t>
+          <t>SR3001</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5239,19 +5239,19 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>27 ord: - ur ett rättighetsperspektiv analysera och diskutera hur sociala, ekonomiska, m…</t>
+          <t>30 ord: - värdera olika strategier för ledarskap och interventioner som har potential at…</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>ASR25P</t>
+          <t>SR3002</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5266,19 +5266,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
+          <t>27 ord: - analysera och kritiskt värdera styrkor och svagheter i forskningsprocessens ol…</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>ASR26N</t>
+          <t>SR3007</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5293,19 +5293,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>ASR26N</t>
+          <t>SR3008</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5315,24 +5315,24 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>30 ord: - diskutera vikten av samarbete och lagarbete inom och mellan utbildningsinstitu…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>ASR284</t>
+          <t>SR3009</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5347,19 +5347,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
+          <t>26 ord: - analysera betydelsen av hälsofrämjande arbete under den reproduktiva livscykel…</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>ASR285</t>
+          <t>SR3009</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5369,24 +5369,24 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
+          <t>29 ord: - identifiera problemområden och formulera relevanta frågeställningar som rör gr…</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>ASR285</t>
+          <t>SR3009</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5401,19 +5401,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
+          <t>27 ord: - redogöra för benigna och maligna gynekologiska förändringar, värdera hälsotill…</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>ASR285</t>
+          <t>SR3010</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5428,19 +5428,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
+          <t>27 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av g…</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>ASR29S</t>
+          <t>SR3011</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5455,19 +5455,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>27 ord: - analysera och värdera resultat i relation till tidigare forskning, värdera den…</t>
+          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>ASR29T</t>
+          <t>SR3012</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5477,24 +5477,24 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>26 ord: - problematisera och reflektera över kvinnans, barnets och närståendes roller oc…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>ASR29T</t>
+          <t>SR3012</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5509,19 +5509,19 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
+          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>ASR29U</t>
+          <t>SR3012</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5536,19 +5536,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>26 ord: - i simulerad miljö utföra undersökningar och behandlingar vid komplicerad gravi…</t>
+          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>ASR29V</t>
+          <t>SR3014</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5563,19 +5563,19 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 10 för 13.5 hp)</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>ASR29V</t>
+          <t>SR3014</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5590,19 +5590,19 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
+          <t>30 ord: - med ett professionellt förhållningssätt informera, ge stöd och trygghet i dial…</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>ASR29V</t>
+          <t>SR3015</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5612,24 +5612,24 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
+          <t>14 lärandemål (maximum rekommenderat: 10 för 13.5 hp)</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>ASR29W</t>
+          <t>SR3015</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5644,19 +5644,19 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
+          <t>35 ord: - självständigt handlägga preventivmedelsrådgivning och informera om lämpliga an…</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>ASR2AD</t>
+          <t>SR3015</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5671,51 +5671,51 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av k…</t>
+          <t>26 ord: - kritiskt analysera, värdera, föreslå och följa upp vårdnadsinsatser och behand…</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2AD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>ASR2BM</t>
+          <t>AVV2A6</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>26 ord: - kritiskt reflektera över hur kvalitets- och säkerhetsledning organiseras och r…</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2BM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV2A6</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>ASR2CE</t>
+          <t>VV2002</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -5725,78 +5725,78 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
+          <t>29 ord: - redogöra för gällande regelverk för olika professioner inom kommunal äldreomso…</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>GSR38B</t>
+          <t>VV3006</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>33 ord: - uppvisa kunskap, förståelse och reflekterande färdigheter om sexuell och repro…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>SR3001</t>
+          <t>VV3011</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>30 ord: - värdera olika strategier för ledarskap och interventioner som har potential at…</t>
+          <t>19 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>SR3002</t>
+          <t>VV3012</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -5806,78 +5806,78 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>27 ord: - analysera och kritiskt värdera styrkor och svagheter i forskningsprocessens ol…</t>
+          <t>29 ord: - tillämpa adekvat vetenskaplig design och metod i datainsamling och analys samt…</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>SR3007</t>
+          <t>VV3012</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>29 ord: - analysera och värdera resultat i relation till tidigare forskning samt den kli…</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>SR3008</t>
+          <t>VV3017</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>29 ord: - tillämpa adekvat vetenskaplig design och metod i datainsamling och analys samt…</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>SR3009</t>
+          <t>VV3017</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -5887,24 +5887,24 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>26 ord: - analysera betydelsen av hälsofrämjande arbete under den reproduktiva livscykel…</t>
+          <t>29 ord: - analysera och värdera resultat i relation till tidigare forskning samt den kli…</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>SR3009</t>
+          <t>VV3017</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -5914,557 +5914,17 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>29 ord: - identifiera problemområden och formulera relevanta frågeställningar som rör gr…</t>
+          <t>26 ord: - göra relevanta bedömningar på mikro-, meso- och makronivå med hänsyn till samh…</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
-        <is>
-          <t>SR3009</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>27 ord: - redogöra för benigna och maligna gynekologiska förändringar, värdera hälsotill…</t>
-        </is>
-      </c>
-      <c r="E204" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
-        <is>
-          <t>SR3010</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>27 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av g…</t>
-        </is>
-      </c>
-      <c r="E205" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
-        <is>
-          <t>SR3011</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
-        </is>
-      </c>
-      <c r="E206" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr">
-        <is>
-          <t>SR3012</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
-        </is>
-      </c>
-      <c r="E207" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
-        <is>
-          <t>SR3012</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
-        </is>
-      </c>
-      <c r="E208" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
-        <is>
-          <t>SR3012</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
-        </is>
-      </c>
-      <c r="E209" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="2" t="inlineStr">
-        <is>
-          <t>SR3014</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>11 lärandemål (maximum rekommenderat: 10 för 13.5 hp)</t>
-        </is>
-      </c>
-      <c r="E210" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
-        <is>
-          <t>SR3014</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>30 ord: - med ett professionellt förhållningssätt informera, ge stöd och trygghet i dial…</t>
-        </is>
-      </c>
-      <c r="E211" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
-        <is>
-          <t>SR3015</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>14 lärandemål (maximum rekommenderat: 10 för 13.5 hp)</t>
-        </is>
-      </c>
-      <c r="E212" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="2" t="inlineStr">
-        <is>
-          <t>SR3015</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>35 ord: - självständigt handlägga preventivmedelsrådgivning och informera om lämpliga an…</t>
-        </is>
-      </c>
-      <c r="E213" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="2" t="inlineStr">
-        <is>
-          <t>SR3015</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>26 ord: - kritiskt analysera, värdera, föreslå och följa upp vårdnadsinsatser och behand…</t>
-        </is>
-      </c>
-      <c r="E214" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
-        <is>
-          <t>AVV2A6</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>26 ord: - kritiskt reflektera över hur kvalitets- och säkerhetsledning organiseras och r…</t>
-        </is>
-      </c>
-      <c r="E215" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV2A6</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
-        <is>
-          <t>VV2002</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>29 ord: - redogöra för gällande regelverk för olika professioner inom kommunal äldreomso…</t>
-        </is>
-      </c>
-      <c r="E216" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr">
-        <is>
-          <t>VV3006</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
-        </is>
-      </c>
-      <c r="E217" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
-        <is>
-          <t>VV3011</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>19 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
-        </is>
-      </c>
-      <c r="E218" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
-        <is>
-          <t>VV3012</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>29 ord: - tillämpa adekvat vetenskaplig design och metod i datainsamling och analys samt…</t>
-        </is>
-      </c>
-      <c r="E219" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
-        <is>
-          <t>VV3012</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>29 ord: - analysera och värdera resultat i relation till tidigare forskning samt den kli…</t>
-        </is>
-      </c>
-      <c r="E220" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
-        <is>
-          <t>VV3017</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>29 ord: - tillämpa adekvat vetenskaplig design och metod i datainsamling och analys samt…</t>
-        </is>
-      </c>
-      <c r="E221" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr">
-        <is>
-          <t>VV3017</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>29 ord: - analysera och värdera resultat i relation till tidigare forskning samt den kli…</t>
-        </is>
-      </c>
-      <c r="E222" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
-        <is>
-          <t>VV3017</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>26 ord: - göra relevanta bedömningar på mikro-, meso- och makronivå med hänsyn till samh…</t>
-        </is>
-      </c>
-      <c r="E223" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E223"/>
+  <autoFilter ref="A1:E203"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -6870,46 +6330,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId402"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A203" r:id="rId403"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A204" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A205" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A206" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A207" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A208" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A209" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A210" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A211" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A212" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E212" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A213" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E213" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A214" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E214" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A215" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E215" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A216" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E216" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A217" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E217" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A218" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E218" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A219" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A220" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A221" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A222" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A223" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId444"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Omfång på lärandemål.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$198</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E203"/>
+  <dimension ref="A1:E198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2335,7 +2335,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>AMC28N</t>
+          <t>AMC29Y</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2350,19 +2350,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>26 ord: - presentera och argumentera för vald design hos ett tänkt forskningsprojekt ino…</t>
+          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC28N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>AMC29F</t>
+          <t>AMC2A7</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2372,24 +2372,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>26 ord: - självständigt identifiera och formulera problemställning och syfte för en vete…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>AMC29F</t>
+          <t>AMC2BG</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2404,19 +2404,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>29 ord: - genomföra en vetenskaplig undersökning med relevant design, metod och analys s…</t>
+          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>AMC29F</t>
+          <t>GMC32X</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2431,19 +2431,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>32 ord: - analysera och värdera resultat från den vetenskapliga undersökningen i relatio…</t>
+          <t>29 ord: - förskriva och informera om förbrukningsartiklar vid urindysfunktion, urinreten…</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC32X</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>AMC29F</t>
+          <t>GMC37E</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2453,24 +2453,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>28 ord: - försvara eget självständigt arbete samt kritiskt granska och värdera annat exa…</t>
+          <t>1 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>AMC29Y</t>
+          <t>GMC37E</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2485,19 +2485,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
+          <t>30 ord: - Namnge, beskriva och förklara anatomi och funktion under människans livscykel …</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>AMC2A7</t>
+          <t>GMC37T</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2507,24 +2507,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 6 hp)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37T</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>AMC2BG</t>
+          <t>MC1072</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2539,19 +2539,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
+          <t>26 ord: - söka relevant information utifrån fysiologiska frågeställningar relaterade til…</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1072</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GMC32X</t>
+          <t>MC1077</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2566,19 +2566,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>29 ord: - förskriva och informera om förbrukningsartiklar vid urindysfunktion, urinreten…</t>
+          <t>31 ord: - redogöra för hygieniska principer i vårdarbetet samt visa kännedom om de lagar…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC32X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GMC37E</t>
+          <t>MC2017</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2588,24 +2588,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GMC37E</t>
+          <t>MC2017</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2620,19 +2620,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>30 ord: - Namnge, beskriva och förklara anatomi och funktion under människans livscykel …</t>
+          <t>26 ord: -  redogöra för innehållet i de författningar som reglerar ansvarsfrågor och ans…</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GMC37T</t>
+          <t>MC2017</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2642,24 +2642,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 6 hp)</t>
+          <t>26 ord: -  redogöra för hur anpassningsstörningar kan manifesteras hos barn, ungdomar oc…</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>MC1072</t>
+          <t>MC3027</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2674,78 +2674,78 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>26 ord: - söka relevant information utifrån fysiologiska frågeställningar relaterade til…</t>
+          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1072</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>MC1077</t>
+          <t>GNV367</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>31 ord: - redogöra för hygieniska principer i vårdarbetet samt visa kännedom om de lagar…</t>
+          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>MC2017</t>
+          <t>GNV367</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>33 ord: - visa grundläggande kunskap om lärande för hållbar utveckling i grundskolans år…</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>MC2017</t>
+          <t>GNV3GV</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2755,24 +2755,24 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>26 ord: -  redogöra för innehållet i de författningar som reglerar ansvarsfrågor och ans…</t>
+          <t>28 ord: - redogöra för grundläggande kunskaper i naturvetenskap, med särskilt fokus på e…</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>MC2017</t>
+          <t>GNV3GV</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2782,46 +2782,46 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>26 ord: -  redogöra för hur anpassningsstörningar kan manifesteras hos barn, ungdomar oc…</t>
+          <t>34 ord: - reflektera över och problematisera skolans roll i arbetet med lärande för håll…</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>MC3027</t>
+          <t>NV1035</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GNV367</t>
+          <t>NV1036</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2836,19 +2836,19 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>14 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GNV367</t>
+          <t>NV1036</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2863,19 +2863,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>33 ord: - visa grundläggande kunskap om lärande för hållbar utveckling i grundskolans år…</t>
+          <t>26 ord: - visa god förtrogenhet med och reflektera över kursplanerna inom SO, NO och tek…</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GNV3GV</t>
+          <t>NV1036</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2890,19 +2890,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>28 ord: - redogöra för grundläggande kunskaper i naturvetenskap, med särskilt fokus på e…</t>
+          <t>32 ord: - visa insikt om hur närmiljö, förstahandsupplevelser, estetik och digital tekni…</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GNV3GV</t>
+          <t>NV3001</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2917,19 +2917,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>34 ord: - reflektera över och problematisera skolans roll i arbetet med lärande för håll…</t>
+          <t>27 ord: - kritiskt diskutera begreppet hållbar utveckling och dess olika dimensioner, so…</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>NV1035</t>
+          <t>NV3001</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2939,29 +2939,29 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>27 ord: - reflektera över vilken roll den högre utbildningen har för hållbar utveckling,…</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>NV1036</t>
+          <t>ASA24K</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2971,127 +2971,127 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24K</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>NV1036</t>
+          <t>ASA24L</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>26 ord: - visa god förtrogenhet med och reflektera över kursplanerna inom SO, NO och tek…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24L</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>NV1036</t>
+          <t>ASA266</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>32 ord: - visa insikt om hur närmiljö, förstahandsupplevelser, estetik och digital tekni…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA266</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>NV3001</t>
+          <t>ASA26U</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>27 ord: - kritiskt diskutera begreppet hållbar utveckling och dess olika dimensioner, so…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA26U</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>NV3001</t>
+          <t>ASA27E</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>27 ord: - reflektera över vilken roll den högre utbildningen har för hållbar utveckling,…</t>
+          <t>9 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>ASA24K</t>
+          <t>ASA293</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3106,19 +3106,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA293</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>ASA24L</t>
+          <t>GSA24U</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3133,19 +3133,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>ASA266</t>
+          <t>GSA24V</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3160,19 +3160,19 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>ASA26U</t>
+          <t>GSA24V</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3182,24 +3182,24 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>27 ord: - redogöra för perspektiv på och metoder för socialt arbete med barn, familjer, …</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA26U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>ASA27E</t>
+          <t>GSA24V</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3209,24 +3209,24 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
+          <t>27 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna rörande …</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>ASA293</t>
+          <t>GSA27Y</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3241,19 +3241,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA293</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA27Y</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GSA24U</t>
+          <t>GSA2AF</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3268,19 +3268,19 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>14 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GSA24V</t>
+          <t>GSA2AF</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3290,24 +3290,24 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>29 ord: - uppvisa kunskaper om en tolkningsram (till exempel teori, teoretiska begrepp, …</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GSA24V</t>
+          <t>GSA2AF</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3322,19 +3322,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för perspektiv på och metoder för socialt arbete med barn, familjer, …</t>
+          <t>28 ord: - välja och beskriva en relevant tolkningsram (till exempel teori, teoretiska be…</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GSA24V</t>
+          <t>GSA2AF</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3349,19 +3349,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna rörande …</t>
+          <t>32 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GSA27Y</t>
+          <t>GSA2BV</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3376,19 +3376,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA27Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>GSA2BV</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3398,24 +3398,24 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>26 ord: - visa förmåga att under handledning planera, strukturera och självständigt geno…</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>GSA2BV</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3430,19 +3430,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>29 ord: - uppvisa kunskaper om en tolkningsram (till exempel teori, teoretiska begrepp, …</t>
+          <t>28 ord: - visa förmåga och färdigheter att identifiera, definiera, analysera och dokumen…</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>GSA2BV</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3457,19 +3457,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>28 ord: - välja och beskriva en relevant tolkningsram (till exempel teori, teoretiska be…</t>
+          <t>28 ord: - kritiskt reflektera över den egna förmågan och den personliga och professionel…</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>GSA2DW</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3479,24 +3479,24 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>32 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GSA2BV</t>
+          <t>GSA2DW</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>29 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna avseende…</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GSA2BV</t>
+          <t>GSA2E3</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3533,24 +3533,24 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>26 ord: - visa förmåga att under handledning planera, strukturera och självständigt geno…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E3</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GSA2BV</t>
+          <t>GSA2E4</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3560,24 +3560,24 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga och färdigheter att identifiera, definiera, analysera och dokumen…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GSA2BV</t>
+          <t>GSA2E4</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3592,19 +3592,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>28 ord: - kritiskt reflektera över den egna förmågan och den personliga och professionel…</t>
+          <t>29 ord: - visa kunskap om och förståelse för hur familje- och samhällsförhållanden påver…</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GSA2DW</t>
+          <t>GSA2E5</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3619,19 +3619,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GSA2DW</t>
+          <t>GSA2NA</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3641,24 +3641,24 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna avseende…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NA</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GSA2E3</t>
+          <t>GSA2NC</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3673,19 +3673,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>14 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GSA2E4</t>
+          <t>GSA2RE</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3700,19 +3700,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2RE</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GSA2E4</t>
+          <t>GSA2SD</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3722,24 +3722,24 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskap om och förståelse för hur familje- och samhällsförhållanden påver…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GSA2E5</t>
+          <t>GSA2SE</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3754,19 +3754,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GSA2NA</t>
+          <t>GSA2XN</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3781,19 +3781,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2XN</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GSA2NC</t>
+          <t>GSA32Y</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3808,19 +3808,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GSA2RE</t>
+          <t>GSA352</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3835,19 +3835,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2RE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA352</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GSA2SD</t>
+          <t>GSA3DM</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3862,19 +3862,19 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GSA2SE</t>
+          <t>GSA3DM</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3884,24 +3884,24 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GSA2XN</t>
+          <t>GSA3DM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3911,24 +3911,24 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2XN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GSA32Y</t>
+          <t>GSA3DN</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3943,19 +3943,19 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GSA352</t>
+          <t>GSA3DN</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3965,24 +3965,24 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>29 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna avseende…</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA352</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GSA3DM</t>
+          <t>GSA3DP</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3997,19 +3997,19 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DP</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>GSA3DM</t>
+          <t>GSA3DQ</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4019,24 +4019,24 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
+          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GSA3DM</t>
+          <t>GSA3DQ</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4051,19 +4051,19 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
+          <t>27 ord: - redogöra för perspektiv på och metoder för socialt arbete med barn, familjer, …</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GSA3DN</t>
+          <t>GSA3DQ</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4073,24 +4073,24 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>27 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna rörande …</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GSA3DN</t>
+          <t>GSA3DR</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4100,24 +4100,24 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna avseende…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DR</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GSA3DP</t>
+          <t>GSA3DS</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4132,19 +4132,19 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GSA3DQ</t>
+          <t>GSA3FK</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4159,19 +4159,19 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GSA3DQ</t>
+          <t>GSA3FK</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4186,19 +4186,19 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för perspektiv på och metoder för socialt arbete med barn, familjer, …</t>
+          <t>34 ord: - utifrån ett brukarperspektiv genomföra olika typer av utredningar inom socialt…</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GSA3DQ</t>
+          <t>GSA3FL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4208,24 +4208,24 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna rörande …</t>
+          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FL</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GSA3DR</t>
+          <t>GSA3HA</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4240,19 +4240,19 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3HA</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GSA3DS</t>
+          <t>SA1045</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4267,19 +4267,19 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1045</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>GSA3FK</t>
+          <t>SA1048</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4294,19 +4294,19 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GSA3FK</t>
+          <t>SA1048</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4321,19 +4321,19 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>34 ord: - utifrån ett brukarperspektiv genomföra olika typer av utredningar inom socialt…</t>
+          <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>GSA3FL</t>
+          <t>SA1048</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4343,24 +4343,24 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GSA3HA</t>
+          <t>SA2020</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4375,19 +4375,19 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>26 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3HA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>SA1045</t>
+          <t>SA2020</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4397,24 +4397,24 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>32 ord: - uppvisa kunskaper som utgör innehåll i en tolkningsram (till exempel teori, te…</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>SA1048</t>
+          <t>SA2020</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4424,24 +4424,24 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>32 ord: - analysera resultat från ett vetenskapligt arbete på sådant sätt att tolkningsr…</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>SA1048</t>
+          <t>SA2020</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4456,19 +4456,19 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
+          <t>32 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>SA1048</t>
+          <t>SA3008</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4478,24 +4478,24 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>SA2020</t>
+          <t>SA3008</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4505,29 +4505,29 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>26 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>30 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>SA2020</t>
+          <t>ASR24V</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4537,24 +4537,24 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>32 ord: - uppvisa kunskaper som utgör innehåll i en tolkningsram (till exempel teori, te…</t>
+          <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>SA2020</t>
+          <t>ASR24V</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4564,24 +4564,24 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>32 ord: - analysera resultat från ett vetenskapligt arbete på sådant sätt att tolkningsr…</t>
+          <t>27 ord: - ur ett rättighetsperspektiv analysera och diskutera hur sociala, ekonomiska, m…</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>SA2020</t>
+          <t>ASR25P</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>32 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
+          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>SA3008</t>
+          <t>ASR26N</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4618,24 +4618,24 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>SA3008</t>
+          <t>ASR26N</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4645,19 +4645,19 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>30 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
+          <t>30 ord: - diskutera vikten av samarbete och lagarbete inom och mellan utbildningsinstitu…</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>ASR24V</t>
+          <t>ASR284</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4672,19 +4672,19 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
+          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>ASR24V</t>
+          <t>ASR285</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4694,24 +4694,24 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>27 ord: - ur ett rättighetsperspektiv analysera och diskutera hur sociala, ekonomiska, m…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>ASR25P</t>
+          <t>ASR285</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4726,19 +4726,19 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
+          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>ASR26N</t>
+          <t>ASR285</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4748,24 +4748,24 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>ASR26N</t>
+          <t>ASR29S</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4780,19 +4780,19 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>30 ord: - diskutera vikten av samarbete och lagarbete inom och mellan utbildningsinstitu…</t>
+          <t>27 ord: - analysera och värdera resultat i relation till tidigare forskning, värdera den…</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>ASR284</t>
+          <t>ASR29T</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4807,19 +4807,19 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
+          <t>26 ord: - problematisera och reflektera över kvinnans, barnets och närståendes roller oc…</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>ASR285</t>
+          <t>ASR29T</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4829,24 +4829,24 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
+          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>ASR285</t>
+          <t>ASR29U</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4861,19 +4861,19 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
+          <t>26 ord: - i simulerad miljö utföra undersökningar och behandlingar vid komplicerad gravi…</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>ASR285</t>
+          <t>ASR29V</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4883,24 +4883,24 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>ASR29S</t>
+          <t>ASR29V</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4915,19 +4915,19 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>27 ord: - analysera och värdera resultat i relation till tidigare forskning, värdera den…</t>
+          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>ASR29T</t>
+          <t>ASR29V</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4942,19 +4942,19 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>26 ord: - problematisera och reflektera över kvinnans, barnets och närståendes roller oc…</t>
+          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>ASR29T</t>
+          <t>ASR29W</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4969,19 +4969,19 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
+          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29W</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>ASR29U</t>
+          <t>ASR2AD</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4996,19 +4996,19 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>26 ord: - i simulerad miljö utföra undersökningar och behandlingar vid komplicerad gravi…</t>
+          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av k…</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2AD</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>ASR29V</t>
+          <t>ASR2BM</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5023,19 +5023,19 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2BM</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>ASR29V</t>
+          <t>ASR2CE</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5050,19 +5050,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
+          <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CE</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>ASR29V</t>
+          <t>GSR38B</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5077,19 +5077,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
+          <t>33 ord: - uppvisa kunskap, förståelse och reflekterande färdigheter om sexuell och repro…</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>ASR29W</t>
+          <t>SR3001</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5104,19 +5104,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
+          <t>30 ord: - värdera olika strategier för ledarskap och interventioner som har potential at…</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>ASR2AD</t>
+          <t>SR3002</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5131,19 +5131,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av k…</t>
+          <t>27 ord: - analysera och kritiskt värdera styrkor och svagheter i forskningsprocessens ol…</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2AD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>ASR2BM</t>
+          <t>SR3007</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5158,19 +5158,19 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2BM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>ASR2CE</t>
+          <t>SR3008</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5180,24 +5180,24 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>GSR38B</t>
+          <t>SR3009</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5212,19 +5212,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>33 ord: - uppvisa kunskap, förståelse och reflekterande färdigheter om sexuell och repro…</t>
+          <t>26 ord: - analysera betydelsen av hälsofrämjande arbete under den reproduktiva livscykel…</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>SR3001</t>
+          <t>SR3009</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5239,19 +5239,19 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>30 ord: - värdera olika strategier för ledarskap och interventioner som har potential at…</t>
+          <t>29 ord: - identifiera problemområden och formulera relevanta frågeställningar som rör gr…</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>SR3002</t>
+          <t>SR3009</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5266,19 +5266,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>27 ord: - analysera och kritiskt värdera styrkor och svagheter i forskningsprocessens ol…</t>
+          <t>27 ord: - redogöra för benigna och maligna gynekologiska förändringar, värdera hälsotill…</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>SR3007</t>
+          <t>SR3010</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5288,24 +5288,24 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>27 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av g…</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>SR3008</t>
+          <t>SR3011</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5315,24 +5315,24 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>SR3009</t>
+          <t>SR3012</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5342,24 +5342,24 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>26 ord: - analysera betydelsen av hälsofrämjande arbete under den reproduktiva livscykel…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>SR3009</t>
+          <t>SR3012</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5374,19 +5374,19 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>29 ord: - identifiera problemområden och formulera relevanta frågeställningar som rör gr…</t>
+          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>SR3009</t>
+          <t>SR3012</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5401,19 +5401,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för benigna och maligna gynekologiska förändringar, värdera hälsotill…</t>
+          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>SR3010</t>
+          <t>SR3014</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5423,24 +5423,24 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>27 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av g…</t>
+          <t>11 lärandemål (maximum rekommenderat: 10 för 13.5 hp)</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>SR3011</t>
+          <t>SR3014</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5455,19 +5455,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
+          <t>30 ord: - med ett professionellt förhållningssätt informera, ge stöd och trygghet i dial…</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>SR3012</t>
+          <t>SR3015</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5482,19 +5482,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
+          <t>14 lärandemål (maximum rekommenderat: 10 för 13.5 hp)</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>SR3012</t>
+          <t>SR3015</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5509,19 +5509,19 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
+          <t>35 ord: - självständigt handlägga preventivmedelsrådgivning och informera om lämpliga an…</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>SR3012</t>
+          <t>SR3015</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5536,51 +5536,51 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
+          <t>26 ord: - kritiskt analysera, värdera, föreslå och följa upp vårdnadsinsatser och behand…</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>SR3014</t>
+          <t>AVV2A6</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 10 för 13.5 hp)</t>
+          <t>26 ord: - kritiskt reflektera över hur kvalitets- och säkerhetsledning organiseras och r…</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV2A6</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>SR3014</t>
+          <t>VV2002</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5590,24 +5590,24 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>30 ord: - med ett professionellt förhållningssätt informera, ge stöd och trygghet i dial…</t>
+          <t>29 ord: - redogöra för gällande regelverk för olika professioner inom kommunal äldreomso…</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>SR3015</t>
+          <t>VV3006</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5617,51 +5617,51 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 10 för 13.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>SR3015</t>
+          <t>VV3011</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>35 ord: - självständigt handlägga preventivmedelsrådgivning och informera om lämpliga an…</t>
+          <t>19 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>SR3015</t>
+          <t>VV3012</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5671,19 +5671,19 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>26 ord: - kritiskt analysera, värdera, föreslå och följa upp vårdnadsinsatser och behand…</t>
+          <t>29 ord: - tillämpa adekvat vetenskaplig design och metod i datainsamling och analys samt…</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>AVV2A6</t>
+          <t>VV3012</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5698,19 +5698,19 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>26 ord: - kritiskt reflektera över hur kvalitets- och säkerhetsledning organiseras och r…</t>
+          <t>29 ord: - analysera och värdera resultat i relation till tidigare forskning samt den kli…</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV2A6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>VV2002</t>
+          <t>VV3017</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5725,19 +5725,19 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för gällande regelverk för olika professioner inom kommunal äldreomso…</t>
+          <t>29 ord: - tillämpa adekvat vetenskaplig design och metod i datainsamling och analys samt…</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>VV3006</t>
+          <t>VV3017</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5747,24 +5747,24 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>29 ord: - analysera och värdera resultat i relation till tidigare forskning samt den kli…</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>VV3011</t>
+          <t>VV3017</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5774,157 +5774,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>19 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>26 ord: - göra relevanta bedömningar på mikro-, meso- och makronivå med hänsyn till samh…</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
-        <is>
-          <t>VV3012</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>29 ord: - tillämpa adekvat vetenskaplig design och metod i datainsamling och analys samt…</t>
-        </is>
-      </c>
-      <c r="E199" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
-        <is>
-          <t>VV3012</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>29 ord: - analysera och värdera resultat i relation till tidigare forskning samt den kli…</t>
-        </is>
-      </c>
-      <c r="E200" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
-        <is>
-          <t>VV3017</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>29 ord: - tillämpa adekvat vetenskaplig design och metod i datainsamling och analys samt…</t>
-        </is>
-      </c>
-      <c r="E201" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
-        <is>
-          <t>VV3017</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>29 ord: - analysera och värdera resultat i relation till tidigare forskning samt den kli…</t>
-        </is>
-      </c>
-      <c r="E202" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
-        <is>
-          <t>VV3017</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>26 ord: - göra relevanta bedömningar på mikro-, meso- och makronivå med hänsyn till samh…</t>
-        </is>
-      </c>
-      <c r="E203" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E203"/>
+  <autoFilter ref="A1:E198"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -6320,16 +6185,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId392"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A198" r:id="rId393"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A201" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A202" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A203" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId404"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Omfång på lärandemål.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$198</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$207</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E198"/>
+  <dimension ref="A1:E207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2335,7 +2335,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>AMC29Y</t>
+          <t>AMC28N</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2350,19 +2350,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
+          <t>26 ord: - presentera och argumentera för vald design hos ett tänkt forskningsprojekt ino…</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC28N</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>AMC2A7</t>
+          <t>AMC29F</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2372,24 +2372,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>26 ord: - självständigt identifiera och formulera problemställning och syfte för en vete…</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>AMC2BG</t>
+          <t>AMC29F</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2404,19 +2404,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
+          <t>29 ord: - genomföra en vetenskaplig undersökning med relevant design, metod och analys s…</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GMC32X</t>
+          <t>AMC29F</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2431,19 +2431,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>29 ord: - förskriva och informera om förbrukningsartiklar vid urindysfunktion, urinreten…</t>
+          <t>32 ord: - analysera och värdera resultat från den vetenskapliga undersökningen i relatio…</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC32X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GMC37E</t>
+          <t>AMC29F</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2453,24 +2453,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>28 ord: - försvara eget självständigt arbete samt kritiskt granska och värdera annat exa…</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GMC37E</t>
+          <t>AMC29Y</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2485,19 +2485,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>30 ord: - Namnge, beskriva och förklara anatomi och funktion under människans livscykel …</t>
+          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GMC37T</t>
+          <t>AMC2A7</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2507,24 +2507,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 6 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>MC1072</t>
+          <t>AMC2AE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2539,19 +2539,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>26 ord: - söka relevant information utifrån fysiologiska frågeställningar relaterade til…</t>
+          <t>26 ord: - visa förståelse för och kritiskt förhållningsätt till vetenskapliga begrepp oc…</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1072</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2AE</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>MC1077</t>
+          <t>AMC2BG</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2566,19 +2566,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>31 ord: - redogöra för hygieniska principer i vårdarbetet samt visa kännedom om de lagar…</t>
+          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>MC2017</t>
+          <t>GMC32X</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2588,24 +2588,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>29 ord: - förskriva och informera om förbrukningsartiklar vid urindysfunktion, urinreten…</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC32X</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>MC2017</t>
+          <t>GMC37E</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2615,24 +2615,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>26 ord: -  redogöra för innehållet i de författningar som reglerar ansvarsfrågor och ans…</t>
+          <t>1 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>MC2017</t>
+          <t>GMC37E</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2647,19 +2647,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>26 ord: -  redogöra för hur anpassningsstörningar kan manifesteras hos barn, ungdomar oc…</t>
+          <t>30 ord: - Namnge, beskriva och förklara anatomi och funktion under människans livscykel …</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>MC3027</t>
+          <t>GMC37T</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2669,56 +2669,56 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 6 hp)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37T</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GNV367</t>
+          <t>MC1072</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - söka relevant information utifrån fysiologiska frågeställningar relaterade til…</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1072</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GNV367</t>
+          <t>MC1077</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2728,51 +2728,51 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>33 ord: - visa grundläggande kunskap om lärande för hållbar utveckling i grundskolans år…</t>
+          <t>31 ord: - redogöra för hygieniska principer i vårdarbetet samt visa kännedom om de lagar…</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GNV3GV</t>
+          <t>MC2017</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>28 ord: - redogöra för grundläggande kunskaper i naturvetenskap, med särskilt fokus på e…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GNV3GV</t>
+          <t>MC2017</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2782,73 +2782,73 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>34 ord: - reflektera över och problematisera skolans roll i arbetet med lärande för håll…</t>
+          <t>26 ord: -  redogöra för innehållet i de författningar som reglerar ansvarsfrågor och ans…</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>NV1035</t>
+          <t>MC2017</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: -  redogöra för hur anpassningsstörningar kan manifesteras hos barn, ungdomar oc…</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>NV1036</t>
+          <t>MC3027</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>NV1036</t>
+          <t>GNV367</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2858,24 +2858,24 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>26 ord: - visa god förtrogenhet med och reflektera över kursplanerna inom SO, NO och tek…</t>
+          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>NV1036</t>
+          <t>GNV367</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2890,19 +2890,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>32 ord: - visa insikt om hur närmiljö, förstahandsupplevelser, estetik och digital tekni…</t>
+          <t>33 ord: - visa grundläggande kunskap om lärande för hållbar utveckling i grundskolans år…</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>NV3001</t>
+          <t>GNV3GV</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2917,19 +2917,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>27 ord: - kritiskt diskutera begreppet hållbar utveckling och dess olika dimensioner, so…</t>
+          <t>28 ord: - redogöra för grundläggande kunskaper i naturvetenskap, med särskilt fokus på e…</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>NV3001</t>
+          <t>GNV3GV</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2944,24 +2944,24 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>27 ord: - reflektera över vilken roll den högre utbildningen har för hållbar utveckling,…</t>
+          <t>34 ord: - reflektera över och problematisera skolans roll i arbetet med lärande för håll…</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>ASA24K</t>
+          <t>NV1035</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>ASA24L</t>
+          <t>NV1036</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2998,127 +2998,127 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>14 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>ASA266</t>
+          <t>NV1036</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>26 ord: - visa god förtrogenhet med och reflektera över kursplanerna inom SO, NO och tek…</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>ASA26U</t>
+          <t>NV1036</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>32 ord: - visa insikt om hur närmiljö, förstahandsupplevelser, estetik och digital tekni…</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA26U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>ASA27E</t>
+          <t>NV3001</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
+          <t>27 ord: - kritiskt diskutera begreppet hållbar utveckling och dess olika dimensioner, so…</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>ASA293</t>
+          <t>NV3001</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>27 ord: - reflektera över vilken roll den högre utbildningen har för hållbar utveckling,…</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA293</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GSA24U</t>
+          <t>ASA24K</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3133,19 +3133,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24K</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GSA24V</t>
+          <t>ASA24L</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3160,19 +3160,19 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24L</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GSA24V</t>
+          <t>ASA266</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3182,24 +3182,24 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för perspektiv på och metoder för socialt arbete med barn, familjer, …</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA266</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GSA24V</t>
+          <t>ASA26U</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3209,24 +3209,24 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna rörande …</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA26U</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GSA27Y</t>
+          <t>ASA27E</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3241,19 +3241,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA27Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>ASA293</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3268,19 +3268,19 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA293</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>GSA24U</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3290,24 +3290,24 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>29 ord: - uppvisa kunskaper om en tolkningsram (till exempel teori, teoretiska begrepp, …</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>GSA24V</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3317,24 +3317,24 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>28 ord: - välja och beskriva en relevant tolkningsram (till exempel teori, teoretiska be…</t>
+          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>GSA24V</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3349,19 +3349,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>32 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
+          <t>27 ord: - redogöra för perspektiv på och metoder för socialt arbete med barn, familjer, …</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GSA2BV</t>
+          <t>GSA24V</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3371,24 +3371,24 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>27 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna rörande …</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GSA2BV</t>
+          <t>GSA27Y</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3398,24 +3398,24 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>26 ord: - visa förmåga att under handledning planera, strukturera och självständigt geno…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA27Y</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GSA2BV</t>
+          <t>GSA2AF</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3425,24 +3425,24 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga och färdigheter att identifiera, definiera, analysera och dokumen…</t>
+          <t>14 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GSA2BV</t>
+          <t>GSA2AF</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3457,19 +3457,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>28 ord: - kritiskt reflektera över den egna förmågan och den personliga och professionel…</t>
+          <t>29 ord: - uppvisa kunskaper om en tolkningsram (till exempel teori, teoretiska begrepp, …</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GSA2DW</t>
+          <t>GSA2AF</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3479,24 +3479,24 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>28 ord: - välja och beskriva en relevant tolkningsram (till exempel teori, teoretiska be…</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GSA2DW</t>
+          <t>GSA2AF</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3511,19 +3511,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna avseende…</t>
+          <t>32 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GSA2E3</t>
+          <t>GSA2BV</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3538,19 +3538,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GSA2E4</t>
+          <t>GSA2BV</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3560,24 +3560,24 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>26 ord: - visa förmåga att under handledning planera, strukturera och självständigt geno…</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GSA2E4</t>
+          <t>GSA2BV</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3592,19 +3592,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskap om och förståelse för hur familje- och samhällsförhållanden påver…</t>
+          <t>28 ord: - visa förmåga och färdigheter att identifiera, definiera, analysera och dokumen…</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GSA2E5</t>
+          <t>GSA2BV</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3614,24 +3614,24 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>28 ord: - kritiskt reflektera över den egna förmågan och den personliga och professionel…</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GSA2NA</t>
+          <t>GSA2DW</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3646,19 +3646,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GSA2NC</t>
+          <t>GSA2DW</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3668,24 +3668,24 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>29 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna avseende…</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GSA2RE</t>
+          <t>GSA2E3</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3700,19 +3700,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2RE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E3</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GSA2SD</t>
+          <t>GSA2E4</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3727,19 +3727,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GSA2SE</t>
+          <t>GSA2E4</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3749,24 +3749,24 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>29 ord: - visa kunskap om och förståelse för hur familje- och samhällsförhållanden påver…</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GSA2XN</t>
+          <t>GSA2E5</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3781,19 +3781,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2XN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GSA32Y</t>
+          <t>GSA2NA</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3808,19 +3808,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NA</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GSA352</t>
+          <t>GSA2NC</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3835,19 +3835,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>14 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA352</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GSA3DM</t>
+          <t>GSA2RE</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3862,19 +3862,19 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2RE</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GSA3DM</t>
+          <t>GSA2SD</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3884,24 +3884,24 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GSA3DM</t>
+          <t>GSA2SE</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3911,24 +3911,24 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
+          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GSA3DN</t>
+          <t>GSA2XN</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3943,19 +3943,19 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2XN</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GSA3DN</t>
+          <t>GSA32Y</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3965,24 +3965,24 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna avseende…</t>
+          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GSA3DP</t>
+          <t>GSA352</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3997,19 +3997,19 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA352</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>GSA3DQ</t>
+          <t>GSA3DM</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4024,19 +4024,19 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GSA3DQ</t>
+          <t>GSA3DM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4051,19 +4051,19 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för perspektiv på och metoder för socialt arbete med barn, familjer, …</t>
+          <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GSA3DQ</t>
+          <t>GSA3DM</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4078,19 +4078,19 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna rörande …</t>
+          <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GSA3DR</t>
+          <t>GSA3DN</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4105,19 +4105,19 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GSA3DS</t>
+          <t>GSA3DN</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4127,24 +4127,24 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>29 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna avseende…</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GSA3FK</t>
+          <t>GSA3DP</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4159,19 +4159,19 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DP</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GSA3FK</t>
+          <t>GSA3DQ</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4181,24 +4181,24 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>34 ord: - utifrån ett brukarperspektiv genomföra olika typer av utredningar inom socialt…</t>
+          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GSA3FL</t>
+          <t>GSA3DQ</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4208,24 +4208,24 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>27 ord: - redogöra för perspektiv på och metoder för socialt arbete med barn, familjer, …</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GSA3HA</t>
+          <t>GSA3DQ</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4235,24 +4235,24 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>27 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna rörande …</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3HA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>SA1045</t>
+          <t>GSA3DR</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4272,14 +4272,14 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DR</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>SA1048</t>
+          <t>GSA3DS</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4294,19 +4294,19 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>SA1048</t>
+          <t>GSA3FK</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4316,24 +4316,24 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>SA1048</t>
+          <t>GSA3FK</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4348,19 +4348,19 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
+          <t>34 ord: - utifrån ett brukarperspektiv genomföra olika typer av utredningar inom socialt…</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>SA2020</t>
+          <t>GSA3FL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4375,19 +4375,19 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>26 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FL</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>SA2020</t>
+          <t>GSA3HA</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4397,24 +4397,24 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>32 ord: - uppvisa kunskaper som utgör innehåll i en tolkningsram (till exempel teori, te…</t>
+          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3HA</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>SA2020</t>
+          <t>SA1045</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4424,24 +4424,24 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>32 ord: - analysera resultat från ett vetenskapligt arbete på sådant sätt att tolkningsr…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1045</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>SA2020</t>
+          <t>SA1048</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>32 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
+          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>SA3008</t>
+          <t>SA1048</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4478,24 +4478,24 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>SA3008</t>
+          <t>SA1048</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4510,51 +4510,51 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>30 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
+          <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>ASR24V</t>
+          <t>SA2020</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
+          <t>26 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>ASR24V</t>
+          <t>SA2020</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4564,24 +4564,24 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>27 ord: - ur ett rättighetsperspektiv analysera och diskutera hur sociala, ekonomiska, m…</t>
+          <t>32 ord: - uppvisa kunskaper som utgör innehåll i en tolkningsram (till exempel teori, te…</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>ASR25P</t>
+          <t>SA2020</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4591,78 +4591,78 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
+          <t>32 ord: - analysera resultat från ett vetenskapligt arbete på sådant sätt att tolkningsr…</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>ASR26N</t>
+          <t>SA2020</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>32 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>ASR26N</t>
+          <t>SA3008</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>30 ord: - diskutera vikten av samarbete och lagarbete inom och mellan utbildningsinstitu…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>ASR284</t>
+          <t>SA3008</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4672,19 +4672,19 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
+          <t>30 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>ASR285</t>
+          <t>ASR24V</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4694,24 +4694,24 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
+          <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>ASR285</t>
+          <t>ASR24V</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4726,19 +4726,19 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
+          <t>27 ord: - ur ett rättighetsperspektiv analysera och diskutera hur sociala, ekonomiska, m…</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>ASR285</t>
+          <t>ASR25P</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4753,19 +4753,19 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
+          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>ASR29S</t>
+          <t>ASR26N</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4775,24 +4775,24 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>27 ord: - analysera och värdera resultat i relation till tidigare forskning, värdera den…</t>
+          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>ASR29T</t>
+          <t>ASR26N</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4807,19 +4807,19 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>26 ord: - problematisera och reflektera över kvinnans, barnets och närståendes roller oc…</t>
+          <t>30 ord: - diskutera vikten av samarbete och lagarbete inom och mellan utbildningsinstitu…</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>ASR29T</t>
+          <t>ASR284</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4834,19 +4834,19 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
+          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>ASR29U</t>
+          <t>ASR285</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4856,24 +4856,24 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>26 ord: - i simulerad miljö utföra undersökningar och behandlingar vid komplicerad gravi…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>ASR29V</t>
+          <t>ASR285</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4883,24 +4883,24 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
+          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>ASR29V</t>
+          <t>ASR285</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4915,19 +4915,19 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
+          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>ASR29V</t>
+          <t>ASR29S</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4942,19 +4942,19 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
+          <t>27 ord: - analysera och värdera resultat i relation till tidigare forskning, värdera den…</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>ASR29W</t>
+          <t>ASR29T</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4969,19 +4969,19 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
+          <t>26 ord: - problematisera och reflektera över kvinnans, barnets och närståendes roller oc…</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>ASR2AD</t>
+          <t>ASR29T</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4996,19 +4996,19 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av k…</t>
+          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2AD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>ASR2BM</t>
+          <t>ASR29U</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5018,24 +5018,24 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>26 ord: - i simulerad miljö utföra undersökningar och behandlingar vid komplicerad gravi…</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2BM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>ASR2CE</t>
+          <t>ASR29V</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5045,24 +5045,24 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>GSR38B</t>
+          <t>ASR29V</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5077,19 +5077,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>33 ord: - uppvisa kunskap, förståelse och reflekterande färdigheter om sexuell och repro…</t>
+          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>SR3001</t>
+          <t>ASR29V</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5104,19 +5104,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>30 ord: - värdera olika strategier för ledarskap och interventioner som har potential at…</t>
+          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>SR3002</t>
+          <t>ASR29W</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5131,19 +5131,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>27 ord: - analysera och kritiskt värdera styrkor och svagheter i forskningsprocessens ol…</t>
+          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29W</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>SR3007</t>
+          <t>ASR2AD</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5153,24 +5153,24 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av k…</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2AD</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>SR3008</t>
+          <t>ASR2BM</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5190,14 +5190,14 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2BM</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>SR3009</t>
+          <t>ASR2CE</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5212,19 +5212,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>26 ord: - analysera betydelsen av hälsofrämjande arbete under den reproduktiva livscykel…</t>
+          <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CE</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>SR3009</t>
+          <t>GSR38B</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5239,19 +5239,19 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>29 ord: - identifiera problemområden och formulera relevanta frågeställningar som rör gr…</t>
+          <t>33 ord: - uppvisa kunskap, förståelse och reflekterande färdigheter om sexuell och repro…</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>SR3009</t>
+          <t>SR3001</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5266,19 +5266,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för benigna och maligna gynekologiska förändringar, värdera hälsotill…</t>
+          <t>30 ord: - värdera olika strategier för ledarskap och interventioner som har potential at…</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>SR3010</t>
+          <t>SR3002</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5293,19 +5293,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>27 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av g…</t>
+          <t>27 ord: - analysera och kritiskt värdera styrkor och svagheter i forskningsprocessens ol…</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>SR3011</t>
+          <t>SR3007</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5315,24 +5315,24 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
+          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>SR3012</t>
+          <t>SR3008</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5347,19 +5347,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>SR3012</t>
+          <t>SR3009</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5374,19 +5374,19 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
+          <t>26 ord: - analysera betydelsen av hälsofrämjande arbete under den reproduktiva livscykel…</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>SR3012</t>
+          <t>SR3009</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5401,19 +5401,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
+          <t>29 ord: - identifiera problemområden och formulera relevanta frågeställningar som rör gr…</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>SR3014</t>
+          <t>SR3009</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5423,24 +5423,24 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 10 för 13.5 hp)</t>
+          <t>27 ord: - redogöra för benigna och maligna gynekologiska förändringar, värdera hälsotill…</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>SR3014</t>
+          <t>SR3010</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5455,19 +5455,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>30 ord: - med ett professionellt förhållningssätt informera, ge stöd och trygghet i dial…</t>
+          <t>27 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av g…</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>SR3015</t>
+          <t>SR3011</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5477,24 +5477,24 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 10 för 13.5 hp)</t>
+          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>SR3015</t>
+          <t>SR3012</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5504,24 +5504,24 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>35 ord: - självständigt handlägga preventivmedelsrådgivning och informera om lämpliga an…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>SR3015</t>
+          <t>SR3012</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>26 ord: - kritiskt analysera, värdera, föreslå och följa upp vårdnadsinsatser och behand…</t>
+          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>AVV2A6</t>
+          <t>SR3012</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -5563,78 +5563,78 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>26 ord: - kritiskt reflektera över hur kvalitets- och säkerhetsledning organiseras och r…</t>
+          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV2A6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>VV2002</t>
+          <t>SR3014</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för gällande regelverk för olika professioner inom kommunal äldreomso…</t>
+          <t>11 lärandemål (maximum rekommenderat: 10 för 13.5 hp)</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>VV3006</t>
+          <t>SR3014</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>30 ord: - med ett professionellt förhållningssätt informera, ge stöd och trygghet i dial…</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>VV3011</t>
+          <t>SR3015</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -5644,24 +5644,24 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>19 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>14 lärandemål (maximum rekommenderat: 10 för 13.5 hp)</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>VV3012</t>
+          <t>SR3015</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5671,24 +5671,24 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>29 ord: - tillämpa adekvat vetenskaplig design och metod i datainsamling och analys samt…</t>
+          <t>35 ord: - självständigt handlägga preventivmedelsrådgivning och informera om lämpliga an…</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>VV3012</t>
+          <t>SR3015</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -5698,19 +5698,19 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>29 ord: - analysera och värdera resultat i relation till tidigare forskning samt den kli…</t>
+          <t>26 ord: - kritiskt analysera, värdera, föreslå och följa upp vårdnadsinsatser och behand…</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>VV3017</t>
+          <t>AVV2A6</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5725,19 +5725,19 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>29 ord: - tillämpa adekvat vetenskaplig design och metod i datainsamling och analys samt…</t>
+          <t>26 ord: - kritiskt reflektera över hur kvalitets- och säkerhetsledning organiseras och r…</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV2A6</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>VV3017</t>
+          <t>VV2002</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5752,44 +5752,287 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>29 ord: - analysera och värdera resultat i relation till tidigare forskning samt den kli…</t>
+          <t>29 ord: - redogöra för gällande regelverk för olika professioner inom kommunal äldreomso…</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
+          <t>VV3006</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>VV3011</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>19 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>VV3012</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>29 ord: - tillämpa adekvat vetenskaplig design och metod i datainsamling och analys samt…</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>VV3012</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>29 ord: - analysera och värdera resultat i relation till tidigare forskning samt den kli…</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
           <t>VV3017</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
+      <c r="B202" t="inlineStr">
         <is>
           <t>VÅE</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>29 ord: - tillämpa adekvat vetenskaplig design och metod i datainsamling och analys samt…</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>VV3017</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>29 ord: - analysera och värdera resultat i relation till tidigare forskning samt den kli…</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>VV3017</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
         <is>
           <t>26 ord: - göra relevanta bedömningar på mikro-, meso- och makronivå med hänsyn till samh…</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
         </is>
       </c>
     </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>FHV0001</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>VÅRDVETS</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>FHV0002</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>VÅRDVETS</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0002</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>FHV0003</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>VÅRDVETS</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0003</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E198"/>
+  <autoFilter ref="A1:E207"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -6185,6 +6428,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId392"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A198" r:id="rId393"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A201" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A202" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A203" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A204" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A205" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A206" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A207" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId412"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Omfång på lärandemål.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$207</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$209</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E207"/>
+  <dimension ref="A1:E209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5224,7 +5224,7 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>GSR38B</t>
+          <t>ASR2CS</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5234,24 +5234,24 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>33 ord: - uppvisa kunskap, förståelse och reflekterande färdigheter om sexuell och repro…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CS</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>SR3001</t>
+          <t>ASR2CS</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5266,19 +5266,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>30 ord: - värdera olika strategier för ledarskap och interventioner som har potential at…</t>
+          <t>26 ord: - redogöra för och motivera metoder för att främja, undersöka och övervaka kvinn…</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CS</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>SR3002</t>
+          <t>GSR38B</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5293,19 +5293,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>27 ord: - analysera och kritiskt värdera styrkor och svagheter i forskningsprocessens ol…</t>
+          <t>33 ord: - uppvisa kunskap, förståelse och reflekterande färdigheter om sexuell och repro…</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>SR3007</t>
+          <t>SR3001</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5315,24 +5315,24 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>30 ord: - värdera olika strategier för ledarskap och interventioner som har potential at…</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>SR3008</t>
+          <t>SR3002</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5342,24 +5342,24 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>27 ord: - analysera och kritiskt värdera styrkor och svagheter i forskningsprocessens ol…</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>SR3009</t>
+          <t>SR3007</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5369,24 +5369,24 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>26 ord: - analysera betydelsen av hälsofrämjande arbete under den reproduktiva livscykel…</t>
+          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>SR3009</t>
+          <t>SR3008</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5396,17 +5396,17 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>29 ord: - identifiera problemområden och formulera relevanta frågeställningar som rör gr…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för benigna och maligna gynekologiska förändringar, värdera hälsotill…</t>
+          <t>26 ord: - analysera betydelsen av hälsofrämjande arbete under den reproduktiva livscykel…</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -5440,7 +5440,7 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>SR3010</t>
+          <t>SR3009</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5455,19 +5455,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>27 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av g…</t>
+          <t>29 ord: - identifiera problemområden och formulera relevanta frågeställningar som rör gr…</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>SR3011</t>
+          <t>SR3009</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5482,19 +5482,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
+          <t>27 ord: - redogöra för benigna och maligna gynekologiska förändringar, värdera hälsotill…</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>SR3012</t>
+          <t>SR3010</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5504,24 +5504,24 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
+          <t>27 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av g…</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>SR3012</t>
+          <t>SR3011</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5536,12 +5536,12 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
+          <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
         </is>
       </c>
     </row>
@@ -5558,12 +5558,12 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>SR3014</t>
+          <t>SR3012</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5585,24 +5585,24 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 10 för 13.5 hp)</t>
+          <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>SR3014</t>
+          <t>SR3012</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5617,19 +5617,19 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>30 ord: - med ett professionellt förhållningssätt informera, ge stöd och trygghet i dial…</t>
+          <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>SR3015</t>
+          <t>SR3014</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5644,19 +5644,19 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 10 för 13.5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 10 för 13.5 hp)</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>SR3015</t>
+          <t>SR3014</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>35 ord: - självständigt handlägga preventivmedelsrådgivning och informera om lämpliga an…</t>
+          <t>30 ord: - med ett professionellt förhållningssätt informera, ge stöd och trygghet i dial…</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
         </is>
       </c>
     </row>
@@ -5693,12 +5693,12 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>26 ord: - kritiskt analysera, värdera, föreslå och följa upp vårdnadsinsatser och behand…</t>
+          <t>14 lärandemål (maximum rekommenderat: 10 för 13.5 hp)</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>AVV2A6</t>
+          <t>SR3015</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -5725,24 +5725,24 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>26 ord: - kritiskt reflektera över hur kvalitets- och säkerhetsledning organiseras och r…</t>
+          <t>35 ord: - självständigt handlägga preventivmedelsrådgivning och informera om lämpliga an…</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV2A6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>VV2002</t>
+          <t>SR3015</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -5752,19 +5752,19 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för gällande regelverk för olika professioner inom kommunal äldreomso…</t>
+          <t>26 ord: - kritiskt analysera, värdera, föreslå och följa upp vårdnadsinsatser och behand…</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>VV3006</t>
+          <t>AVV2A6</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5774,24 +5774,24 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>26 ord: - kritiskt reflektera över hur kvalitets- och säkerhetsledning organiseras och r…</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV2A6</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>VV3011</t>
+          <t>VV2002</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5801,24 +5801,24 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>19 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>29 ord: - redogöra för gällande regelverk för olika professioner inom kommunal äldreomso…</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>VV3012</t>
+          <t>VV3006</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5828,24 +5828,24 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>29 ord: - tillämpa adekvat vetenskaplig design och metod i datainsamling och analys samt…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>VV3012</t>
+          <t>VV3011</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5855,24 +5855,24 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>29 ord: - analysera och värdera resultat i relation till tidigare forskning samt den kli…</t>
+          <t>19 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>VV3017</t>
+          <t>VV3012</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5892,14 +5892,14 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>VV3017</t>
+          <t>VV3012</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
         </is>
       </c>
     </row>
@@ -5941,7 +5941,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>26 ord: - göra relevanta bedömningar på mikro-, meso- och makronivå med hänsyn till samh…</t>
+          <t>29 ord: - tillämpa adekvat vetenskaplig design och metod i datainsamling och analys samt…</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -5953,86 +5953,140 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>FHV0001</t>
+          <t>VV3017</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>VÅRDVETS</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>29 ord: - analysera och värdera resultat i relation till tidigare forskning samt den kli…</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>FHV0002</t>
+          <t>VV3017</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>VÅRDVETS</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>26 ord: - göra relevanta bedömningar på mikro-, meso- och makronivå med hänsyn till samh…</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
+          <t>FHV0001</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>VÅRDVETS</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>FHV0002</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>VÅRDVETS</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0002</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
           <t>FHV0003</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B209" t="inlineStr">
         <is>
           <t>VÅRDVETS</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr">
+      <c r="C209" t="inlineStr">
         <is>
           <t>För få mål</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr">
+      <c r="D209" t="inlineStr">
         <is>
           <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="E209" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0003</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E207"/>
+  <autoFilter ref="A1:E209"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -6446,6 +6500,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId410"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A207" r:id="rId411"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A208" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A209" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId416"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Omfång på lärandemål.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$209</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$G$209</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E209"/>
+  <dimension ref="A1:G209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>40 ord: - presentera och argumentera för vald design av en projektplan för en vetenskapl…</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C8</t>
         </is>
@@ -509,15 +527,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>29 ord: - genomföra en vetenskaplig undersökning med relevant design, metod och analys s…</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C9</t>
         </is>
@@ -536,15 +560,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>36 ord: - analysera och värdera resultat från den vetenskapliga undersökningen i relatio…</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C9</t>
         </is>
@@ -563,15 +593,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>26 ord: - presentera, sammanfatta och försvara eget självständigt arbete, samt som oppon…</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C9</t>
         </is>
@@ -590,15 +626,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>32 ord: - redogöra för och värdera olika sätt att kategorisera smärta i förhållande till…</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2CA</t>
         </is>
@@ -617,15 +659,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>28 ord: - redogöra för centrala anpassningar i organ och vävnader som följer av regelbun…</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2CB</t>
         </is>
@@ -644,15 +692,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>28 ord: - genomföra enklare datainsamling av fysisk aktivitetsnivå och fysisk prestation…</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2CB</t>
         </is>
@@ -671,15 +725,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>31 ord: - med stöd i relevant teoribildning identifiera hinder och underlättande faktore…</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2CB</t>
         </is>
@@ -698,15 +758,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>29 ord: - självständigt identifiera ett idrottsdidaktiskt problemområde och formulera fo…</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH237</t>
         </is>
@@ -725,15 +791,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>31 ord: - utifrån ett vetenskapsteoretiskt perspektiv diskutera kvalitativ och kvantitat…</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH237</t>
         </is>
@@ -752,15 +824,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>30 ord: - genomföra ett självständigt idrottsdidaktiskt vetenskapligt arbete med tydlig …</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH237</t>
         </is>
@@ -779,15 +857,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+          <t>2020-03-05</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>29 ord: - självständigt identifiera ett idrottsdidaktiskt problemområde och formulera fo…</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH24T</t>
         </is>
@@ -806,15 +890,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+          <t>2020-03-05</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>31 ord: - utifrån ett vetenskapsteoretiskt perspektiv diskutera kvalitativ och kvantitat…</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH24T</t>
         </is>
@@ -833,15 +923,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+          <t>2020-03-05</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>30 ord: - genomföra ett självständigt idrottsdidaktiskt vetenskapligt arbete med tydlig …</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH24T</t>
         </is>
@@ -860,15 +956,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>2020-03-05</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2020-05-20</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>För få mål</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2G4</t>
         </is>
@@ -887,15 +993,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+          <t>2021-06-07</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>30 ord: - med goda rörelsekvaliteter delta i olika rörelseaktiviteter med relevans för t…</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QL</t>
         </is>
@@ -914,15 +1026,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WT</t>
         </is>
@@ -941,15 +1059,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WY</t>
         </is>
@@ -968,15 +1092,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2022-08-22</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>29 ord: - utifrån vetenskaplig grund inom området välja övningar och designa ett träning…</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2X3</t>
         </is>
@@ -995,15 +1129,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+          <t>2022-12-12</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>26 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZC</t>
         </is>
@@ -1022,15 +1162,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+          <t>2022-12-12</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZD</t>
         </is>
@@ -1049,15 +1195,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+          <t>2023-02-07</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>27 ord: - formulera en affärsplan med tillhörande budget inom området idrott och hälsa s…</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH335</t>
         </is>
@@ -1076,15 +1228,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+          <t>2023-05-09</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>28 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34S</t>
         </is>
@@ -1103,15 +1261,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+          <t>2023-05-09</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34S</t>
         </is>
@@ -1130,15 +1294,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>För få mål</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35T</t>
         </is>
@@ -1157,15 +1327,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
         </is>
@@ -1184,15 +1360,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
@@ -1211,15 +1393,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>28 ord: - på en grundläggande nivå diskutera och problematisera skolämnet idrott och häl…</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
@@ -1238,15 +1426,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
@@ -1265,15 +1459,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>26 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
@@ -1292,15 +1492,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
         </is>
@@ -1319,15 +1525,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>19 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37S</t>
         </is>
@@ -1346,15 +1558,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>28 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH38Z</t>
         </is>
@@ -1373,15 +1591,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH38Z</t>
         </is>
@@ -1400,15 +1624,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH392</t>
         </is>
@@ -1427,15 +1657,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39E</t>
         </is>
@@ -1454,15 +1690,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>26 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH39H</t>
         </is>
@@ -1481,15 +1723,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AN</t>
         </is>
@@ -1508,15 +1756,21 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
         </is>
@@ -1535,15 +1789,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>28 ord: - på en grundläggande nivå diskutera och problematisera skolämnet idrott och häl…</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
         </is>
@@ -1562,15 +1822,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>26 ord: - utifrån valt syfte, innehåll och målgrupp samt i relation till aktuella styrdo…</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
         </is>
@@ -1589,15 +1855,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>26 ord: - diskutera och problematisera skolämnet idrott och hälsa utifrån olika didaktis…</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
         </is>
@@ -1616,15 +1888,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>29 ord: - utifrån vetenskaplig grund inom området välja övningar och designa ett träning…</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
         </is>
@@ -1643,15 +1921,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>28 ord: - utifrån vetenskaplig grund inom området välja övningar och designa ett hälsoin…</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
         </is>
@@ -1670,15 +1954,21 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>För få mål</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3FA</t>
         </is>
@@ -1697,15 +1987,21 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>För få mål</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G4</t>
         </is>
@@ -1724,15 +2020,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>För få mål</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G6</t>
         </is>
@@ -1751,15 +2053,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>28 ord: - formulera en affärsplan med tillhörande budget inom området idrott och hälsa s…</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
         </is>
@@ -1778,15 +2086,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
         </is>
@@ -1805,15 +2119,21 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>26 ord: - skapa lärandesituationer i ett urval av de behandlade rörelseaktiviteterna med…</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
         </is>
@@ -1832,15 +2152,21 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>För få mål</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
         </is>
@@ -1859,15 +2185,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>27 ord: - skapa stimulerande lärandesituationer i olika pedagogiska sammanhang, som ocks…</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
         </is>
@@ -1886,15 +2218,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>För få mål</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1012</t>
         </is>
@@ -1913,15 +2251,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
+          <t>2011-03-30</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>29 ord: - skapa lärandesituationer i de kunskapsområden som explicit nämns i kursplanern…</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1029</t>
         </is>
@@ -1940,15 +2284,25 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t>2012-12-05</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2013-11-25</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>16 lärandemål (maximum rekommenderat: 12 för 20 hp)</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1062</t>
         </is>
@@ -1967,15 +2321,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
+          <t>2015-04-09</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>30 ord: - tillämpa grundläggande kunskaper inom ämnesområdet fysisk träning med specifik…</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
         </is>
@@ -1994,15 +2354,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
+          <t>2015-04-09</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>26 ord: - praktisk genomföra och instruera övningar inriktade mot optimering av de fysis…</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
         </is>
@@ -2021,15 +2387,21 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
+          <t>2015-04-09</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>28 ord: - redogöra för de viktigaste mikro- och makronutrienterna och deras betydelse vi…</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
         </is>
@@ -2048,15 +2420,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
+          <t>2015-04-09</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>36 ord: - visa förståelse för samt praktiskt tillämpa de centrala principerna för utform…</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
         </is>
@@ -2075,15 +2453,21 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>För få mål</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>3 lärandemål (minimum rekommenderat: 5 för 30 hp)</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
         </is>
@@ -2102,15 +2486,21 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
         </is>
@@ -2129,15 +2519,21 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>26 ord: - självständigt identifiera, formulera och diskutera frågeställningar som berör …</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
         </is>
@@ -2156,15 +2552,21 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>26 ord: - självständigt identifiera, formulera och diskutera frågeställningar som berör …</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2005</t>
         </is>
@@ -2183,15 +2585,21 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
+          <t>2020-02-20</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>26 ord: - självständigt söka, sammanställa och kritiskt granska evidensbaserad informati…</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC243</t>
         </is>
@@ -2210,15 +2618,21 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>38 ord: - beskriva samband mellan fysisk aktivitet och hälsa vid en vald diagnos eller s…</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
         </is>
@@ -2237,15 +2651,21 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>27 ord: - jämföra och kritiskt diskutera olika mät- och utvärderingsmetoder för fysisk a…</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
         </is>
@@ -2264,15 +2684,21 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>34 ord: - utifrån vetenskaplig evidens beskriva hur fysisk träning kan utformas beroende…</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
         </is>
@@ -2291,15 +2717,21 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>35 ord: - med stöd i vetenskaplig litteratur och egen erfarenhet reflektera kring den ro…</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
         </is>
@@ -2318,15 +2750,21 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>31 ord: - med stöd i relevant teoribildning identifiera hinder och underlättande faktore…</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
         </is>
@@ -2345,15 +2783,21 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
+          <t>2022-12-12</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>26 ord: - presentera och argumentera för vald design hos ett tänkt forskningsprojekt ino…</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC28N</t>
         </is>
@@ -2372,15 +2816,21 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>26 ord: - självständigt identifiera och formulera problemställning och syfte för en vete…</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
         </is>
@@ -2399,15 +2849,21 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>29 ord: - genomföra en vetenskaplig undersökning med relevant design, metod och analys s…</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
         </is>
@@ -2426,15 +2882,21 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>32 ord: - analysera och värdera resultat från den vetenskapliga undersökningen i relatio…</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
         </is>
@@ -2453,15 +2915,21 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>28 ord: - försvara eget självständigt arbete samt kritiskt granska och värdera annat exa…</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
         </is>
@@ -2480,15 +2948,21 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
         </is>
@@ -2507,15 +2981,21 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
         </is>
@@ -2534,15 +3014,21 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>26 ord: - visa förståelse för och kritiskt förhållningsätt till vetenskapliga begrepp oc…</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2AE</t>
         </is>
@@ -2561,15 +3047,21 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
         </is>
@@ -2588,15 +3080,21 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
+          <t>2023-02-07</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>29 ord: - förskriva och informera om förbrukningsartiklar vid urindysfunktion, urinreten…</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC32X</t>
         </is>
@@ -2615,15 +3113,21 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>För få mål</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>1 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
         </is>
@@ -2642,15 +3146,21 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>30 ord: - Namnge, beskriva och förklara anatomi och funktion under människans livscykel …</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37E</t>
         </is>
@@ -2669,15 +3179,21 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>För få mål</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>2 lärandemål (minimum rekommenderat: 3 för 6 hp)</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC37T</t>
         </is>
@@ -2696,15 +3212,25 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>2013-09-09</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t>2014-01-22</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t>26 ord: - söka relevant information utifrån fysiologiska frågeställningar relaterade til…</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1072</t>
         </is>
@@ -2723,15 +3249,21 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
+          <t>2015-02-12</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>31 ord: - redogöra för hygieniska principer i vårdarbetet samt visa kännedom om de lagar…</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
         </is>
@@ -2750,15 +3282,21 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
+          <t>2012-08-30</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
         </is>
@@ -2777,15 +3315,21 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
+          <t>2012-08-30</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>26 ord: -  redogöra för innehållet i de författningar som reglerar ansvarsfrågor och ans…</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
         </is>
@@ -2804,15 +3348,21 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
+          <t>2012-08-30</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>26 ord: -  redogöra för hur anpassningsstörningar kan manifesteras hos barn, ungdomar oc…</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
         </is>
@@ -2831,15 +3381,21 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
+          <t>2017-03-13</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>27 ord: - identifiera och diskutera miljö- och hållbarhetsperspektiv i samband med läkem…</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
         </is>
@@ -2858,15 +3414,21 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
         </is>
@@ -2885,15 +3447,21 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
         <is>
           <t>33 ord: - visa grundläggande kunskap om lärande för hållbar utveckling i grundskolans år…</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
         </is>
@@ -2912,15 +3480,21 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
         <is>
           <t>28 ord: - redogöra för grundläggande kunskaper i naturvetenskap, med särskilt fokus på e…</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
         </is>
@@ -2939,15 +3513,21 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
         <is>
           <t>34 ord: - reflektera över och problematisera skolans roll i arbetet med lärande för håll…</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
         </is>
@@ -2966,15 +3546,21 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
+          <t>2017-08-24</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
         </is>
@@ -2993,15 +3579,21 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
+          <t>2017-09-28</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>14 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
         </is>
@@ -3020,15 +3612,21 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
+          <t>2017-09-28</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>26 ord: - visa god förtrogenhet med och reflektera över kursplanerna inom SO, NO och tek…</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
         </is>
@@ -3047,15 +3645,21 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
+          <t>2017-09-28</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>32 ord: - visa insikt om hur närmiljö, förstahandsupplevelser, estetik och digital tekni…</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
         </is>
@@ -3074,15 +3678,21 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
+          <t>2016-03-03</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>27 ord: - kritiskt diskutera begreppet hållbar utveckling och dess olika dimensioner, so…</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
         </is>
@@ -3101,15 +3711,21 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
+          <t>2016-03-03</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>27 ord: - reflektera över vilken roll den högre utbildningen har för hållbar utveckling,…</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
         </is>
@@ -3128,15 +3744,25 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
+          <t>2020-02-13</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2020-05-04</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24K</t>
         </is>
@@ -3155,15 +3781,25 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
+          <t>2020-02-13</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2020-05-04</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24L</t>
         </is>
@@ -3182,15 +3818,25 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA266</t>
         </is>
@@ -3209,15 +3855,25 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
+          <t>2021-03-12</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2021-03-16</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA26U</t>
         </is>
@@ -3236,15 +3892,21 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
+          <t>2021-11-09</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>9 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
         </is>
@@ -3263,15 +3925,21 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
+          <t>2023-05-09</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA293</t>
         </is>
@@ -3290,15 +3958,25 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
+          <t>2018-09-27</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2018-10-19</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
         </is>
@@ -3317,15 +3995,21 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
+          <t>2018-09-27</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
         </is>
@@ -3344,15 +4028,21 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
+          <t>2018-09-27</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
         <is>
           <t>27 ord: - redogöra för perspektiv på och metoder för socialt arbete med barn, familjer, …</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
         </is>
@@ -3371,15 +4061,21 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
+          <t>2018-09-27</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
         <is>
           <t>27 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna rörande …</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
         </is>
@@ -3398,15 +4094,21 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
+          <t>2019-03-12</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="F110" t="inlineStr">
         <is>
           <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA27Y</t>
         </is>
@@ -3425,15 +4127,25 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
+          <t>2019-08-29</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="F111" t="inlineStr">
         <is>
           <t>14 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
@@ -3452,15 +4164,25 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>2019-08-29</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
           <t>29 ord: - uppvisa kunskaper om en tolkningsram (till exempel teori, teoretiska begrepp, …</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
@@ -3479,15 +4201,25 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>2019-08-29</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
           <t>28 ord: - välja och beskriva en relevant tolkningsram (till exempel teori, teoretiska be…</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
@@ -3506,15 +4238,25 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>2019-08-29</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
           <t>32 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
@@ -3533,15 +4275,25 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
+          <t>2019-10-29</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2023-01-19</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="F115" t="inlineStr">
         <is>
           <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
@@ -3560,15 +4312,25 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>2019-10-29</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
+          <t>2023-01-19</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
           <t>26 ord: - visa förmåga att under handledning planera, strukturera och självständigt geno…</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
@@ -3587,15 +4349,25 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>2019-10-29</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
+          <t>2023-01-19</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
           <t>28 ord: - visa förmåga och färdigheter att identifiera, definiera, analysera och dokumen…</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
@@ -3614,15 +4386,25 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>2019-10-29</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
+          <t>2023-01-19</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
           <t>28 ord: - kritiskt reflektera över den egna förmågan och den personliga och professionel…</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
@@ -3641,15 +4423,25 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
+          <t>2020-02-20</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2023-11-30</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="F119" t="inlineStr">
         <is>
           <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
         </is>
@@ -3668,15 +4460,25 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>2020-02-20</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
+          <t>2023-11-30</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
           <t>29 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna avseende…</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
         </is>
@@ -3695,15 +4497,25 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
+          <t>2020-02-13</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="F121" t="inlineStr">
         <is>
           <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E3</t>
         </is>
@@ -3722,15 +4534,21 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
+          <t>2020-02-13</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="F122" t="inlineStr">
         <is>
           <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
         </is>
@@ -3749,15 +4567,21 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
+          <t>2020-02-13</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
         <is>
           <t>29 ord: - visa kunskap om och förståelse för hur familje- och samhällsförhållanden påver…</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
         </is>
@@ -3776,15 +4600,21 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
+          <t>2020-02-13</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="F124" t="inlineStr">
         <is>
           <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
         </is>
@@ -3803,15 +4633,25 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
+          <t>2021-03-09</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2021-03-18</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="F125" t="inlineStr">
         <is>
           <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NA</t>
         </is>
@@ -3830,15 +4670,21 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
+          <t>2021-03-09</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="F126" t="inlineStr">
         <is>
           <t>14 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
         </is>
@@ -3857,15 +4703,21 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="F127" t="inlineStr">
         <is>
           <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2RE</t>
         </is>
@@ -3884,15 +4736,21 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
+          <t>2021-12-08</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="F128" t="inlineStr">
         <is>
           <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
         </is>
@@ -3911,15 +4769,21 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
+          <t>2021-12-08</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="F129" t="inlineStr">
         <is>
           <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
         </is>
@@ -3938,15 +4802,21 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2XN</t>
         </is>
@@ -3965,15 +4835,21 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
+          <t>2023-02-07</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="F131" t="inlineStr">
         <is>
           <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
         </is>
@@ -3992,15 +4868,21 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
+          <t>2023-05-09</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA352</t>
         </is>
@@ -4019,15 +4901,21 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
         </is>
@@ -4046,15 +4934,21 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
         <is>
           <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
         </is>
@@ -4073,15 +4967,21 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
         <is>
           <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
         </is>
@@ -4100,15 +5000,21 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
+      <c r="F136" t="inlineStr">
         <is>
           <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
         </is>
@@ -4127,15 +5033,21 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
         <is>
           <t>29 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna avseende…</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
         </is>
@@ -4154,15 +5066,21 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="F138" t="inlineStr">
         <is>
           <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DP</t>
         </is>
@@ -4181,15 +5099,21 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="F139" t="inlineStr">
         <is>
           <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
         </is>
@@ -4208,15 +5132,21 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
         <is>
           <t>27 ord: - redogöra för perspektiv på och metoder för socialt arbete med barn, familjer, …</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
         </is>
@@ -4235,15 +5165,21 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
         <is>
           <t>27 ord: - visa förmåga att reflektera över hur de egna personliga värderingarna rörande …</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
         </is>
@@ -4262,15 +5198,21 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="F142" t="inlineStr">
         <is>
           <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DR</t>
         </is>
@@ -4289,15 +5231,21 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="F143" t="inlineStr">
         <is>
           <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
         </is>
@@ -4316,15 +5264,21 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
+      <c r="F144" t="inlineStr">
         <is>
           <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
         </is>
@@ -4343,15 +5297,21 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
         <is>
           <t>34 ord: - utifrån ett brukarperspektiv genomföra olika typer av utredningar inom socialt…</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
         </is>
@@ -4370,15 +5330,21 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="F146" t="inlineStr">
         <is>
           <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FL</t>
         </is>
@@ -4397,15 +5363,21 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
+      <c r="F147" t="inlineStr">
         <is>
           <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3HA</t>
         </is>
@@ -4424,15 +5396,21 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
+          <t>2017-03-13</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
+      <c r="F148" t="inlineStr">
         <is>
           <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1045</t>
         </is>
@@ -4451,15 +5429,21 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
+          <t>2017-11-30</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="F149" t="inlineStr">
         <is>
           <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
         </is>
@@ -4478,15 +5462,21 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
+          <t>2017-11-30</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
         <is>
           <t>28 ord: - visa förmåga att på grundläggande nivå tillämpa metoder i socialt arbete inom …</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
         </is>
@@ -4505,15 +5495,21 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
+          <t>2017-11-30</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
         <is>
           <t>27 ord: - kunna redogöra för grundläggande metoder och arbetssätt som tillämpas i social…</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
         </is>
@@ -4532,15 +5528,21 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
+          <t>2014-12-23</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
+      <c r="F152" t="inlineStr">
         <is>
           <t>26 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
@@ -4559,15 +5561,21 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
+          <t>2014-12-23</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
         <is>
           <t>32 ord: - uppvisa kunskaper som utgör innehåll i en tolkningsram (till exempel teori, te…</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
@@ -4586,15 +5594,21 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
+          <t>2014-12-23</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
         <is>
           <t>32 ord: - analysera resultat från ett vetenskapligt arbete på sådant sätt att tolkningsr…</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
@@ -4613,15 +5627,21 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
+          <t>2014-12-23</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
         <is>
           <t>32 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
@@ -4640,15 +5660,21 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
+          <t>2016-09-08</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
+      <c r="F156" t="inlineStr">
         <is>
           <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
         </is>
@@ -4667,15 +5693,21 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
+          <t>2016-09-08</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
         <is>
           <t>30 ord: - komponera och integrera de olika delarna i ett vetenskapligt arbete på ett såd…</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
         </is>
@@ -4694,15 +5726,25 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
           <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
         </is>
@@ -4721,15 +5763,25 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
           <t>27 ord: - ur ett rättighetsperspektiv analysera och diskutera hur sociala, ekonomiska, m…</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
         </is>
@@ -4748,15 +5800,21 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
+          <t>2020-04-29</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
         <is>
           <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
         </is>
@@ -4775,15 +5833,25 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
+          <t>2021-03-01</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2021-03-03</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
+      <c r="F161" t="inlineStr">
         <is>
           <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
         </is>
@@ -4802,15 +5870,25 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
+          <t>2021-03-03</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
           <t>30 ord: - diskutera vikten av samarbete och lagarbete inom och mellan utbildningsinstitu…</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
         </is>
@@ -4829,15 +5907,21 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
         <is>
           <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
         </is>
@@ -4856,15 +5940,21 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="F164" t="inlineStr">
         <is>
           <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
@@ -4883,15 +5973,21 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
         <is>
           <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
@@ -4910,15 +6006,21 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
         <is>
           <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
@@ -4937,15 +6039,21 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
         <is>
           <t>27 ord: - analysera och värdera resultat i relation till tidigare forskning, värdera den…</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
         </is>
@@ -4964,15 +6072,21 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
         <is>
           <t>26 ord: - problematisera och reflektera över kvinnans, barnets och närståendes roller oc…</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
         </is>
@@ -4991,15 +6105,21 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
         <is>
           <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av o…</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29T</t>
         </is>
@@ -5018,15 +6138,21 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
         <is>
           <t>26 ord: - i simulerad miljö utföra undersökningar och behandlingar vid komplicerad gravi…</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
         </is>
@@ -5045,15 +6171,21 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr">
+      <c r="F171" t="inlineStr">
         <is>
           <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
         </is>
@@ -5072,15 +6204,21 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
         <is>
           <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
         </is>
@@ -5099,15 +6237,21 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
         <is>
           <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
         </is>
@@ -5126,15 +6270,21 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
         <is>
           <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29W</t>
         </is>
@@ -5153,15 +6303,21 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
         <is>
           <t>28 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av k…</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2AD</t>
         </is>
@@ -5180,15 +6336,21 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr">
+      <c r="F176" t="inlineStr">
         <is>
           <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2BM</t>
         </is>
@@ -5207,15 +6369,21 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
         <is>
           <t>26 ord: - redogöra för centrala begrepp inom global sexuell och reproduktiv hälsa och rä…</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CE</t>
         </is>
@@ -5234,15 +6402,21 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
+      <c r="F178" t="inlineStr">
         <is>
           <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CS</t>
         </is>
@@ -5261,15 +6435,21 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
         <is>
           <t>26 ord: - redogöra för och motivera metoder för att främja, undersöka och övervaka kvinn…</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CS</t>
         </is>
@@ -5288,15 +6468,21 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
         <is>
           <t>33 ord: - uppvisa kunskap, förståelse och reflekterande färdigheter om sexuell och repro…</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
         </is>
@@ -5315,15 +6501,21 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
         <is>
           <t>30 ord: - värdera olika strategier för ledarskap och interventioner som har potential at…</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
         </is>
@@ -5342,15 +6534,21 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
         <is>
           <t>27 ord: - analysera och kritiskt värdera styrkor och svagheter i forskningsprocessens ol…</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
         </is>
@@ -5369,15 +6567,21 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
+      <c r="F183" t="inlineStr">
         <is>
           <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
         </is>
@@ -5396,15 +6600,21 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
+          <t>2016-10-12</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr">
+      <c r="F184" t="inlineStr">
         <is>
           <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
         </is>
@@ -5423,15 +6633,25 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>2016-10-12</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
+          <t>2017-10-05</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
           <t>26 ord: - analysera betydelsen av hälsofrämjande arbete under den reproduktiva livscykel…</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
         </is>
@@ -5450,15 +6670,25 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>2016-10-12</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
+          <t>2017-10-05</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
           <t>29 ord: - identifiera problemområden och formulera relevanta frågeställningar som rör gr…</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
         </is>
@@ -5477,15 +6707,25 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>2016-10-12</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
+          <t>2017-10-05</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
           <t>27 ord: - redogöra för benigna och maligna gynekologiska förändringar, värdera hälsotill…</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
         </is>
@@ -5504,15 +6744,25 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>2016-10-12</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
+          <t>2017-10-05</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
           <t>27 ord: - i simulerad miljö utföra undersökningar och behandlingar vid handläggning av g…</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
         </is>
@@ -5531,15 +6781,25 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>2016-10-12</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
+          <t>2017-05-22</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
           <t>26 ord: - aktivt delta i vård av kvinnor med normal graviditet inför, under och efter fö…</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
         </is>
@@ -5558,15 +6818,21 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
+          <t>2016-10-12</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr">
+      <c r="F190" t="inlineStr">
         <is>
           <t>13 lärandemål (maximum rekommenderat: 10 för 9 hp)</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
@@ -5585,15 +6851,21 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
+          <t>2016-10-12</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
         <is>
           <t>26 ord: - aktivt delta i abortverksamhet och visa på självständighet i vården av kvinnor…</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
@@ -5612,15 +6884,21 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
+          <t>2016-10-12</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
         <is>
           <t>29 ord: - tillämpa ett professionellt förhållningssätt i kommunikation med vårdtagare oc…</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
@@ -5639,15 +6917,25 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
+          <t>2016-10-12</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2017-05-22</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr">
+      <c r="F193" t="inlineStr">
         <is>
           <t>11 lärandemål (maximum rekommenderat: 10 för 13.5 hp)</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
         </is>
@@ -5666,15 +6954,25 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>2016-10-12</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
+          <t>2017-05-22</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
           <t>30 ord: - med ett professionellt förhållningssätt informera, ge stöd och trygghet i dial…</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
         </is>
@@ -5693,15 +6991,25 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
+          <t>2016-10-12</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2018-01-10</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr">
+      <c r="F195" t="inlineStr">
         <is>
           <t>14 lärandemål (maximum rekommenderat: 10 för 13.5 hp)</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
         </is>
@@ -5720,15 +7028,25 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>2016-10-12</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
+          <t>2018-01-10</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
           <t>35 ord: - självständigt handlägga preventivmedelsrådgivning och informera om lämpliga an…</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="G196" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
         </is>
@@ -5747,15 +7065,25 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>2016-10-12</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
+          <t>2018-01-10</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
           <t>26 ord: - kritiskt analysera, värdera, föreslå och följa upp vårdnadsinsatser och behand…</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="G197" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
         </is>
@@ -5774,15 +7102,21 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
         <is>
           <t>26 ord: - kritiskt reflektera över hur kvalitets- och säkerhetsledning organiseras och r…</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="G198" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV2A6</t>
         </is>
@@ -5801,15 +7135,25 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>2009-09-01</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
+          <t>2012-03-05</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
           <t>29 ord: - redogöra för gällande regelverk för olika professioner inom kommunal äldreomso…</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="G199" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
         </is>
@@ -5828,15 +7172,25 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
+          <t>2009-04-21</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2010-10-18</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr">
+      <c r="F200" t="inlineStr">
         <is>
           <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
         </is>
@@ -5855,15 +7209,25 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
+          <t>2010-06-01</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2010-10-18</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
+      <c r="F201" t="inlineStr">
         <is>
           <t>19 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="G201" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
         </is>
@@ -5882,15 +7246,25 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>2012-01-12</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
+          <t>2018-11-14</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
           <t>29 ord: - tillämpa adekvat vetenskaplig design och metod i datainsamling och analys samt…</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
         </is>
@@ -5909,15 +7283,25 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>2012-01-12</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
+          <t>2018-11-14</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
           <t>29 ord: - analysera och värdera resultat i relation till tidigare forskning samt den kli…</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
         </is>
@@ -5936,15 +7320,21 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
+          <t>2015-12-22</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
         <is>
           <t>29 ord: - tillämpa adekvat vetenskaplig design och metod i datainsamling och analys samt…</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
         </is>
@@ -5963,15 +7353,21 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
+          <t>2015-12-22</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
         <is>
           <t>29 ord: - analysera och värdera resultat i relation till tidigare forskning samt den kli…</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="G205" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
         </is>
@@ -5990,15 +7386,21 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
+          <t>2015-12-22</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
         <is>
           <t>26 ord: - göra relevanta bedömningar på mikro-, meso- och makronivå med hänsyn till samh…</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="G206" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
         </is>
@@ -6017,15 +7419,21 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
+          <t>2018-01-25</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
           <t>För många mål</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr">
+      <c r="F207" t="inlineStr">
         <is>
           <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="G207" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0001</t>
         </is>
@@ -6044,15 +7452,25 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
+          <t>2018-03-28</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2022-09-28</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
           <t>För få mål</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
+      <c r="F208" t="inlineStr">
         <is>
           <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="G208" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0002</t>
         </is>
@@ -6071,439 +7489,445 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
+          <t>2018-11-01</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
           <t>För få mål</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
+      <c r="F209" t="inlineStr">
         <is>
           <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="G209" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0003</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E209"/>
+  <autoFilter ref="A1:G209"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId188"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId192"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId196"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId202"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId204"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId206"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId208"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId210"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId212"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId214"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId216"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId218"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId220"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId222"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId224"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId226"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId228"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId230"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId232"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId234"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId236"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId238"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId240"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId242"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId244"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId246"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId248"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId250"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId252"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId254"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId256"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId258"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId260"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId262"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId264"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId266"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId268"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId270"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId272"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId274"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId276"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId278"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId280"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId282"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId284"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId286"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId288"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId290"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId292"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId294"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId296"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId298"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId300"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId302"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId304"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId306"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId308"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId310"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId312"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId314"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G159" r:id="rId316"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId318"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId320"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G162" r:id="rId322"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G163" r:id="rId324"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId326"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G165" r:id="rId328"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId330"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G167" r:id="rId332"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G168" r:id="rId334"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G169" r:id="rId336"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G170" r:id="rId338"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G171" r:id="rId340"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId342"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G173" r:id="rId344"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G174" r:id="rId346"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A175" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E175" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G175" r:id="rId348"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A176" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G176" r:id="rId350"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId352"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId354"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A179" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId356"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A180" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId358"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A181" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId360"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A182" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId362"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A183" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId364"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A184" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId366"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A185" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G185" r:id="rId368"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A186" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G186" r:id="rId370"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A187" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G187" r:id="rId372"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A188" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G188" r:id="rId374"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId376"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G190" r:id="rId378"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId380"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId382"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G193" r:id="rId384"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G194" r:id="rId386"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A195" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId388"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A196" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G196" r:id="rId390"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A197" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G197" r:id="rId392"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A198" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G198" r:id="rId394"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G199" r:id="rId396"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G200" r:id="rId398"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A201" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G201" r:id="rId400"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A202" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G202" r:id="rId402"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A203" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId404"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A204" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId406"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A205" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId408"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A206" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId410"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A207" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId412"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A208" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId414"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A209" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G209" r:id="rId416"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
